--- a/database/Take Notes/RL/RL.xlsx
+++ b/database/Take Notes/RL/RL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Cursor AI\database\Take Notes\RL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA1B621F-9F49-4460-8C0C-15BCC4A0FCE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11A2E230-8242-4DFA-8655-3648403BED19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1089" uniqueCount="1089">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1090" uniqueCount="1090">
   <si>
     <t>ID</t>
   </si>
@@ -3650,6 +3650,9 @@
   </si>
   <si>
     <t>https://youtu.be/b-4VYNbBKVw</t>
+  </si>
+  <si>
+    <t>https://youtu.be/H9750VLTvt0</t>
   </si>
 </sst>
 </file>
@@ -3719,15 +3722,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -4053,7 +4053,7 @@
       <c r="E1" s="2" t="s">
         <v>1083</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="2" t="s">
         <v>1087</v>
       </c>
     </row>
@@ -4086,6 +4086,9 @@
       </c>
       <c r="C3" t="s">
         <v>543</v>
+      </c>
+      <c r="F3" t="s">
+        <v>1089</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">

--- a/database/Take Notes/RL/RL.xlsx
+++ b/database/Take Notes/RL/RL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Cursor AI\database\Take Notes\RL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11A2E230-8242-4DFA-8655-3648403BED19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B57E6282-4218-4CA2-9B8E-B7252A83C886}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1090" uniqueCount="1090">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1631" uniqueCount="1095">
   <si>
     <t>ID</t>
   </si>
@@ -3654,12 +3654,285 @@
   <si>
     <t>https://youtu.be/H9750VLTvt0</t>
   </si>
+  <si>
+    <t>Podcast Conversation: What Is Supersymmetry? (A2–B1 Level)
+Host:
+Welcome to today’s science podcast! I am Bel, and today we are talking about supersymmetry. It sounds difficult, but we will explain it in a simple way. So, what is supersymmetry?
+Expert:
+Supersymmetry is a mathematical idea. Scientists use it to understand the basic parts of matter and how they are organized.
+Host:
+Why do scientists use ideas like symmetry?
+Expert:
+Because we have learned that things that look different can actually be connected by symmetry.
+For example, think about a sphere, like a basketball. When you turn it, it looks different, but it is still the same shape.
+Host:
+So symmetry means something stays the same, even when it changes?
+Expert:
+Yes, exactly. In physics, we found that some particles can change into other particles, but the math equations describing them stay the same.
+Host:
+That sounds interesting. But what was missing?
+Expert:
+What we could not find was a symmetry that connects two big groups of particles:
+matter particles and force particles.
+Host:
+What are matter particles?
+Expert:
+Matter particles are particles that make things. For example, electrons, muons, and quarks.
+Host:
+And force particles?
+Expert:
+Force particles carry forces. For example, photons, gluons, and W and Z bosons.
+Host:
+So how does supersymmetry help?
+Expert:
+Supersymmetry is a symmetry that connects matter particles and force particles.
+It says they are related at a deep level.
+Host:
+Does supersymmetry exist in the real world?
+Expert:
+Mathematically, scientists have shown that supersymmetry could be the last possible symmetry of fundamental particles.
+But so far, we have no clear evidence that nature uses it.
+Host:
+So what are scientists doing now?
+Expert:
+They are looking for evidence. They want to see if supersymmetry is really working in the universe.
+✅ Final Recap
+Host:
+Now let’s recap what we learned today.
+Supersymmetry is a mathematical idea.
+Symmetry means something stays the same after a change.
+Particles can look different but follow the same rules.
+There are matter particles and force particles.
+Supersymmetry connects these two groups.
+Scientists are still searching for proof in the real world.
+Host:
+That’s the main ideas that you learned today!
+I’m Bel — thank you for listening.
+Like and subscribe for Better English Learning!</t>
+  </si>
+  <si>
+    <t>Welcome to today’s science podcast! I am Bel, and today we are talking about supersymmetry. It sounds difficult, but we will explain it in a simple way. So, what is supersymmetry?
+Supersymmetry is a mathematical idea. Scientists use it to understand the basic parts of matter and how they are organized.
+Why do scientists use ideas like symmetry?
+Because we have learned that things that look different can actually be connected by symmetry.
+For example, think about a sphere, like a basketball. When you turn it, it looks different, but it is still the same shape.
+So symmetry means something stays the same, even when it changes?
+Yes, exactly. In physics, we found that some particles can change into other particles, but the math equations describing them stay the same.
+That sounds interesting. But what was missing?
+What we could not find was a symmetry that connects two big groups of particles: matter particles and force particles.
+What are matter particles?
+Matter particles are particles that make things. For example, electrons, muons, and quarks.
+And force particles?
+Force particles carry forces. For example, photons, gluons, and W and Z bosons.
+So how does supersymmetry help?
+Supersymmetry is a symmetry that connects matter particles and force particles. It says they are related at a deep level.
+Does supersymmetry exist in the real world?
+Mathematically, scientists have shown that supersymmetry could be the last possible symmetry of fundamental particles. But so far, we have no clear evidence that nature uses it.
+So what are scientists doing now?
+They are looking for evidence. They want to see if supersymmetry is really working in the universe.
+Now let’s recap what we learned today.
+Supersymmetry is a mathematical idea.
+Symmetry means something stays the same after a change.
+Particles can look different but follow the same rules.
+There are matter particles and force particles.
+Supersymmetry connects these two groups.
+Scientists are still searching for proof in the real world.
+That's the main ideas that you learned today! We will now review some new vocabularies.
+Repeat after me.
+Supersymmetry
+&lt;break time="2s" /&gt; 
+Supersymmetry
+&lt;break time="2s" /&gt;
+Supersymmetry
+&lt;break time="2s" /&gt; 
+Good job! Supersymmetry is a mathematical idea that connects particles. Next word.
+Symmetry
+&lt;break time="2s" /&gt; 
+Symmetry
+&lt;break time="2s" /&gt; 
+Symmetry
+&lt;break time="2s" /&gt; 
+Great! Symmetry means something stays the same after a change. Next word.
+Particle
+&lt;break time="2s" /&gt; 
+Particle
+&lt;break time="2s" /&gt; 
+Particle
+&lt;break time="2s" /&gt; 
+Well done! A particle is a very small part of matter. Next.
+Matter particle
+&lt;break time="1s" /&gt; 
+Matter particle
+&lt;break time="1s" /&gt; 
+Matter particle
+&lt;break time="1s" /&gt; 
+A matter particle helps make things, like electrons. Next!
+Force particle
+&lt;break time="1s" /&gt; 
+Force particle
+&lt;break time="1s" /&gt; 
+Force particle
+&lt;break time="1s" /&gt; 
+A force particle carries forces, like light or energy. Next.
+Equation
+&lt;break time="1s" /&gt; 
+Equation
+&lt;break time="1s" /&gt; 
+Equation
+&lt;break time="1s" /&gt; 
+An equation is a math sentence that explains how things work. Last one!
+Evidence
+&lt;break time="1s" /&gt; 
+Evidence
+&lt;break time="1s" /&gt; 
+Evidence
+&lt;break time="1s" /&gt; 
+Well done! Evidence is proof that something is true.
+That's the end of the video!  
+I’m Bel — like and subscribe for Better English Learning!</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>Podcast Conversation: Changes in Air Pollution (A2–B1 Level)
+Host:
+Welcome to today’s science podcast! I am Bel, and today we are talking about air pollution and how it has changed since the 1950s. What was air pollution like in the past?
+Expert:
+In the 1950s, air pollution was very easy to see. Many big cities had thick black fogs called smogs.
+Host:
+What caused these smogs?
+Expert:
+The main cause was factories. They burned a lot of coal, and this caused serious health problems.
+Host:
+Was it dangerous?
+Expert:
+Yes, very dangerous. In London, in 1952, a very bad smog caused over four thousand deaths.
+Host:
+That sounds terrible. What did people do?
+Expert:
+In 1956, Britain introduced the Clean Air Act. This law controlled pollution from factories.
+Host:
+And did it work?
+Expert:
+Yes. After that, the black smogs disappeared.
+Host:
+But air pollution is still a problem today, right?
+Expert:
+Yes, it is. The big difference today is that air pollution is mostly invisible.
+Host:
+So where does pollution come from now?
+Expert:
+Today, the main source is vehicles, like cars and lorries. They don’t make black smoke, but they still harm our health.
+Host:
+Why is this type of pollution increasing?
+Expert:
+Because we are much more vehicle-dependent.
+There are far more cars, lorries, trains, and planes than in the 1950s.
+Host:
+Let me check if I understand.
+Host:
+In the past, factories caused visible smog.
+Today, vehicles cause invisible pollution.
+Both are dangerous to health.
+Expert:
+Exactly. Vehicle pollution is now the main source of air pollution around the world.
+✅ Final Recap
+Host:
+Now let’s recap what we learned today.
+In the 1950s, air pollution was visible.
+Thick black smogs came from factories.
+Smog caused serious health problems.
+The Clean Air Act helped reduce factory pollution.
+Today, air pollution is mostly invisible.
+Cars and lorries are now the main source.
+Host:
+That’s the main ideas that you learned today!
+I’m Bel — thank you for listening.
+Like and subscribe for Better English Learning!</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Welcome to today’s science podcast! I am Bel, and today we are talking about air pollution and how it has changed since the 1950s.
+In today’s lecture, I’m going to talk about changes in air pollution since the middle of the last century and what caused these changes.
+By the 1950s, air pollution was very visible. Many large cities had thick black fogs called smogs.
+The main source of this pollution was factories, and it caused serious health problems.
+For example, in London in 1952, a very severe smog caused over four thousand deaths.
+Because of this, something had to be done.
+In 1956, a Clean Air Act was introduced in Britain. This law controlled pollution from factories, and the smogs soon disappeared.
+However, today air pollution is still a big problem.
+The main difference now is that air pollution is invisible.
+The main source of pollution today is vehicles, such as cars and lorries.
+These vehicles do not produce black smoke, but they still cause health risks.
+One important reason for this pollution is that we are much more vehicle-dependent.
+There are far more cars, lorries, trains, and planes than in the 1950s.
+Today, vehicles are the main source of air pollution around the world.
+Now let’s recap what we learned today.
+In the past, air pollution was easy to see.
+Factories caused thick black smogs.
+Smogs caused serious health problems.
+The Clean Air Act helped reduce pollution.
+Today, air pollution is invisible.
+Vehicles are now the main source of air pollution.
+That's the main ideas that you learned today! We will now review some new vocabularies.
+Repeat after me.
+Air pollution
+&lt;break time="2s" /&gt; 
+Air pollution
+&lt;break time="2s" /&gt;
+Air pollution
+&lt;break time="2s" /&gt; 
+Good job! Air pollution means dirty or harmful air. Next word.
+Smog
+&lt;break time="2s" /&gt; 
+Smog
+&lt;break time="2s" /&gt; 
+Smog
+&lt;break time="2s" /&gt; 
+Great! Smog is thick, dirty air that you can see. Next word.
+Factory
+&lt;break time="2s" /&gt; 
+Factory
+&lt;break time="2s" /&gt; 
+Factory
+&lt;break time="2s" /&gt; 
+Well done! A factory is a place where things are made. Next.
+Clean Air Act
+&lt;break time="1s" /&gt; 
+Clean Air Act
+&lt;break time="1s" /&gt; 
+Clean Air Act
+&lt;break time="1s" /&gt; 
+The Clean Air Act is a law to reduce air pollution. Next!
+Vehicle
+&lt;break time="1s" /&gt; 
+Vehicle
+&lt;break time="1s" /&gt; 
+Vehicle
+&lt;break time="1s" /&gt; 
+A vehicle is something we use to travel, like a car or bus. Next.
+Health risk
+&lt;break time="1s" /&gt; 
+Health risk
+&lt;break time="1s" /&gt; 
+Health risk
+&lt;break time="1s" /&gt; 
+A health risk is something that can harm your health. Last one!
+Vehicle-dependent
+&lt;break time="1s" /&gt; 
+Vehicle-dependent
+&lt;break time="1s" /&gt; 
+Vehicle-dependent
+&lt;break time="1s" /&gt; 
+Well done! Vehicle-dependent means needing vehicles to live and work.
+That's the end of the video!  
+I’m Bel — like and subscribe for Better English Learning!</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3671,6 +3944,14 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -3719,10 +4000,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -3730,8 +4012,11 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -4034,10 +4319,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F541"/>
+  <dimension ref="A1:H541"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="4" max="4" width="16.7109375" customWidth="1"/>
+    <col min="5" max="5" width="27.28515625" customWidth="1"/>
+    <col min="6" max="6" width="21.42578125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4057,7 +4347,7 @@
         <v>1087</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -4077,7 +4367,7 @@
         <v>1088</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -4090,8 +4380,11 @@
       <c r="F3" t="s">
         <v>1089</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H3" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -4101,8 +4394,17 @@
       <c r="C4" t="s">
         <v>544</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D4" t="s">
+        <v>1090</v>
+      </c>
+      <c r="E4" t="s">
+        <v>1091</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>1088</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -4112,8 +4414,14 @@
       <c r="C5" t="s">
         <v>545</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D5" s="3" t="s">
+        <v>1093</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>1094</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -4123,8 +4431,11 @@
       <c r="C6" t="s">
         <v>546</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E6" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -4134,8 +4445,11 @@
       <c r="C7" t="s">
         <v>547</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E7" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -4145,8 +4459,11 @@
       <c r="C8" t="s">
         <v>548</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E8" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -4156,8 +4473,11 @@
       <c r="C9" t="s">
         <v>549</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E9" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -4167,8 +4487,11 @@
       <c r="C10" t="s">
         <v>550</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E10" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
@@ -4178,8 +4501,11 @@
       <c r="C11" t="s">
         <v>551</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E11" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
@@ -4189,8 +4515,11 @@
       <c r="C12" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E12" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
@@ -4200,8 +4529,11 @@
       <c r="C13" t="s">
         <v>553</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E13" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
@@ -4211,8 +4543,11 @@
       <c r="C14" t="s">
         <v>554</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E14" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
@@ -4222,8 +4557,11 @@
       <c r="C15" t="s">
         <v>555</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E15" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
@@ -4233,8 +4571,11 @@
       <c r="C16" t="s">
         <v>556</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E16" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
@@ -4244,8 +4585,11 @@
       <c r="C17" t="s">
         <v>557</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E17" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
@@ -4255,8 +4599,11 @@
       <c r="C18" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E18" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
@@ -4266,8 +4613,11 @@
       <c r="C19" t="s">
         <v>559</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E19" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
@@ -4277,8 +4627,11 @@
       <c r="C20" t="s">
         <v>560</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E20" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
@@ -4288,8 +4641,11 @@
       <c r="C21" t="s">
         <v>561</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E21" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21</v>
       </c>
@@ -4299,8 +4655,11 @@
       <c r="C22" t="s">
         <v>562</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E22" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>22</v>
       </c>
@@ -4310,8 +4669,11 @@
       <c r="C23" t="s">
         <v>563</v>
       </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E23" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>23</v>
       </c>
@@ -4321,8 +4683,11 @@
       <c r="C24" t="s">
         <v>564</v>
       </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E24" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>24</v>
       </c>
@@ -4332,8 +4697,11 @@
       <c r="C25" t="s">
         <v>565</v>
       </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E25" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25</v>
       </c>
@@ -4343,8 +4711,11 @@
       <c r="C26" t="s">
         <v>566</v>
       </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E26" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26</v>
       </c>
@@ -4354,8 +4725,11 @@
       <c r="C27" t="s">
         <v>567</v>
       </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E27" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>27</v>
       </c>
@@ -4365,8 +4739,11 @@
       <c r="C28" t="s">
         <v>568</v>
       </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E28" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>28</v>
       </c>
@@ -4376,8 +4753,11 @@
       <c r="C29" t="s">
         <v>569</v>
       </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E29" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>29</v>
       </c>
@@ -4387,8 +4767,11 @@
       <c r="C30" t="s">
         <v>570</v>
       </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E30" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>30</v>
       </c>
@@ -4398,8 +4781,11 @@
       <c r="C31" t="s">
         <v>571</v>
       </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E31" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>31</v>
       </c>
@@ -4409,8 +4795,11 @@
       <c r="C32" t="s">
         <v>572</v>
       </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E32" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>32</v>
       </c>
@@ -4420,8 +4809,11 @@
       <c r="C33" t="s">
         <v>573</v>
       </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E33" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>33</v>
       </c>
@@ -4431,8 +4823,11 @@
       <c r="C34" t="s">
         <v>574</v>
       </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E34" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>34</v>
       </c>
@@ -4442,8 +4837,11 @@
       <c r="C35" t="s">
         <v>575</v>
       </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E35" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>35</v>
       </c>
@@ -4453,8 +4851,11 @@
       <c r="C36" t="s">
         <v>576</v>
       </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E36" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>36</v>
       </c>
@@ -4464,8 +4865,11 @@
       <c r="C37" t="s">
         <v>577</v>
       </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E37" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>37</v>
       </c>
@@ -4475,8 +4879,11 @@
       <c r="C38" t="s">
         <v>578</v>
       </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E38" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>38</v>
       </c>
@@ -4486,8 +4893,11 @@
       <c r="C39" t="s">
         <v>579</v>
       </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E39" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>39</v>
       </c>
@@ -4497,8 +4907,11 @@
       <c r="C40" t="s">
         <v>580</v>
       </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E40" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>40</v>
       </c>
@@ -4508,8 +4921,11 @@
       <c r="C41" t="s">
         <v>581</v>
       </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E41" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>41</v>
       </c>
@@ -4519,8 +4935,11 @@
       <c r="C42" t="s">
         <v>582</v>
       </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E42" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>42</v>
       </c>
@@ -4530,8 +4949,11 @@
       <c r="C43" t="s">
         <v>583</v>
       </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E43" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>43</v>
       </c>
@@ -4541,8 +4963,11 @@
       <c r="C44" t="s">
         <v>584</v>
       </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E44" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>44</v>
       </c>
@@ -4552,8 +4977,11 @@
       <c r="C45" t="s">
         <v>585</v>
       </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E45" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>45</v>
       </c>
@@ -4563,8 +4991,11 @@
       <c r="C46" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E46" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>46</v>
       </c>
@@ -4574,8 +5005,11 @@
       <c r="C47" t="s">
         <v>587</v>
       </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E47" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>47</v>
       </c>
@@ -4585,8 +5019,11 @@
       <c r="C48" t="s">
         <v>588</v>
       </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E48" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>48</v>
       </c>
@@ -4596,8 +5033,11 @@
       <c r="C49" t="s">
         <v>589</v>
       </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E49" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>49</v>
       </c>
@@ -4607,8 +5047,11 @@
       <c r="C50" t="s">
         <v>590</v>
       </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E50" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>50</v>
       </c>
@@ -4618,8 +5061,11 @@
       <c r="C51" t="s">
         <v>591</v>
       </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E51" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>51</v>
       </c>
@@ -4629,8 +5075,11 @@
       <c r="C52" t="s">
         <v>592</v>
       </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E52" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>52</v>
       </c>
@@ -4640,8 +5089,11 @@
       <c r="C53" t="s">
         <v>593</v>
       </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E53" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>53</v>
       </c>
@@ -4651,8 +5103,11 @@
       <c r="C54" t="s">
         <v>594</v>
       </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E54" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>54</v>
       </c>
@@ -4662,8 +5117,11 @@
       <c r="C55" t="s">
         <v>595</v>
       </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E55" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>56</v>
       </c>
@@ -4673,8 +5131,11 @@
       <c r="C56" t="s">
         <v>596</v>
       </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E56" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>57</v>
       </c>
@@ -4684,8 +5145,11 @@
       <c r="C57" t="s">
         <v>597</v>
       </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E57" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>58</v>
       </c>
@@ -4695,8 +5159,11 @@
       <c r="C58" t="s">
         <v>598</v>
       </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E58" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>59</v>
       </c>
@@ -4706,8 +5173,11 @@
       <c r="C59" t="s">
         <v>599</v>
       </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E59" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>60</v>
       </c>
@@ -4717,8 +5187,11 @@
       <c r="C60" t="s">
         <v>600</v>
       </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E60" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>61</v>
       </c>
@@ -4728,8 +5201,11 @@
       <c r="C61" t="s">
         <v>601</v>
       </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E61" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>62</v>
       </c>
@@ -4739,8 +5215,11 @@
       <c r="C62" t="s">
         <v>602</v>
       </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E62" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>63</v>
       </c>
@@ -4750,8 +5229,11 @@
       <c r="C63" t="s">
         <v>603</v>
       </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E63" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>64</v>
       </c>
@@ -4761,8 +5243,11 @@
       <c r="C64" t="s">
         <v>604</v>
       </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E64" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>65</v>
       </c>
@@ -4772,8 +5257,11 @@
       <c r="C65" t="s">
         <v>605</v>
       </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E65" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>66</v>
       </c>
@@ -4783,8 +5271,11 @@
       <c r="C66" t="s">
         <v>606</v>
       </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E66" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>67</v>
       </c>
@@ -4794,8 +5285,11 @@
       <c r="C67" t="s">
         <v>607</v>
       </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E67" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>68</v>
       </c>
@@ -4805,8 +5299,11 @@
       <c r="C68" t="s">
         <v>608</v>
       </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E68" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>69</v>
       </c>
@@ -4816,8 +5313,11 @@
       <c r="C69" t="s">
         <v>609</v>
       </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E69" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>70</v>
       </c>
@@ -4827,8 +5327,11 @@
       <c r="C70" t="s">
         <v>610</v>
       </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E70" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>71</v>
       </c>
@@ -4838,8 +5341,11 @@
       <c r="C71" t="s">
         <v>611</v>
       </c>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E71" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>72</v>
       </c>
@@ -4849,8 +5355,11 @@
       <c r="C72" t="s">
         <v>612</v>
       </c>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E72" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>73</v>
       </c>
@@ -4860,8 +5369,11 @@
       <c r="C73" t="s">
         <v>613</v>
       </c>
-    </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E73" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>74</v>
       </c>
@@ -4871,8 +5383,11 @@
       <c r="C74" t="s">
         <v>614</v>
       </c>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E74" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>75</v>
       </c>
@@ -4882,8 +5397,11 @@
       <c r="C75" t="s">
         <v>615</v>
       </c>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E75" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>76</v>
       </c>
@@ -4893,8 +5411,11 @@
       <c r="C76" t="s">
         <v>616</v>
       </c>
-    </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E76" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>77</v>
       </c>
@@ -4904,8 +5425,11 @@
       <c r="C77" t="s">
         <v>617</v>
       </c>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E77" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>78</v>
       </c>
@@ -4915,8 +5439,11 @@
       <c r="C78" t="s">
         <v>618</v>
       </c>
-    </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E78" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>79</v>
       </c>
@@ -4926,8 +5453,11 @@
       <c r="C79" t="s">
         <v>619</v>
       </c>
-    </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E79" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>80</v>
       </c>
@@ -4937,8 +5467,11 @@
       <c r="C80" t="s">
         <v>620</v>
       </c>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E80" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>81</v>
       </c>
@@ -4948,8 +5481,11 @@
       <c r="C81" t="s">
         <v>621</v>
       </c>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E81" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>82</v>
       </c>
@@ -4959,8 +5495,11 @@
       <c r="C82" t="s">
         <v>622</v>
       </c>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E82" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>83</v>
       </c>
@@ -4970,8 +5509,11 @@
       <c r="C83" t="s">
         <v>623</v>
       </c>
-    </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E83" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>84</v>
       </c>
@@ -4981,8 +5523,11 @@
       <c r="C84" t="s">
         <v>624</v>
       </c>
-    </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E84" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>85</v>
       </c>
@@ -4992,8 +5537,11 @@
       <c r="C85" t="s">
         <v>625</v>
       </c>
-    </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E85" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>86</v>
       </c>
@@ -5003,8 +5551,11 @@
       <c r="C86" t="s">
         <v>626</v>
       </c>
-    </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E86" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>87</v>
       </c>
@@ -5014,8 +5565,11 @@
       <c r="C87" t="s">
         <v>627</v>
       </c>
-    </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E87" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>88</v>
       </c>
@@ -5025,8 +5579,11 @@
       <c r="C88" t="s">
         <v>628</v>
       </c>
-    </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E88" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>89</v>
       </c>
@@ -5036,8 +5593,11 @@
       <c r="C89" t="s">
         <v>629</v>
       </c>
-    </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E89" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>90</v>
       </c>
@@ -5047,8 +5607,11 @@
       <c r="C90" t="s">
         <v>630</v>
       </c>
-    </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E90" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>91</v>
       </c>
@@ -5058,8 +5621,11 @@
       <c r="C91" t="s">
         <v>631</v>
       </c>
-    </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E91" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>92</v>
       </c>
@@ -5069,8 +5635,11 @@
       <c r="C92" t="s">
         <v>632</v>
       </c>
-    </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E92" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>93</v>
       </c>
@@ -5080,8 +5649,11 @@
       <c r="C93" t="s">
         <v>633</v>
       </c>
-    </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E93" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>94</v>
       </c>
@@ -5091,8 +5663,11 @@
       <c r="C94" t="s">
         <v>634</v>
       </c>
-    </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E94" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>95</v>
       </c>
@@ -5102,8 +5677,11 @@
       <c r="C95" t="s">
         <v>635</v>
       </c>
-    </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E95" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>96</v>
       </c>
@@ -5113,8 +5691,11 @@
       <c r="C96" t="s">
         <v>636</v>
       </c>
-    </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E96" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>97</v>
       </c>
@@ -5124,8 +5705,11 @@
       <c r="C97" t="s">
         <v>637</v>
       </c>
-    </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E97" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>98</v>
       </c>
@@ -5135,8 +5719,11 @@
       <c r="C98" t="s">
         <v>638</v>
       </c>
-    </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E98" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>99</v>
       </c>
@@ -5146,8 +5733,11 @@
       <c r="C99" t="s">
         <v>639</v>
       </c>
-    </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E99" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>100</v>
       </c>
@@ -5157,8 +5747,11 @@
       <c r="C100" t="s">
         <v>640</v>
       </c>
-    </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E100" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>101</v>
       </c>
@@ -5168,8 +5761,11 @@
       <c r="C101" t="s">
         <v>641</v>
       </c>
-    </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E101" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102">
         <v>102</v>
       </c>
@@ -5179,8 +5775,11 @@
       <c r="C102" t="s">
         <v>642</v>
       </c>
-    </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E102" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>103</v>
       </c>
@@ -5190,8 +5789,11 @@
       <c r="C103" t="s">
         <v>643</v>
       </c>
-    </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E103" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>104</v>
       </c>
@@ -5201,8 +5803,11 @@
       <c r="C104" t="s">
         <v>644</v>
       </c>
-    </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E104" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>105</v>
       </c>
@@ -5212,8 +5817,11 @@
       <c r="C105" t="s">
         <v>645</v>
       </c>
-    </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E105" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A106">
         <v>106</v>
       </c>
@@ -5223,8 +5831,11 @@
       <c r="C106" t="s">
         <v>646</v>
       </c>
-    </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E106" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A107">
         <v>107</v>
       </c>
@@ -5234,8 +5845,11 @@
       <c r="C107" t="s">
         <v>647</v>
       </c>
-    </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E107" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A108">
         <v>108</v>
       </c>
@@ -5245,8 +5859,11 @@
       <c r="C108" t="s">
         <v>648</v>
       </c>
-    </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E108" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A109">
         <v>109</v>
       </c>
@@ -5256,8 +5873,11 @@
       <c r="C109" t="s">
         <v>649</v>
       </c>
-    </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E109" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A110">
         <v>110</v>
       </c>
@@ -5267,8 +5887,11 @@
       <c r="C110" t="s">
         <v>650</v>
       </c>
-    </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E110" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A111">
         <v>111</v>
       </c>
@@ -5278,8 +5901,11 @@
       <c r="C111" t="s">
         <v>651</v>
       </c>
-    </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E111" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A112">
         <v>112</v>
       </c>
@@ -5289,8 +5915,11 @@
       <c r="C112" t="s">
         <v>652</v>
       </c>
-    </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E112" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A113">
         <v>113</v>
       </c>
@@ -5300,8 +5929,11 @@
       <c r="C113" t="s">
         <v>653</v>
       </c>
-    </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E113" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A114">
         <v>114</v>
       </c>
@@ -5311,8 +5943,11 @@
       <c r="C114" t="s">
         <v>654</v>
       </c>
-    </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E114" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A115">
         <v>115</v>
       </c>
@@ -5322,8 +5957,11 @@
       <c r="C115" t="s">
         <v>655</v>
       </c>
-    </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E115" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A116">
         <v>116</v>
       </c>
@@ -5333,8 +5971,11 @@
       <c r="C116" t="s">
         <v>656</v>
       </c>
-    </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E116" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A117">
         <v>117</v>
       </c>
@@ -5344,8 +5985,11 @@
       <c r="C117" t="s">
         <v>657</v>
       </c>
-    </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E117" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A118">
         <v>118</v>
       </c>
@@ -5355,8 +5999,11 @@
       <c r="C118" t="s">
         <v>658</v>
       </c>
-    </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E118" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A119">
         <v>119</v>
       </c>
@@ -5366,8 +6013,11 @@
       <c r="C119" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E119" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A120">
         <v>120</v>
       </c>
@@ -5377,8 +6027,11 @@
       <c r="C120" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E120" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A121">
         <v>121</v>
       </c>
@@ -5388,8 +6041,11 @@
       <c r="C121" t="s">
         <v>661</v>
       </c>
-    </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E121" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A122">
         <v>122</v>
       </c>
@@ -5399,8 +6055,11 @@
       <c r="C122" t="s">
         <v>662</v>
       </c>
-    </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E122" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A123">
         <v>123</v>
       </c>
@@ -5410,8 +6069,11 @@
       <c r="C123" t="s">
         <v>663</v>
       </c>
-    </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E123" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A124">
         <v>124</v>
       </c>
@@ -5421,8 +6083,11 @@
       <c r="C124" t="s">
         <v>664</v>
       </c>
-    </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E124" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A125">
         <v>125</v>
       </c>
@@ -5432,8 +6097,11 @@
       <c r="C125" t="s">
         <v>665</v>
       </c>
-    </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E125" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A126">
         <v>126</v>
       </c>
@@ -5443,8 +6111,11 @@
       <c r="C126" t="s">
         <v>666</v>
       </c>
-    </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E126" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A127">
         <v>127</v>
       </c>
@@ -5454,8 +6125,11 @@
       <c r="C127" t="s">
         <v>667</v>
       </c>
-    </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E127" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A128">
         <v>128</v>
       </c>
@@ -5465,8 +6139,11 @@
       <c r="C128" t="s">
         <v>668</v>
       </c>
-    </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E128" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A129">
         <v>129</v>
       </c>
@@ -5476,8 +6153,11 @@
       <c r="C129" t="s">
         <v>669</v>
       </c>
-    </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E129" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A130">
         <v>130</v>
       </c>
@@ -5487,8 +6167,11 @@
       <c r="C130" t="s">
         <v>670</v>
       </c>
-    </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E130" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A131">
         <v>131</v>
       </c>
@@ -5498,8 +6181,11 @@
       <c r="C131" t="s">
         <v>671</v>
       </c>
-    </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E131" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A132">
         <v>132</v>
       </c>
@@ -5509,8 +6195,11 @@
       <c r="C132" t="s">
         <v>672</v>
       </c>
-    </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E132" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A133">
         <v>133</v>
       </c>
@@ -5520,8 +6209,11 @@
       <c r="C133" t="s">
         <v>673</v>
       </c>
-    </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E133" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A134">
         <v>134</v>
       </c>
@@ -5531,8 +6223,11 @@
       <c r="C134" t="s">
         <v>674</v>
       </c>
-    </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E134" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A135">
         <v>135</v>
       </c>
@@ -5542,8 +6237,11 @@
       <c r="C135" t="s">
         <v>675</v>
       </c>
-    </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E135" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A136">
         <v>136</v>
       </c>
@@ -5553,8 +6251,11 @@
       <c r="C136" t="s">
         <v>676</v>
       </c>
-    </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E136" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A137">
         <v>137</v>
       </c>
@@ -5564,8 +6265,11 @@
       <c r="C137" t="s">
         <v>677</v>
       </c>
-    </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E137" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A138">
         <v>138</v>
       </c>
@@ -5575,8 +6279,11 @@
       <c r="C138" t="s">
         <v>678</v>
       </c>
-    </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E138" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A139">
         <v>139</v>
       </c>
@@ -5586,8 +6293,11 @@
       <c r="C139" t="s">
         <v>679</v>
       </c>
-    </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E139" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A140">
         <v>140</v>
       </c>
@@ -5597,8 +6307,11 @@
       <c r="C140" t="s">
         <v>680</v>
       </c>
-    </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E140" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A141">
         <v>141</v>
       </c>
@@ -5608,8 +6321,11 @@
       <c r="C141" t="s">
         <v>681</v>
       </c>
-    </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E141" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A142">
         <v>142</v>
       </c>
@@ -5619,8 +6335,11 @@
       <c r="C142" t="s">
         <v>682</v>
       </c>
-    </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E142" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A143">
         <v>143</v>
       </c>
@@ -5630,8 +6349,11 @@
       <c r="C143" t="s">
         <v>683</v>
       </c>
-    </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E143" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A144">
         <v>144</v>
       </c>
@@ -5641,8 +6363,11 @@
       <c r="C144" t="s">
         <v>684</v>
       </c>
-    </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E144" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A145">
         <v>145</v>
       </c>
@@ -5652,8 +6377,11 @@
       <c r="C145" t="s">
         <v>685</v>
       </c>
-    </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E145" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A146">
         <v>146</v>
       </c>
@@ -5663,8 +6391,11 @@
       <c r="C146" t="s">
         <v>686</v>
       </c>
-    </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E146" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A147">
         <v>147</v>
       </c>
@@ -5674,8 +6405,11 @@
       <c r="C147" t="s">
         <v>687</v>
       </c>
-    </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E147" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A148">
         <v>148</v>
       </c>
@@ -5685,8 +6419,11 @@
       <c r="C148" t="s">
         <v>688</v>
       </c>
-    </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E148" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A149">
         <v>149</v>
       </c>
@@ -5696,8 +6433,11 @@
       <c r="C149" t="s">
         <v>689</v>
       </c>
-    </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E149" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A150">
         <v>150</v>
       </c>
@@ -5707,8 +6447,11 @@
       <c r="C150" t="s">
         <v>690</v>
       </c>
-    </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E150" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A151">
         <v>151</v>
       </c>
@@ -5718,8 +6461,11 @@
       <c r="C151" t="s">
         <v>691</v>
       </c>
-    </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E151" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A152">
         <v>152</v>
       </c>
@@ -5729,8 +6475,11 @@
       <c r="C152" t="s">
         <v>692</v>
       </c>
-    </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E152" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A153">
         <v>153</v>
       </c>
@@ -5740,8 +6489,11 @@
       <c r="C153" t="s">
         <v>693</v>
       </c>
-    </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E153" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A154">
         <v>154</v>
       </c>
@@ -5751,8 +6503,11 @@
       <c r="C154" t="s">
         <v>694</v>
       </c>
-    </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E154" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A155">
         <v>155</v>
       </c>
@@ -5762,8 +6517,11 @@
       <c r="C155" t="s">
         <v>695</v>
       </c>
-    </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E155" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A156">
         <v>156</v>
       </c>
@@ -5773,8 +6531,11 @@
       <c r="C156" t="s">
         <v>696</v>
       </c>
-    </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E156" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="157" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A157">
         <v>157</v>
       </c>
@@ -5784,8 +6545,11 @@
       <c r="C157" t="s">
         <v>697</v>
       </c>
-    </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E157" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="158" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A158">
         <v>159</v>
       </c>
@@ -5795,8 +6559,11 @@
       <c r="C158" t="s">
         <v>698</v>
       </c>
-    </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E158" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="159" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A159">
         <v>160</v>
       </c>
@@ -5806,8 +6573,11 @@
       <c r="C159" t="s">
         <v>699</v>
       </c>
-    </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E159" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="160" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A160">
         <v>161</v>
       </c>
@@ -5817,8 +6587,11 @@
       <c r="C160" t="s">
         <v>700</v>
       </c>
-    </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E160" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="161" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A161">
         <v>162</v>
       </c>
@@ -5828,8 +6601,11 @@
       <c r="C161" t="s">
         <v>701</v>
       </c>
-    </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E161" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="162" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A162">
         <v>163</v>
       </c>
@@ -5839,8 +6615,11 @@
       <c r="C162" t="s">
         <v>702</v>
       </c>
-    </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E162" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="163" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A163">
         <v>164</v>
       </c>
@@ -5850,8 +6629,11 @@
       <c r="C163" t="s">
         <v>703</v>
       </c>
-    </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E163" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="164" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A164">
         <v>165</v>
       </c>
@@ -5861,8 +6643,11 @@
       <c r="C164" t="s">
         <v>704</v>
       </c>
-    </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E164" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="165" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A165">
         <v>166</v>
       </c>
@@ -5872,8 +6657,11 @@
       <c r="C165" t="s">
         <v>705</v>
       </c>
-    </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E165" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="166" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A166">
         <v>167</v>
       </c>
@@ -5883,8 +6671,11 @@
       <c r="C166" t="s">
         <v>706</v>
       </c>
-    </row>
-    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E166" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="167" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A167">
         <v>168</v>
       </c>
@@ -5894,8 +6685,11 @@
       <c r="C167" t="s">
         <v>707</v>
       </c>
-    </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E167" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="168" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A168">
         <v>169</v>
       </c>
@@ -5905,8 +6699,11 @@
       <c r="C168" t="s">
         <v>708</v>
       </c>
-    </row>
-    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E168" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="169" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A169">
         <v>170</v>
       </c>
@@ -5916,8 +6713,11 @@
       <c r="C169" t="s">
         <v>709</v>
       </c>
-    </row>
-    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E169" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="170" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A170">
         <v>171</v>
       </c>
@@ -5927,8 +6727,11 @@
       <c r="C170" t="s">
         <v>710</v>
       </c>
-    </row>
-    <row r="171" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E170" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="171" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A171">
         <v>172</v>
       </c>
@@ -5938,8 +6741,11 @@
       <c r="C171" t="s">
         <v>711</v>
       </c>
-    </row>
-    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E171" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="172" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A172">
         <v>173</v>
       </c>
@@ -5949,8 +6755,11 @@
       <c r="C172" t="s">
         <v>712</v>
       </c>
-    </row>
-    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E172" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="173" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A173">
         <v>174</v>
       </c>
@@ -5960,8 +6769,11 @@
       <c r="C173" t="s">
         <v>713</v>
       </c>
-    </row>
-    <row r="174" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E173" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="174" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A174">
         <v>175</v>
       </c>
@@ -5971,8 +6783,11 @@
       <c r="C174" t="s">
         <v>714</v>
       </c>
-    </row>
-    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E174" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="175" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A175">
         <v>180</v>
       </c>
@@ -5982,8 +6797,11 @@
       <c r="C175" t="s">
         <v>715</v>
       </c>
-    </row>
-    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E175" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="176" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A176">
         <v>181</v>
       </c>
@@ -5993,8 +6811,11 @@
       <c r="C176" t="s">
         <v>716</v>
       </c>
-    </row>
-    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E176" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="177" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A177">
         <v>182</v>
       </c>
@@ -6004,8 +6825,11 @@
       <c r="C177" t="s">
         <v>717</v>
       </c>
-    </row>
-    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E177" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="178" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A178">
         <v>183</v>
       </c>
@@ -6015,8 +6839,11 @@
       <c r="C178" t="s">
         <v>718</v>
       </c>
-    </row>
-    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E178" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="179" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A179">
         <v>184</v>
       </c>
@@ -6026,8 +6853,11 @@
       <c r="C179" t="s">
         <v>719</v>
       </c>
-    </row>
-    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E179" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="180" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A180">
         <v>185</v>
       </c>
@@ -6037,8 +6867,11 @@
       <c r="C180" t="s">
         <v>720</v>
       </c>
-    </row>
-    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E180" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="181" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A181">
         <v>186</v>
       </c>
@@ -6048,8 +6881,11 @@
       <c r="C181" t="s">
         <v>721</v>
       </c>
-    </row>
-    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E181" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="182" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A182">
         <v>188</v>
       </c>
@@ -6059,8 +6895,11 @@
       <c r="C182" t="s">
         <v>722</v>
       </c>
-    </row>
-    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E182" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="183" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A183">
         <v>189</v>
       </c>
@@ -6070,8 +6909,11 @@
       <c r="C183" t="s">
         <v>723</v>
       </c>
-    </row>
-    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E183" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="184" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A184">
         <v>191</v>
       </c>
@@ -6081,8 +6923,11 @@
       <c r="C184" t="s">
         <v>724</v>
       </c>
-    </row>
-    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E184" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="185" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A185">
         <v>192</v>
       </c>
@@ -6092,8 +6937,11 @@
       <c r="C185" t="s">
         <v>725</v>
       </c>
-    </row>
-    <row r="186" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E185" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="186" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A186">
         <v>193</v>
       </c>
@@ -6103,8 +6951,11 @@
       <c r="C186" t="s">
         <v>726</v>
       </c>
-    </row>
-    <row r="187" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E186" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="187" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A187">
         <v>194</v>
       </c>
@@ -6114,8 +6965,11 @@
       <c r="C187" t="s">
         <v>727</v>
       </c>
-    </row>
-    <row r="188" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E187" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="188" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A188">
         <v>199</v>
       </c>
@@ -6125,8 +6979,11 @@
       <c r="C188" t="s">
         <v>728</v>
       </c>
-    </row>
-    <row r="189" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E188" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="189" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A189">
         <v>200</v>
       </c>
@@ -6136,8 +6993,11 @@
       <c r="C189" t="s">
         <v>729</v>
       </c>
-    </row>
-    <row r="190" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E189" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="190" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A190">
         <v>203</v>
       </c>
@@ -6147,8 +7007,11 @@
       <c r="C190" t="s">
         <v>730</v>
       </c>
-    </row>
-    <row r="191" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E190" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="191" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A191">
         <v>216</v>
       </c>
@@ -6158,8 +7021,11 @@
       <c r="C191" t="s">
         <v>731</v>
       </c>
-    </row>
-    <row r="192" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E191" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="192" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A192">
         <v>217</v>
       </c>
@@ -6169,8 +7035,11 @@
       <c r="C192" t="s">
         <v>732</v>
       </c>
-    </row>
-    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E192" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="193" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A193">
         <v>223</v>
       </c>
@@ -6180,8 +7049,11 @@
       <c r="C193" t="s">
         <v>733</v>
       </c>
-    </row>
-    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E193" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="194" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A194">
         <v>229</v>
       </c>
@@ -6191,8 +7063,11 @@
       <c r="C194" t="s">
         <v>734</v>
       </c>
-    </row>
-    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E194" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="195" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A195">
         <v>230</v>
       </c>
@@ -6202,8 +7077,11 @@
       <c r="C195" t="s">
         <v>735</v>
       </c>
-    </row>
-    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E195" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="196" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A196">
         <v>232</v>
       </c>
@@ -6213,8 +7091,11 @@
       <c r="C196" t="s">
         <v>736</v>
       </c>
-    </row>
-    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E196" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="197" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A197">
         <v>233</v>
       </c>
@@ -6224,8 +7105,11 @@
       <c r="C197" t="s">
         <v>737</v>
       </c>
-    </row>
-    <row r="198" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E197" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="198" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A198">
         <v>234</v>
       </c>
@@ -6235,8 +7119,11 @@
       <c r="C198" t="s">
         <v>738</v>
       </c>
-    </row>
-    <row r="199" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E198" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="199" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A199">
         <v>235</v>
       </c>
@@ -6246,8 +7133,11 @@
       <c r="C199" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="200" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E199" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="200" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A200">
         <v>237</v>
       </c>
@@ -6257,8 +7147,11 @@
       <c r="C200" t="s">
         <v>740</v>
       </c>
-    </row>
-    <row r="201" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E200" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="201" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A201">
         <v>238</v>
       </c>
@@ -6268,8 +7161,11 @@
       <c r="C201" t="s">
         <v>741</v>
       </c>
-    </row>
-    <row r="202" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E201" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="202" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A202">
         <v>240</v>
       </c>
@@ -6279,8 +7175,11 @@
       <c r="C202" t="s">
         <v>742</v>
       </c>
-    </row>
-    <row r="203" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E202" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="203" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A203">
         <v>242</v>
       </c>
@@ -6290,8 +7189,11 @@
       <c r="C203" t="s">
         <v>743</v>
       </c>
-    </row>
-    <row r="204" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E203" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="204" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A204">
         <v>243</v>
       </c>
@@ -6301,8 +7203,11 @@
       <c r="C204" t="s">
         <v>744</v>
       </c>
-    </row>
-    <row r="205" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E204" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="205" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A205">
         <v>244</v>
       </c>
@@ -6312,8 +7217,11 @@
       <c r="C205" t="s">
         <v>745</v>
       </c>
-    </row>
-    <row r="206" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E205" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="206" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A206">
         <v>245</v>
       </c>
@@ -6323,8 +7231,11 @@
       <c r="C206" t="s">
         <v>746</v>
       </c>
-    </row>
-    <row r="207" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E206" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="207" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A207">
         <v>247</v>
       </c>
@@ -6334,8 +7245,11 @@
       <c r="C207" t="s">
         <v>747</v>
       </c>
-    </row>
-    <row r="208" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E207" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="208" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A208">
         <v>248</v>
       </c>
@@ -6345,8 +7259,11 @@
       <c r="C208" t="s">
         <v>748</v>
       </c>
-    </row>
-    <row r="209" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E208" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="209" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A209">
         <v>249</v>
       </c>
@@ -6356,8 +7273,11 @@
       <c r="C209" t="s">
         <v>749</v>
       </c>
-    </row>
-    <row r="210" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E209" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="210" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A210">
         <v>250</v>
       </c>
@@ -6367,8 +7287,11 @@
       <c r="C210" t="s">
         <v>750</v>
       </c>
-    </row>
-    <row r="211" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E210" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="211" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A211">
         <v>252</v>
       </c>
@@ -6378,8 +7301,11 @@
       <c r="C211" t="s">
         <v>751</v>
       </c>
-    </row>
-    <row r="212" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E211" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="212" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A212">
         <v>253</v>
       </c>
@@ -6389,8 +7315,11 @@
       <c r="C212" t="s">
         <v>752</v>
       </c>
-    </row>
-    <row r="213" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E212" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="213" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A213">
         <v>254</v>
       </c>
@@ -6400,8 +7329,11 @@
       <c r="C213" t="s">
         <v>753</v>
       </c>
-    </row>
-    <row r="214" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E213" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="214" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A214">
         <v>256</v>
       </c>
@@ -6411,8 +7343,11 @@
       <c r="C214" t="s">
         <v>754</v>
       </c>
-    </row>
-    <row r="215" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E214" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="215" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A215">
         <v>257</v>
       </c>
@@ -6422,8 +7357,11 @@
       <c r="C215" t="s">
         <v>755</v>
       </c>
-    </row>
-    <row r="216" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E215" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="216" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A216">
         <v>258</v>
       </c>
@@ -6433,8 +7371,11 @@
       <c r="C216" t="s">
         <v>756</v>
       </c>
-    </row>
-    <row r="217" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E216" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="217" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A217">
         <v>259</v>
       </c>
@@ -6444,8 +7385,11 @@
       <c r="C217" t="s">
         <v>757</v>
       </c>
-    </row>
-    <row r="218" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E217" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="218" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A218">
         <v>260</v>
       </c>
@@ -6455,8 +7399,11 @@
       <c r="C218" t="s">
         <v>758</v>
       </c>
-    </row>
-    <row r="219" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E218" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="219" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A219">
         <v>261</v>
       </c>
@@ -6466,8 +7413,11 @@
       <c r="C219" t="s">
         <v>759</v>
       </c>
-    </row>
-    <row r="220" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E219" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="220" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A220">
         <v>262</v>
       </c>
@@ -6477,8 +7427,11 @@
       <c r="C220" t="s">
         <v>760</v>
       </c>
-    </row>
-    <row r="221" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E220" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="221" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A221">
         <v>263</v>
       </c>
@@ -6488,8 +7441,11 @@
       <c r="C221" t="s">
         <v>761</v>
       </c>
-    </row>
-    <row r="222" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E221" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="222" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A222">
         <v>264</v>
       </c>
@@ -6499,8 +7455,11 @@
       <c r="C222" t="s">
         <v>762</v>
       </c>
-    </row>
-    <row r="223" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E222" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="223" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A223">
         <v>265</v>
       </c>
@@ -6510,8 +7469,11 @@
       <c r="C223" t="s">
         <v>763</v>
       </c>
-    </row>
-    <row r="224" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E223" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="224" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A224">
         <v>266</v>
       </c>
@@ -6521,8 +7483,11 @@
       <c r="C224" t="s">
         <v>764</v>
       </c>
-    </row>
-    <row r="225" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E224" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="225" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A225">
         <v>268</v>
       </c>
@@ -6532,8 +7497,11 @@
       <c r="C225" t="s">
         <v>765</v>
       </c>
-    </row>
-    <row r="226" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E225" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="226" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A226">
         <v>269</v>
       </c>
@@ -6543,8 +7511,11 @@
       <c r="C226" t="s">
         <v>766</v>
       </c>
-    </row>
-    <row r="227" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E226" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="227" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A227">
         <v>270</v>
       </c>
@@ -6554,8 +7525,11 @@
       <c r="C227" t="s">
         <v>767</v>
       </c>
-    </row>
-    <row r="228" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E227" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="228" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A228">
         <v>271</v>
       </c>
@@ -6565,8 +7539,11 @@
       <c r="C228" t="s">
         <v>768</v>
       </c>
-    </row>
-    <row r="229" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E228" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="229" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A229">
         <v>272</v>
       </c>
@@ -6576,8 +7553,11 @@
       <c r="C229" t="s">
         <v>769</v>
       </c>
-    </row>
-    <row r="230" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E229" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="230" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A230">
         <v>273</v>
       </c>
@@ -6587,8 +7567,11 @@
       <c r="C230" t="s">
         <v>770</v>
       </c>
-    </row>
-    <row r="231" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E230" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="231" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A231">
         <v>274</v>
       </c>
@@ -6598,8 +7581,11 @@
       <c r="C231" t="s">
         <v>771</v>
       </c>
-    </row>
-    <row r="232" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E231" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="232" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A232">
         <v>276</v>
       </c>
@@ -6609,8 +7595,11 @@
       <c r="C232" t="s">
         <v>772</v>
       </c>
-    </row>
-    <row r="233" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E232" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="233" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A233">
         <v>278</v>
       </c>
@@ -6620,8 +7609,11 @@
       <c r="C233" t="s">
         <v>773</v>
       </c>
-    </row>
-    <row r="234" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E233" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="234" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A234">
         <v>279</v>
       </c>
@@ -6631,8 +7623,11 @@
       <c r="C234" t="s">
         <v>774</v>
       </c>
-    </row>
-    <row r="235" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E234" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="235" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A235">
         <v>280</v>
       </c>
@@ -6642,8 +7637,11 @@
       <c r="C235" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="236" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E235" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="236" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A236">
         <v>281</v>
       </c>
@@ -6653,8 +7651,11 @@
       <c r="C236" t="s">
         <v>776</v>
       </c>
-    </row>
-    <row r="237" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E236" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="237" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A237">
         <v>283</v>
       </c>
@@ -6664,8 +7665,11 @@
       <c r="C237" t="s">
         <v>777</v>
       </c>
-    </row>
-    <row r="238" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E237" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="238" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A238">
         <v>284</v>
       </c>
@@ -6675,8 +7679,11 @@
       <c r="C238" t="s">
         <v>778</v>
       </c>
-    </row>
-    <row r="239" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E238" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="239" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A239">
         <v>286</v>
       </c>
@@ -6686,8 +7693,11 @@
       <c r="C239" t="s">
         <v>779</v>
       </c>
-    </row>
-    <row r="240" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E239" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="240" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A240">
         <v>287</v>
       </c>
@@ -6697,8 +7707,11 @@
       <c r="C240" t="s">
         <v>780</v>
       </c>
-    </row>
-    <row r="241" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E240" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="241" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A241">
         <v>288</v>
       </c>
@@ -6708,8 +7721,11 @@
       <c r="C241" t="s">
         <v>781</v>
       </c>
-    </row>
-    <row r="242" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E241" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="242" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A242">
         <v>294</v>
       </c>
@@ -6719,8 +7735,11 @@
       <c r="C242" t="s">
         <v>782</v>
       </c>
-    </row>
-    <row r="243" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E242" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="243" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A243">
         <v>295</v>
       </c>
@@ -6730,8 +7749,11 @@
       <c r="C243" t="s">
         <v>783</v>
       </c>
-    </row>
-    <row r="244" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E243" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="244" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A244">
         <v>296</v>
       </c>
@@ -6741,8 +7763,11 @@
       <c r="C244" t="s">
         <v>784</v>
       </c>
-    </row>
-    <row r="245" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E244" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="245" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A245">
         <v>297</v>
       </c>
@@ -6752,8 +7777,11 @@
       <c r="C245" t="s">
         <v>785</v>
       </c>
-    </row>
-    <row r="246" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E245" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="246" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A246">
         <v>305</v>
       </c>
@@ -6763,8 +7791,11 @@
       <c r="C246" t="s">
         <v>786</v>
       </c>
-    </row>
-    <row r="247" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E246" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="247" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A247">
         <v>306</v>
       </c>
@@ -6774,8 +7805,11 @@
       <c r="C247" t="s">
         <v>787</v>
       </c>
-    </row>
-    <row r="248" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E247" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="248" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A248">
         <v>307</v>
       </c>
@@ -6785,8 +7819,11 @@
       <c r="C248" t="s">
         <v>788</v>
       </c>
-    </row>
-    <row r="249" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E248" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="249" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A249">
         <v>311</v>
       </c>
@@ -6796,8 +7833,11 @@
       <c r="C249" t="s">
         <v>789</v>
       </c>
-    </row>
-    <row r="250" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E249" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="250" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A250">
         <v>315</v>
       </c>
@@ -6807,8 +7847,11 @@
       <c r="C250" t="s">
         <v>790</v>
       </c>
-    </row>
-    <row r="251" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E250" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="251" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A251">
         <v>322</v>
       </c>
@@ -6818,8 +7861,11 @@
       <c r="C251" t="s">
         <v>791</v>
       </c>
-    </row>
-    <row r="252" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E251" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="252" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A252">
         <v>326</v>
       </c>
@@ -6829,8 +7875,11 @@
       <c r="C252" t="s">
         <v>792</v>
       </c>
-    </row>
-    <row r="253" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E252" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="253" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A253">
         <v>327</v>
       </c>
@@ -6840,8 +7889,11 @@
       <c r="C253" t="s">
         <v>793</v>
       </c>
-    </row>
-    <row r="254" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E253" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="254" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A254">
         <v>328</v>
       </c>
@@ -6851,8 +7903,11 @@
       <c r="C254" t="s">
         <v>794</v>
       </c>
-    </row>
-    <row r="255" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E254" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="255" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A255">
         <v>330</v>
       </c>
@@ -6862,8 +7917,11 @@
       <c r="C255" t="s">
         <v>795</v>
       </c>
-    </row>
-    <row r="256" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E255" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="256" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A256">
         <v>331</v>
       </c>
@@ -6873,8 +7931,11 @@
       <c r="C256" t="s">
         <v>796</v>
       </c>
-    </row>
-    <row r="257" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E256" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="257" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A257">
         <v>332</v>
       </c>
@@ -6884,8 +7945,11 @@
       <c r="C257" t="s">
         <v>797</v>
       </c>
-    </row>
-    <row r="258" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E257" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="258" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A258">
         <v>333</v>
       </c>
@@ -6895,8 +7959,11 @@
       <c r="C258" t="s">
         <v>798</v>
       </c>
-    </row>
-    <row r="259" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E258" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="259" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A259">
         <v>335</v>
       </c>
@@ -6906,8 +7973,11 @@
       <c r="C259" t="s">
         <v>799</v>
       </c>
-    </row>
-    <row r="260" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E259" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="260" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A260">
         <v>336</v>
       </c>
@@ -6917,8 +7987,11 @@
       <c r="C260" t="s">
         <v>800</v>
       </c>
-    </row>
-    <row r="261" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E260" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="261" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A261">
         <v>337</v>
       </c>
@@ -6928,8 +8001,11 @@
       <c r="C261" t="s">
         <v>801</v>
       </c>
-    </row>
-    <row r="262" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E261" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="262" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A262">
         <v>338</v>
       </c>
@@ -6939,8 +8015,11 @@
       <c r="C262" t="s">
         <v>802</v>
       </c>
-    </row>
-    <row r="263" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E262" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="263" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A263">
         <v>339</v>
       </c>
@@ -6950,8 +8029,11 @@
       <c r="C263" t="s">
         <v>803</v>
       </c>
-    </row>
-    <row r="264" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E263" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="264" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A264">
         <v>340</v>
       </c>
@@ -6961,8 +8043,11 @@
       <c r="C264" t="s">
         <v>804</v>
       </c>
-    </row>
-    <row r="265" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E264" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="265" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A265">
         <v>342</v>
       </c>
@@ -6972,8 +8057,11 @@
       <c r="C265" t="s">
         <v>805</v>
       </c>
-    </row>
-    <row r="266" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E265" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="266" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A266">
         <v>343</v>
       </c>
@@ -6983,8 +8071,11 @@
       <c r="C266" t="s">
         <v>806</v>
       </c>
-    </row>
-    <row r="267" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E266" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="267" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A267">
         <v>344</v>
       </c>
@@ -6994,8 +8085,11 @@
       <c r="C267" t="s">
         <v>807</v>
       </c>
-    </row>
-    <row r="268" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E267" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="268" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A268">
         <v>345</v>
       </c>
@@ -7005,8 +8099,11 @@
       <c r="C268" t="s">
         <v>808</v>
       </c>
-    </row>
-    <row r="269" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E268" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="269" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A269">
         <v>346</v>
       </c>
@@ -7016,8 +8113,11 @@
       <c r="C269" t="s">
         <v>809</v>
       </c>
-    </row>
-    <row r="270" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E269" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="270" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A270">
         <v>347</v>
       </c>
@@ -7027,8 +8127,11 @@
       <c r="C270" t="s">
         <v>810</v>
       </c>
-    </row>
-    <row r="271" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E270" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="271" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A271">
         <v>348</v>
       </c>
@@ -7038,8 +8141,11 @@
       <c r="C271" t="s">
         <v>811</v>
       </c>
-    </row>
-    <row r="272" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E271" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="272" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A272">
         <v>349</v>
       </c>
@@ -7049,8 +8155,11 @@
       <c r="C272" t="s">
         <v>812</v>
       </c>
-    </row>
-    <row r="273" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E272" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="273" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A273">
         <v>350</v>
       </c>
@@ -7060,8 +8169,11 @@
       <c r="C273" t="s">
         <v>813</v>
       </c>
-    </row>
-    <row r="274" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E273" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="274" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A274">
         <v>351</v>
       </c>
@@ -7071,8 +8183,11 @@
       <c r="C274" t="s">
         <v>814</v>
       </c>
-    </row>
-    <row r="275" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E274" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="275" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A275">
         <v>352</v>
       </c>
@@ -7082,8 +8197,11 @@
       <c r="C275" t="s">
         <v>815</v>
       </c>
-    </row>
-    <row r="276" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E275" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="276" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A276">
         <v>353</v>
       </c>
@@ -7093,8 +8211,11 @@
       <c r="C276" t="s">
         <v>816</v>
       </c>
-    </row>
-    <row r="277" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E276" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="277" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A277">
         <v>354</v>
       </c>
@@ -7104,8 +8225,11 @@
       <c r="C277" t="s">
         <v>817</v>
       </c>
-    </row>
-    <row r="278" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E277" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="278" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A278">
         <v>355</v>
       </c>
@@ -7115,8 +8239,11 @@
       <c r="C278" t="s">
         <v>818</v>
       </c>
-    </row>
-    <row r="279" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E278" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="279" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A279">
         <v>356</v>
       </c>
@@ -7126,8 +8253,11 @@
       <c r="C279" t="s">
         <v>819</v>
       </c>
-    </row>
-    <row r="280" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E279" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="280" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A280">
         <v>357</v>
       </c>
@@ -7137,8 +8267,11 @@
       <c r="C280" t="s">
         <v>820</v>
       </c>
-    </row>
-    <row r="281" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E280" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="281" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A281">
         <v>358</v>
       </c>
@@ -7148,8 +8281,11 @@
       <c r="C281" t="s">
         <v>821</v>
       </c>
-    </row>
-    <row r="282" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E281" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="282" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A282">
         <v>359</v>
       </c>
@@ -7159,8 +8295,11 @@
       <c r="C282" t="s">
         <v>822</v>
       </c>
-    </row>
-    <row r="283" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E282" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="283" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A283">
         <v>360</v>
       </c>
@@ -7170,8 +8309,11 @@
       <c r="C283" t="s">
         <v>823</v>
       </c>
-    </row>
-    <row r="284" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E283" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="284" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A284">
         <v>361</v>
       </c>
@@ -7181,8 +8323,11 @@
       <c r="C284" t="s">
         <v>824</v>
       </c>
-    </row>
-    <row r="285" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E284" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="285" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A285">
         <v>362</v>
       </c>
@@ -7192,8 +8337,11 @@
       <c r="C285" t="s">
         <v>825</v>
       </c>
-    </row>
-    <row r="286" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E285" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="286" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A286">
         <v>363</v>
       </c>
@@ -7203,8 +8351,11 @@
       <c r="C286" t="s">
         <v>826</v>
       </c>
-    </row>
-    <row r="287" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E286" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="287" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A287">
         <v>364</v>
       </c>
@@ -7214,8 +8365,11 @@
       <c r="C287" t="s">
         <v>827</v>
       </c>
-    </row>
-    <row r="288" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E287" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="288" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A288">
         <v>365</v>
       </c>
@@ -7225,8 +8379,11 @@
       <c r="C288" t="s">
         <v>828</v>
       </c>
-    </row>
-    <row r="289" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E288" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="289" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A289">
         <v>366</v>
       </c>
@@ -7236,8 +8393,11 @@
       <c r="C289" t="s">
         <v>829</v>
       </c>
-    </row>
-    <row r="290" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E289" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="290" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A290">
         <v>367</v>
       </c>
@@ -7247,8 +8407,11 @@
       <c r="C290" t="s">
         <v>830</v>
       </c>
-    </row>
-    <row r="291" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E290" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="291" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A291">
         <v>368</v>
       </c>
@@ -7258,8 +8421,11 @@
       <c r="C291" t="s">
         <v>831</v>
       </c>
-    </row>
-    <row r="292" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E291" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="292" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A292">
         <v>369</v>
       </c>
@@ -7269,8 +8435,11 @@
       <c r="C292" t="s">
         <v>832</v>
       </c>
-    </row>
-    <row r="293" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E292" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="293" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A293">
         <v>370</v>
       </c>
@@ -7280,8 +8449,11 @@
       <c r="C293" t="s">
         <v>833</v>
       </c>
-    </row>
-    <row r="294" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E293" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="294" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A294">
         <v>371</v>
       </c>
@@ -7291,8 +8463,11 @@
       <c r="C294" t="s">
         <v>834</v>
       </c>
-    </row>
-    <row r="295" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E294" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="295" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A295">
         <v>372</v>
       </c>
@@ -7302,8 +8477,11 @@
       <c r="C295" t="s">
         <v>835</v>
       </c>
-    </row>
-    <row r="296" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E295" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="296" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A296">
         <v>373</v>
       </c>
@@ -7313,8 +8491,11 @@
       <c r="C296" t="s">
         <v>836</v>
       </c>
-    </row>
-    <row r="297" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E296" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="297" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A297">
         <v>374</v>
       </c>
@@ -7324,8 +8505,11 @@
       <c r="C297" t="s">
         <v>837</v>
       </c>
-    </row>
-    <row r="298" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E297" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="298" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A298">
         <v>375</v>
       </c>
@@ -7335,8 +8519,11 @@
       <c r="C298" t="s">
         <v>838</v>
       </c>
-    </row>
-    <row r="299" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E298" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="299" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A299">
         <v>376</v>
       </c>
@@ -7346,8 +8533,11 @@
       <c r="C299" t="s">
         <v>839</v>
       </c>
-    </row>
-    <row r="300" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E299" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="300" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A300">
         <v>377</v>
       </c>
@@ -7357,8 +8547,11 @@
       <c r="C300" t="s">
         <v>840</v>
       </c>
-    </row>
-    <row r="301" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E300" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="301" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A301">
         <v>378</v>
       </c>
@@ -7368,8 +8561,11 @@
       <c r="C301" t="s">
         <v>841</v>
       </c>
-    </row>
-    <row r="302" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E301" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="302" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A302">
         <v>379</v>
       </c>
@@ -7379,8 +8575,11 @@
       <c r="C302" t="s">
         <v>842</v>
       </c>
-    </row>
-    <row r="303" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E302" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="303" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A303">
         <v>380</v>
       </c>
@@ -7390,8 +8589,11 @@
       <c r="C303" t="s">
         <v>843</v>
       </c>
-    </row>
-    <row r="304" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E303" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="304" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A304">
         <v>381</v>
       </c>
@@ -7401,8 +8603,11 @@
       <c r="C304" t="s">
         <v>844</v>
       </c>
-    </row>
-    <row r="305" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E304" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="305" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A305">
         <v>382</v>
       </c>
@@ -7412,8 +8617,11 @@
       <c r="C305" t="s">
         <v>845</v>
       </c>
-    </row>
-    <row r="306" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E305" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="306" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A306">
         <v>383</v>
       </c>
@@ -7423,8 +8631,11 @@
       <c r="C306" t="s">
         <v>846</v>
       </c>
-    </row>
-    <row r="307" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E306" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="307" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A307">
         <v>384</v>
       </c>
@@ -7434,8 +8645,11 @@
       <c r="C307" t="s">
         <v>847</v>
       </c>
-    </row>
-    <row r="308" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E307" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="308" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A308">
         <v>385</v>
       </c>
@@ -7445,8 +8659,11 @@
       <c r="C308" t="s">
         <v>848</v>
       </c>
-    </row>
-    <row r="309" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E308" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="309" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A309">
         <v>386</v>
       </c>
@@ -7456,8 +8673,11 @@
       <c r="C309" t="s">
         <v>849</v>
       </c>
-    </row>
-    <row r="310" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E309" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="310" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A310">
         <v>387</v>
       </c>
@@ -7467,8 +8687,11 @@
       <c r="C310" t="s">
         <v>850</v>
       </c>
-    </row>
-    <row r="311" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E310" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="311" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A311">
         <v>388</v>
       </c>
@@ -7478,8 +8701,11 @@
       <c r="C311" t="s">
         <v>851</v>
       </c>
-    </row>
-    <row r="312" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E311" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="312" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A312">
         <v>389</v>
       </c>
@@ -7489,8 +8715,11 @@
       <c r="C312" t="s">
         <v>852</v>
       </c>
-    </row>
-    <row r="313" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E312" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="313" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A313">
         <v>390</v>
       </c>
@@ -7500,8 +8729,11 @@
       <c r="C313" t="s">
         <v>853</v>
       </c>
-    </row>
-    <row r="314" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E313" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="314" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A314">
         <v>391</v>
       </c>
@@ -7511,8 +8743,11 @@
       <c r="C314" t="s">
         <v>854</v>
       </c>
-    </row>
-    <row r="315" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E314" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="315" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A315">
         <v>392</v>
       </c>
@@ -7522,8 +8757,11 @@
       <c r="C315" t="s">
         <v>855</v>
       </c>
-    </row>
-    <row r="316" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E315" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="316" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A316">
         <v>393</v>
       </c>
@@ -7533,8 +8771,11 @@
       <c r="C316" t="s">
         <v>856</v>
       </c>
-    </row>
-    <row r="317" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E316" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="317" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A317">
         <v>394</v>
       </c>
@@ -7544,8 +8785,11 @@
       <c r="C317" t="s">
         <v>857</v>
       </c>
-    </row>
-    <row r="318" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E317" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="318" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A318">
         <v>395</v>
       </c>
@@ -7555,8 +8799,11 @@
       <c r="C318" t="s">
         <v>858</v>
       </c>
-    </row>
-    <row r="319" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E318" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="319" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A319">
         <v>396</v>
       </c>
@@ -7566,8 +8813,11 @@
       <c r="C319" t="s">
         <v>859</v>
       </c>
-    </row>
-    <row r="320" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E319" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="320" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A320">
         <v>397</v>
       </c>
@@ -7577,8 +8827,11 @@
       <c r="C320" t="s">
         <v>860</v>
       </c>
-    </row>
-    <row r="321" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E320" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="321" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A321">
         <v>398</v>
       </c>
@@ -7588,8 +8841,11 @@
       <c r="C321" t="s">
         <v>861</v>
       </c>
-    </row>
-    <row r="322" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E321" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="322" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A322">
         <v>399</v>
       </c>
@@ -7599,8 +8855,11 @@
       <c r="C322" t="s">
         <v>862</v>
       </c>
-    </row>
-    <row r="323" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E322" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="323" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A323">
         <v>400</v>
       </c>
@@ -7610,8 +8869,11 @@
       <c r="C323" t="s">
         <v>863</v>
       </c>
-    </row>
-    <row r="324" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E323" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="324" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A324">
         <v>401</v>
       </c>
@@ -7621,8 +8883,11 @@
       <c r="C324" t="s">
         <v>864</v>
       </c>
-    </row>
-    <row r="325" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E324" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="325" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A325">
         <v>426</v>
       </c>
@@ -7632,8 +8897,11 @@
       <c r="C325" t="s">
         <v>865</v>
       </c>
-    </row>
-    <row r="326" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E325" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="326" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A326">
         <v>427</v>
       </c>
@@ -7643,8 +8911,11 @@
       <c r="C326" t="s">
         <v>866</v>
       </c>
-    </row>
-    <row r="327" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E326" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="327" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A327">
         <v>428</v>
       </c>
@@ -7654,8 +8925,11 @@
       <c r="C327" t="s">
         <v>867</v>
       </c>
-    </row>
-    <row r="328" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E327" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="328" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A328">
         <v>430</v>
       </c>
@@ -7665,8 +8939,11 @@
       <c r="C328" t="s">
         <v>868</v>
       </c>
-    </row>
-    <row r="329" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E328" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="329" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A329">
         <v>431</v>
       </c>
@@ -7676,8 +8953,11 @@
       <c r="C329" t="s">
         <v>869</v>
       </c>
-    </row>
-    <row r="330" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E329" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="330" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A330">
         <v>432</v>
       </c>
@@ -7687,8 +8967,11 @@
       <c r="C330" t="s">
         <v>870</v>
       </c>
-    </row>
-    <row r="331" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E330" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="331" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A331">
         <v>433</v>
       </c>
@@ -7698,8 +8981,11 @@
       <c r="C331" t="s">
         <v>871</v>
       </c>
-    </row>
-    <row r="332" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E331" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="332" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A332">
         <v>434</v>
       </c>
@@ -7709,8 +8995,11 @@
       <c r="C332" t="s">
         <v>872</v>
       </c>
-    </row>
-    <row r="333" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E332" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="333" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A333">
         <v>435</v>
       </c>
@@ -7720,8 +9009,11 @@
       <c r="C333" t="s">
         <v>873</v>
       </c>
-    </row>
-    <row r="334" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E333" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="334" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A334">
         <v>436</v>
       </c>
@@ -7731,8 +9023,11 @@
       <c r="C334" t="s">
         <v>874</v>
       </c>
-    </row>
-    <row r="335" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E334" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="335" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A335">
         <v>437</v>
       </c>
@@ -7742,8 +9037,11 @@
       <c r="C335" t="s">
         <v>875</v>
       </c>
-    </row>
-    <row r="336" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E335" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="336" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A336">
         <v>438</v>
       </c>
@@ -7753,8 +9051,11 @@
       <c r="C336" t="s">
         <v>876</v>
       </c>
-    </row>
-    <row r="337" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E336" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="337" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A337">
         <v>439</v>
       </c>
@@ -7764,8 +9065,11 @@
       <c r="C337" t="s">
         <v>877</v>
       </c>
-    </row>
-    <row r="338" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E337" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="338" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A338">
         <v>440</v>
       </c>
@@ -7775,8 +9079,11 @@
       <c r="C338" t="s">
         <v>878</v>
       </c>
-    </row>
-    <row r="339" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E338" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="339" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A339">
         <v>441</v>
       </c>
@@ -7786,8 +9093,11 @@
       <c r="C339" t="s">
         <v>879</v>
       </c>
-    </row>
-    <row r="340" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E339" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="340" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A340">
         <v>442</v>
       </c>
@@ -7797,8 +9107,11 @@
       <c r="C340" t="s">
         <v>880</v>
       </c>
-    </row>
-    <row r="341" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E340" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="341" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A341">
         <v>443</v>
       </c>
@@ -7808,8 +9121,11 @@
       <c r="C341" t="s">
         <v>881</v>
       </c>
-    </row>
-    <row r="342" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E341" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="342" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A342">
         <v>444</v>
       </c>
@@ -7819,8 +9135,11 @@
       <c r="C342" t="s">
         <v>882</v>
       </c>
-    </row>
-    <row r="343" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E342" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="343" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A343">
         <v>445</v>
       </c>
@@ -7830,8 +9149,11 @@
       <c r="C343" t="s">
         <v>883</v>
       </c>
-    </row>
-    <row r="344" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E343" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="344" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A344">
         <v>446</v>
       </c>
@@ -7841,8 +9163,11 @@
       <c r="C344" t="s">
         <v>884</v>
       </c>
-    </row>
-    <row r="345" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E344" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="345" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A345">
         <v>447</v>
       </c>
@@ -7852,8 +9177,11 @@
       <c r="C345" t="s">
         <v>885</v>
       </c>
-    </row>
-    <row r="346" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E345" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="346" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A346">
         <v>449</v>
       </c>
@@ -7863,8 +9191,11 @@
       <c r="C346" t="s">
         <v>886</v>
       </c>
-    </row>
-    <row r="347" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E346" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="347" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A347">
         <v>450</v>
       </c>
@@ -7874,8 +9205,11 @@
       <c r="C347" t="s">
         <v>887</v>
       </c>
-    </row>
-    <row r="348" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E347" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="348" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A348">
         <v>451</v>
       </c>
@@ -7885,8 +9219,11 @@
       <c r="C348" t="s">
         <v>888</v>
       </c>
-    </row>
-    <row r="349" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E348" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="349" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A349">
         <v>452</v>
       </c>
@@ -7896,8 +9233,11 @@
       <c r="C349" t="s">
         <v>889</v>
       </c>
-    </row>
-    <row r="350" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E349" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="350" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A350">
         <v>453</v>
       </c>
@@ -7907,8 +9247,11 @@
       <c r="C350" t="s">
         <v>890</v>
       </c>
-    </row>
-    <row r="351" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E350" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="351" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A351">
         <v>454</v>
       </c>
@@ -7918,8 +9261,11 @@
       <c r="C351" t="s">
         <v>891</v>
       </c>
-    </row>
-    <row r="352" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E351" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="352" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A352">
         <v>456</v>
       </c>
@@ -7929,8 +9275,11 @@
       <c r="C352" t="s">
         <v>892</v>
       </c>
-    </row>
-    <row r="353" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E352" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="353" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A353">
         <v>457</v>
       </c>
@@ -7940,8 +9289,11 @@
       <c r="C353" t="s">
         <v>893</v>
       </c>
-    </row>
-    <row r="354" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E353" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="354" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A354">
         <v>458</v>
       </c>
@@ -7951,8 +9303,11 @@
       <c r="C354" t="s">
         <v>894</v>
       </c>
-    </row>
-    <row r="355" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E354" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="355" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A355">
         <v>459</v>
       </c>
@@ -7962,8 +9317,11 @@
       <c r="C355" t="s">
         <v>895</v>
       </c>
-    </row>
-    <row r="356" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E355" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="356" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A356">
         <v>460</v>
       </c>
@@ -7973,8 +9331,11 @@
       <c r="C356" t="s">
         <v>896</v>
       </c>
-    </row>
-    <row r="357" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E356" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="357" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A357">
         <v>461</v>
       </c>
@@ -7984,8 +9345,11 @@
       <c r="C357" t="s">
         <v>897</v>
       </c>
-    </row>
-    <row r="358" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E357" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="358" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A358">
         <v>462</v>
       </c>
@@ -7995,8 +9359,11 @@
       <c r="C358" t="s">
         <v>898</v>
       </c>
-    </row>
-    <row r="359" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E358" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="359" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A359">
         <v>463</v>
       </c>
@@ -8006,8 +9373,11 @@
       <c r="C359" t="s">
         <v>899</v>
       </c>
-    </row>
-    <row r="360" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E359" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="360" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A360">
         <v>464</v>
       </c>
@@ -8017,8 +9387,11 @@
       <c r="C360" t="s">
         <v>900</v>
       </c>
-    </row>
-    <row r="361" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E360" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="361" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A361">
         <v>465</v>
       </c>
@@ -8028,8 +9401,11 @@
       <c r="C361" t="s">
         <v>901</v>
       </c>
-    </row>
-    <row r="362" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E361" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="362" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A362">
         <v>466</v>
       </c>
@@ -8039,8 +9415,11 @@
       <c r="C362" t="s">
         <v>902</v>
       </c>
-    </row>
-    <row r="363" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E362" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="363" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A363">
         <v>469</v>
       </c>
@@ -8050,8 +9429,11 @@
       <c r="C363" t="s">
         <v>903</v>
       </c>
-    </row>
-    <row r="364" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E363" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="364" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A364">
         <v>470</v>
       </c>
@@ -8061,8 +9443,11 @@
       <c r="C364" t="s">
         <v>904</v>
       </c>
-    </row>
-    <row r="365" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E364" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="365" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A365">
         <v>471</v>
       </c>
@@ -8072,8 +9457,11 @@
       <c r="C365" t="s">
         <v>905</v>
       </c>
-    </row>
-    <row r="366" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E365" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="366" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A366">
         <v>472</v>
       </c>
@@ -8083,8 +9471,11 @@
       <c r="C366" t="s">
         <v>906</v>
       </c>
-    </row>
-    <row r="367" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E366" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="367" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A367">
         <v>473</v>
       </c>
@@ -8094,8 +9485,11 @@
       <c r="C367" t="s">
         <v>907</v>
       </c>
-    </row>
-    <row r="368" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E367" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="368" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A368">
         <v>474</v>
       </c>
@@ -8105,8 +9499,11 @@
       <c r="C368" t="s">
         <v>908</v>
       </c>
-    </row>
-    <row r="369" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E368" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="369" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A369">
         <v>475</v>
       </c>
@@ -8116,8 +9513,11 @@
       <c r="C369" t="s">
         <v>909</v>
       </c>
-    </row>
-    <row r="370" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E369" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="370" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A370">
         <v>476</v>
       </c>
@@ -8127,8 +9527,11 @@
       <c r="C370" t="s">
         <v>910</v>
       </c>
-    </row>
-    <row r="371" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E370" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="371" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A371">
         <v>477</v>
       </c>
@@ -8138,8 +9541,11 @@
       <c r="C371" t="s">
         <v>911</v>
       </c>
-    </row>
-    <row r="372" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E371" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="372" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A372">
         <v>478</v>
       </c>
@@ -8149,8 +9555,11 @@
       <c r="C372" t="s">
         <v>912</v>
       </c>
-    </row>
-    <row r="373" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E372" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="373" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A373">
         <v>481</v>
       </c>
@@ -8160,8 +9569,11 @@
       <c r="C373" t="s">
         <v>913</v>
       </c>
-    </row>
-    <row r="374" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E373" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="374" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A374">
         <v>482</v>
       </c>
@@ -8171,8 +9583,11 @@
       <c r="C374" t="s">
         <v>914</v>
       </c>
-    </row>
-    <row r="375" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E374" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="375" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A375">
         <v>483</v>
       </c>
@@ -8182,8 +9597,11 @@
       <c r="C375" t="s">
         <v>915</v>
       </c>
-    </row>
-    <row r="376" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E375" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="376" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A376">
         <v>484</v>
       </c>
@@ -8193,8 +9611,11 @@
       <c r="C376" t="s">
         <v>916</v>
       </c>
-    </row>
-    <row r="377" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E376" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="377" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A377">
         <v>485</v>
       </c>
@@ -8204,8 +9625,11 @@
       <c r="C377" t="s">
         <v>917</v>
       </c>
-    </row>
-    <row r="378" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E377" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="378" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A378">
         <v>487</v>
       </c>
@@ -8215,8 +9639,11 @@
       <c r="C378" t="s">
         <v>918</v>
       </c>
-    </row>
-    <row r="379" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E378" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="379" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A379">
         <v>488</v>
       </c>
@@ -8226,8 +9653,11 @@
       <c r="C379" t="s">
         <v>919</v>
       </c>
-    </row>
-    <row r="380" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E379" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="380" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A380">
         <v>489</v>
       </c>
@@ -8237,8 +9667,11 @@
       <c r="C380" t="s">
         <v>920</v>
       </c>
-    </row>
-    <row r="381" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E380" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="381" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A381">
         <v>490</v>
       </c>
@@ -8248,8 +9681,11 @@
       <c r="C381" t="s">
         <v>921</v>
       </c>
-    </row>
-    <row r="382" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E381" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="382" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A382">
         <v>491</v>
       </c>
@@ -8259,8 +9695,11 @@
       <c r="C382" t="s">
         <v>922</v>
       </c>
-    </row>
-    <row r="383" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E382" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="383" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A383">
         <v>492</v>
       </c>
@@ -8270,8 +9709,11 @@
       <c r="C383" t="s">
         <v>923</v>
       </c>
-    </row>
-    <row r="384" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E383" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="384" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A384">
         <v>493</v>
       </c>
@@ -8281,8 +9723,11 @@
       <c r="C384" t="s">
         <v>924</v>
       </c>
-    </row>
-    <row r="385" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E384" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="385" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A385">
         <v>494</v>
       </c>
@@ -8292,8 +9737,11 @@
       <c r="C385" t="s">
         <v>925</v>
       </c>
-    </row>
-    <row r="386" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E385" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="386" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A386">
         <v>495</v>
       </c>
@@ -8303,8 +9751,11 @@
       <c r="C386" t="s">
         <v>926</v>
       </c>
-    </row>
-    <row r="387" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E386" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="387" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A387">
         <v>496</v>
       </c>
@@ -8314,8 +9765,11 @@
       <c r="C387" t="s">
         <v>927</v>
       </c>
-    </row>
-    <row r="388" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E387" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="388" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A388">
         <v>498</v>
       </c>
@@ -8325,8 +9779,11 @@
       <c r="C388" t="s">
         <v>928</v>
       </c>
-    </row>
-    <row r="389" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E388" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="389" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A389">
         <v>499</v>
       </c>
@@ -8336,8 +9793,11 @@
       <c r="C389" t="s">
         <v>929</v>
       </c>
-    </row>
-    <row r="390" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E389" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="390" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A390">
         <v>500</v>
       </c>
@@ -8347,8 +9807,11 @@
       <c r="C390" t="s">
         <v>930</v>
       </c>
-    </row>
-    <row r="391" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E390" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="391" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A391">
         <v>501</v>
       </c>
@@ -8358,8 +9821,11 @@
       <c r="C391" t="s">
         <v>931</v>
       </c>
-    </row>
-    <row r="392" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E391" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="392" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A392">
         <v>502</v>
       </c>
@@ -8369,8 +9835,11 @@
       <c r="C392" t="s">
         <v>932</v>
       </c>
-    </row>
-    <row r="393" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E392" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="393" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A393">
         <v>503</v>
       </c>
@@ -8380,8 +9849,11 @@
       <c r="C393" t="s">
         <v>933</v>
       </c>
-    </row>
-    <row r="394" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E393" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="394" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A394">
         <v>504</v>
       </c>
@@ -8391,8 +9863,11 @@
       <c r="C394" t="s">
         <v>934</v>
       </c>
-    </row>
-    <row r="395" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E394" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="395" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A395">
         <v>505</v>
       </c>
@@ -8402,8 +9877,11 @@
       <c r="C395" t="s">
         <v>935</v>
       </c>
-    </row>
-    <row r="396" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E395" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="396" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A396">
         <v>506</v>
       </c>
@@ -8413,8 +9891,11 @@
       <c r="C396" t="s">
         <v>936</v>
       </c>
-    </row>
-    <row r="397" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E396" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="397" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A397">
         <v>507</v>
       </c>
@@ -8424,8 +9905,11 @@
       <c r="C397" t="s">
         <v>937</v>
       </c>
-    </row>
-    <row r="398" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E397" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="398" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A398">
         <v>508</v>
       </c>
@@ -8435,8 +9919,11 @@
       <c r="C398" t="s">
         <v>938</v>
       </c>
-    </row>
-    <row r="399" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E398" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="399" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A399">
         <v>509</v>
       </c>
@@ -8446,8 +9933,11 @@
       <c r="C399" t="s">
         <v>939</v>
       </c>
-    </row>
-    <row r="400" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E399" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="400" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A400">
         <v>510</v>
       </c>
@@ -8457,8 +9947,11 @@
       <c r="C400" t="s">
         <v>940</v>
       </c>
-    </row>
-    <row r="401" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E400" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="401" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A401">
         <v>511</v>
       </c>
@@ -8468,8 +9961,11 @@
       <c r="C401" t="s">
         <v>941</v>
       </c>
-    </row>
-    <row r="402" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E401" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="402" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A402">
         <v>512</v>
       </c>
@@ -8479,8 +9975,11 @@
       <c r="C402" t="s">
         <v>942</v>
       </c>
-    </row>
-    <row r="403" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E402" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="403" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A403">
         <v>513</v>
       </c>
@@ -8490,8 +9989,11 @@
       <c r="C403" t="s">
         <v>943</v>
       </c>
-    </row>
-    <row r="404" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E403" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="404" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A404">
         <v>514</v>
       </c>
@@ -8501,8 +10003,11 @@
       <c r="C404" t="s">
         <v>944</v>
       </c>
-    </row>
-    <row r="405" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E404" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="405" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A405">
         <v>515</v>
       </c>
@@ -8512,8 +10017,11 @@
       <c r="C405" t="s">
         <v>945</v>
       </c>
-    </row>
-    <row r="406" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E405" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="406" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A406">
         <v>516</v>
       </c>
@@ -8523,8 +10031,11 @@
       <c r="C406" t="s">
         <v>946</v>
       </c>
-    </row>
-    <row r="407" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E406" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="407" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A407">
         <v>517</v>
       </c>
@@ -8534,8 +10045,11 @@
       <c r="C407" t="s">
         <v>947</v>
       </c>
-    </row>
-    <row r="408" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E407" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="408" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A408">
         <v>518</v>
       </c>
@@ -8545,8 +10059,11 @@
       <c r="C408" t="s">
         <v>948</v>
       </c>
-    </row>
-    <row r="409" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E408" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="409" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A409">
         <v>519</v>
       </c>
@@ -8556,8 +10073,11 @@
       <c r="C409" t="s">
         <v>949</v>
       </c>
-    </row>
-    <row r="410" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E409" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="410" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A410">
         <v>520</v>
       </c>
@@ -8567,8 +10087,11 @@
       <c r="C410" t="s">
         <v>950</v>
       </c>
-    </row>
-    <row r="411" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E410" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="411" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A411">
         <v>521</v>
       </c>
@@ -8578,8 +10101,11 @@
       <c r="C411" t="s">
         <v>951</v>
       </c>
-    </row>
-    <row r="412" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E411" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="412" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A412">
         <v>522</v>
       </c>
@@ -8589,8 +10115,11 @@
       <c r="C412" t="s">
         <v>952</v>
       </c>
-    </row>
-    <row r="413" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E412" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="413" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A413">
         <v>523</v>
       </c>
@@ -8600,8 +10129,11 @@
       <c r="C413" t="s">
         <v>953</v>
       </c>
-    </row>
-    <row r="414" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E413" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="414" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A414">
         <v>524</v>
       </c>
@@ -8611,8 +10143,11 @@
       <c r="C414" t="s">
         <v>954</v>
       </c>
-    </row>
-    <row r="415" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E414" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="415" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A415">
         <v>525</v>
       </c>
@@ -8622,8 +10157,11 @@
       <c r="C415" t="s">
         <v>955</v>
       </c>
-    </row>
-    <row r="416" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E415" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="416" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A416">
         <v>526</v>
       </c>
@@ -8633,8 +10171,11 @@
       <c r="C416" t="s">
         <v>956</v>
       </c>
-    </row>
-    <row r="417" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E416" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="417" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A417">
         <v>527</v>
       </c>
@@ -8644,8 +10185,11 @@
       <c r="C417" t="s">
         <v>957</v>
       </c>
-    </row>
-    <row r="418" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E417" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="418" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A418">
         <v>528</v>
       </c>
@@ -8655,8 +10199,11 @@
       <c r="C418" t="s">
         <v>958</v>
       </c>
-    </row>
-    <row r="419" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E418" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="419" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A419">
         <v>529</v>
       </c>
@@ -8666,8 +10213,11 @@
       <c r="C419" t="s">
         <v>959</v>
       </c>
-    </row>
-    <row r="420" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E419" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="420" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A420">
         <v>530</v>
       </c>
@@ -8677,8 +10227,11 @@
       <c r="C420" t="s">
         <v>960</v>
       </c>
-    </row>
-    <row r="421" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E420" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="421" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A421">
         <v>531</v>
       </c>
@@ -8688,8 +10241,11 @@
       <c r="C421" t="s">
         <v>961</v>
       </c>
-    </row>
-    <row r="422" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E421" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="422" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A422">
         <v>532</v>
       </c>
@@ -8699,8 +10255,11 @@
       <c r="C422" t="s">
         <v>962</v>
       </c>
-    </row>
-    <row r="423" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E422" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="423" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A423">
         <v>533</v>
       </c>
@@ -8710,8 +10269,11 @@
       <c r="C423" t="s">
         <v>963</v>
       </c>
-    </row>
-    <row r="424" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E423" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="424" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A424">
         <v>534</v>
       </c>
@@ -8721,8 +10283,11 @@
       <c r="C424" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="425" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E424" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="425" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A425">
         <v>535</v>
       </c>
@@ -8732,8 +10297,11 @@
       <c r="C425" t="s">
         <v>965</v>
       </c>
-    </row>
-    <row r="426" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E425" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="426" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A426">
         <v>536</v>
       </c>
@@ -8743,8 +10311,11 @@
       <c r="C426" t="s">
         <v>966</v>
       </c>
-    </row>
-    <row r="427" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E426" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="427" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A427">
         <v>537</v>
       </c>
@@ -8754,8 +10325,11 @@
       <c r="C427" t="s">
         <v>967</v>
       </c>
-    </row>
-    <row r="428" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E427" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="428" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A428">
         <v>538</v>
       </c>
@@ -8765,8 +10339,11 @@
       <c r="C428" t="s">
         <v>968</v>
       </c>
-    </row>
-    <row r="429" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E428" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="429" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A429">
         <v>539</v>
       </c>
@@ -8776,8 +10353,11 @@
       <c r="C429" t="s">
         <v>969</v>
       </c>
-    </row>
-    <row r="430" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E429" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="430" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A430">
         <v>540</v>
       </c>
@@ -8787,8 +10367,11 @@
       <c r="C430" t="s">
         <v>970</v>
       </c>
-    </row>
-    <row r="431" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E430" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="431" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A431">
         <v>541</v>
       </c>
@@ -8798,8 +10381,11 @@
       <c r="C431" t="s">
         <v>971</v>
       </c>
-    </row>
-    <row r="432" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E431" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="432" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A432">
         <v>542</v>
       </c>
@@ -8809,8 +10395,11 @@
       <c r="C432" t="s">
         <v>972</v>
       </c>
-    </row>
-    <row r="433" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E432" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="433" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A433">
         <v>543</v>
       </c>
@@ -8820,8 +10409,11 @@
       <c r="C433" t="s">
         <v>973</v>
       </c>
-    </row>
-    <row r="434" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E433" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="434" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A434">
         <v>544</v>
       </c>
@@ -8831,8 +10423,11 @@
       <c r="C434" t="s">
         <v>974</v>
       </c>
-    </row>
-    <row r="435" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E434" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="435" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A435">
         <v>545</v>
       </c>
@@ -8842,8 +10437,11 @@
       <c r="C435" t="s">
         <v>975</v>
       </c>
-    </row>
-    <row r="436" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E435" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="436" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A436">
         <v>546</v>
       </c>
@@ -8853,8 +10451,11 @@
       <c r="C436" t="s">
         <v>976</v>
       </c>
-    </row>
-    <row r="437" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E436" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="437" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A437">
         <v>547</v>
       </c>
@@ -8864,8 +10465,11 @@
       <c r="C437" t="s">
         <v>977</v>
       </c>
-    </row>
-    <row r="438" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E437" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="438" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A438">
         <v>548</v>
       </c>
@@ -8875,8 +10479,11 @@
       <c r="C438" t="s">
         <v>978</v>
       </c>
-    </row>
-    <row r="439" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E438" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="439" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A439">
         <v>549</v>
       </c>
@@ -8886,8 +10493,11 @@
       <c r="C439" t="s">
         <v>979</v>
       </c>
-    </row>
-    <row r="440" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E439" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="440" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A440">
         <v>550</v>
       </c>
@@ -8897,8 +10507,11 @@
       <c r="C440" t="s">
         <v>980</v>
       </c>
-    </row>
-    <row r="441" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E440" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="441" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A441">
         <v>551</v>
       </c>
@@ -8908,8 +10521,11 @@
       <c r="C441" t="s">
         <v>981</v>
       </c>
-    </row>
-    <row r="442" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E441" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="442" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A442">
         <v>552</v>
       </c>
@@ -8919,8 +10535,11 @@
       <c r="C442" t="s">
         <v>982</v>
       </c>
-    </row>
-    <row r="443" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E442" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="443" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A443">
         <v>553</v>
       </c>
@@ -8930,8 +10549,11 @@
       <c r="C443" t="s">
         <v>983</v>
       </c>
-    </row>
-    <row r="444" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E443" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="444" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A444">
         <v>554</v>
       </c>
@@ -8941,8 +10563,11 @@
       <c r="C444" t="s">
         <v>984</v>
       </c>
-    </row>
-    <row r="445" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E444" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="445" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A445">
         <v>555</v>
       </c>
@@ -8952,8 +10577,11 @@
       <c r="C445" t="s">
         <v>985</v>
       </c>
-    </row>
-    <row r="446" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E445" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="446" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A446">
         <v>556</v>
       </c>
@@ -8963,8 +10591,11 @@
       <c r="C446" t="s">
         <v>986</v>
       </c>
-    </row>
-    <row r="447" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E446" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="447" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A447">
         <v>557</v>
       </c>
@@ -8974,8 +10605,11 @@
       <c r="C447" t="s">
         <v>987</v>
       </c>
-    </row>
-    <row r="448" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E447" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="448" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A448">
         <v>558</v>
       </c>
@@ -8985,8 +10619,11 @@
       <c r="C448" t="s">
         <v>988</v>
       </c>
-    </row>
-    <row r="449" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E448" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="449" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A449">
         <v>559</v>
       </c>
@@ -8996,8 +10633,11 @@
       <c r="C449" t="s">
         <v>989</v>
       </c>
-    </row>
-    <row r="450" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E449" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="450" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A450">
         <v>560</v>
       </c>
@@ -9007,8 +10647,11 @@
       <c r="C450" t="s">
         <v>990</v>
       </c>
-    </row>
-    <row r="451" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E450" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="451" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A451">
         <v>561</v>
       </c>
@@ -9018,8 +10661,11 @@
       <c r="C451" t="s">
         <v>991</v>
       </c>
-    </row>
-    <row r="452" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E451" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="452" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A452">
         <v>562</v>
       </c>
@@ -9029,8 +10675,11 @@
       <c r="C452" t="s">
         <v>992</v>
       </c>
-    </row>
-    <row r="453" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E452" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="453" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A453">
         <v>563</v>
       </c>
@@ -9040,8 +10689,11 @@
       <c r="C453" t="s">
         <v>993</v>
       </c>
-    </row>
-    <row r="454" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E453" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="454" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A454">
         <v>564</v>
       </c>
@@ -9051,8 +10703,11 @@
       <c r="C454" t="s">
         <v>994</v>
       </c>
-    </row>
-    <row r="455" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E454" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="455" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A455">
         <v>565</v>
       </c>
@@ -9062,8 +10717,11 @@
       <c r="C455" t="s">
         <v>995</v>
       </c>
-    </row>
-    <row r="456" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E455" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="456" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A456">
         <v>566</v>
       </c>
@@ -9073,8 +10731,11 @@
       <c r="C456" t="s">
         <v>996</v>
       </c>
-    </row>
-    <row r="457" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E456" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="457" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A457">
         <v>567</v>
       </c>
@@ -9084,8 +10745,11 @@
       <c r="C457" t="s">
         <v>997</v>
       </c>
-    </row>
-    <row r="458" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E457" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="458" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A458">
         <v>568</v>
       </c>
@@ -9095,8 +10759,11 @@
       <c r="C458" t="s">
         <v>998</v>
       </c>
-    </row>
-    <row r="459" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E458" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="459" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A459">
         <v>569</v>
       </c>
@@ -9106,8 +10773,11 @@
       <c r="C459" t="s">
         <v>999</v>
       </c>
-    </row>
-    <row r="460" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E459" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="460" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A460">
         <v>570</v>
       </c>
@@ -9117,8 +10787,11 @@
       <c r="C460" t="s">
         <v>1000</v>
       </c>
-    </row>
-    <row r="461" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E460" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="461" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A461">
         <v>571</v>
       </c>
@@ -9128,8 +10801,11 @@
       <c r="C461" t="s">
         <v>1001</v>
       </c>
-    </row>
-    <row r="462" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E461" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="462" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A462">
         <v>572</v>
       </c>
@@ -9139,8 +10815,11 @@
       <c r="C462" t="s">
         <v>1002</v>
       </c>
-    </row>
-    <row r="463" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E462" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="463" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A463">
         <v>573</v>
       </c>
@@ -9150,8 +10829,11 @@
       <c r="C463" t="s">
         <v>1003</v>
       </c>
-    </row>
-    <row r="464" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E463" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="464" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A464">
         <v>574</v>
       </c>
@@ -9161,8 +10843,11 @@
       <c r="C464" t="s">
         <v>1004</v>
       </c>
-    </row>
-    <row r="465" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E464" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="465" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A465">
         <v>575</v>
       </c>
@@ -9172,8 +10857,11 @@
       <c r="C465" t="s">
         <v>1005</v>
       </c>
-    </row>
-    <row r="466" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E465" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="466" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A466">
         <v>576</v>
       </c>
@@ -9183,8 +10871,11 @@
       <c r="C466" t="s">
         <v>1006</v>
       </c>
-    </row>
-    <row r="467" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E466" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="467" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A467">
         <v>577</v>
       </c>
@@ -9194,8 +10885,11 @@
       <c r="C467" t="s">
         <v>1007</v>
       </c>
-    </row>
-    <row r="468" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E467" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="468" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A468">
         <v>578</v>
       </c>
@@ -9205,8 +10899,11 @@
       <c r="C468" t="s">
         <v>1008</v>
       </c>
-    </row>
-    <row r="469" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E468" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="469" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A469">
         <v>579</v>
       </c>
@@ -9216,8 +10913,11 @@
       <c r="C469" t="s">
         <v>1009</v>
       </c>
-    </row>
-    <row r="470" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E469" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="470" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A470">
         <v>580</v>
       </c>
@@ -9227,8 +10927,11 @@
       <c r="C470" t="s">
         <v>1010</v>
       </c>
-    </row>
-    <row r="471" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E470" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="471" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A471">
         <v>581</v>
       </c>
@@ -9238,8 +10941,11 @@
       <c r="C471" t="s">
         <v>1011</v>
       </c>
-    </row>
-    <row r="472" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E471" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="472" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A472">
         <v>582</v>
       </c>
@@ -9249,8 +10955,11 @@
       <c r="C472" t="s">
         <v>1012</v>
       </c>
-    </row>
-    <row r="473" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E472" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="473" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A473">
         <v>583</v>
       </c>
@@ -9260,8 +10969,11 @@
       <c r="C473" t="s">
         <v>1013</v>
       </c>
-    </row>
-    <row r="474" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E473" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="474" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A474">
         <v>584</v>
       </c>
@@ -9271,8 +10983,11 @@
       <c r="C474" t="s">
         <v>1014</v>
       </c>
-    </row>
-    <row r="475" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E474" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="475" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A475">
         <v>585</v>
       </c>
@@ -9282,8 +10997,11 @@
       <c r="C475" t="s">
         <v>1015</v>
       </c>
-    </row>
-    <row r="476" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E475" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="476" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A476">
         <v>586</v>
       </c>
@@ -9293,8 +11011,11 @@
       <c r="C476" t="s">
         <v>1016</v>
       </c>
-    </row>
-    <row r="477" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E476" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="477" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A477">
         <v>590</v>
       </c>
@@ -9304,8 +11025,11 @@
       <c r="C477" t="s">
         <v>1017</v>
       </c>
-    </row>
-    <row r="478" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E477" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="478" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A478">
         <v>591</v>
       </c>
@@ -9315,8 +11039,11 @@
       <c r="C478" t="s">
         <v>1018</v>
       </c>
-    </row>
-    <row r="479" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E478" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="479" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A479">
         <v>592</v>
       </c>
@@ -9326,8 +11053,11 @@
       <c r="C479" t="s">
         <v>1019</v>
       </c>
-    </row>
-    <row r="480" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E479" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="480" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A480">
         <v>593</v>
       </c>
@@ -9337,8 +11067,11 @@
       <c r="C480" t="s">
         <v>1020</v>
       </c>
-    </row>
-    <row r="481" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E480" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="481" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A481">
         <v>594</v>
       </c>
@@ -9348,8 +11081,11 @@
       <c r="C481" t="s">
         <v>1021</v>
       </c>
-    </row>
-    <row r="482" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E481" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="482" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A482">
         <v>595</v>
       </c>
@@ -9359,8 +11095,11 @@
       <c r="C482" t="s">
         <v>1022</v>
       </c>
-    </row>
-    <row r="483" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E482" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="483" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A483">
         <v>596</v>
       </c>
@@ -9370,8 +11109,11 @@
       <c r="C483" t="s">
         <v>1023</v>
       </c>
-    </row>
-    <row r="484" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E483" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="484" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A484">
         <v>597</v>
       </c>
@@ -9381,8 +11123,11 @@
       <c r="C484" t="s">
         <v>1024</v>
       </c>
-    </row>
-    <row r="485" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E484" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="485" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A485">
         <v>598</v>
       </c>
@@ -9392,8 +11137,11 @@
       <c r="C485" t="s">
         <v>1025</v>
       </c>
-    </row>
-    <row r="486" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E485" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="486" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A486">
         <v>599</v>
       </c>
@@ -9403,8 +11151,11 @@
       <c r="C486" t="s">
         <v>1026</v>
       </c>
-    </row>
-    <row r="487" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E486" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="487" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A487">
         <v>600</v>
       </c>
@@ -9414,8 +11165,11 @@
       <c r="C487" t="s">
         <v>1027</v>
       </c>
-    </row>
-    <row r="488" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E487" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="488" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A488">
         <v>601</v>
       </c>
@@ -9425,8 +11179,11 @@
       <c r="C488" t="s">
         <v>1028</v>
       </c>
-    </row>
-    <row r="489" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E488" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="489" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A489">
         <v>602</v>
       </c>
@@ -9436,8 +11193,11 @@
       <c r="C489" t="s">
         <v>1029</v>
       </c>
-    </row>
-    <row r="490" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E489" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="490" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A490">
         <v>603</v>
       </c>
@@ -9447,8 +11207,11 @@
       <c r="C490" t="s">
         <v>1030</v>
       </c>
-    </row>
-    <row r="491" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E490" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="491" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A491">
         <v>604</v>
       </c>
@@ -9458,8 +11221,11 @@
       <c r="C491" t="s">
         <v>1031</v>
       </c>
-    </row>
-    <row r="492" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E491" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="492" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A492">
         <v>605</v>
       </c>
@@ -9469,8 +11235,11 @@
       <c r="C492" t="s">
         <v>1032</v>
       </c>
-    </row>
-    <row r="493" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E492" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="493" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A493">
         <v>606</v>
       </c>
@@ -9480,8 +11249,11 @@
       <c r="C493" t="s">
         <v>1033</v>
       </c>
-    </row>
-    <row r="494" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E493" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="494" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A494">
         <v>607</v>
       </c>
@@ -9491,8 +11263,11 @@
       <c r="C494" t="s">
         <v>1034</v>
       </c>
-    </row>
-    <row r="495" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E494" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="495" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A495">
         <v>608</v>
       </c>
@@ -9502,8 +11277,11 @@
       <c r="C495" t="s">
         <v>1035</v>
       </c>
-    </row>
-    <row r="496" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E495" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="496" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A496">
         <v>609</v>
       </c>
@@ -9513,8 +11291,11 @@
       <c r="C496" t="s">
         <v>1036</v>
       </c>
-    </row>
-    <row r="497" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E496" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="497" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A497">
         <v>610</v>
       </c>
@@ -9524,8 +11305,11 @@
       <c r="C497" t="s">
         <v>1037</v>
       </c>
-    </row>
-    <row r="498" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E497" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="498" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A498">
         <v>611</v>
       </c>
@@ -9535,8 +11319,11 @@
       <c r="C498" t="s">
         <v>1038</v>
       </c>
-    </row>
-    <row r="499" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E498" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="499" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A499">
         <v>612</v>
       </c>
@@ -9546,8 +11333,11 @@
       <c r="C499" t="s">
         <v>1039</v>
       </c>
-    </row>
-    <row r="500" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E499" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="500" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A500">
         <v>613</v>
       </c>
@@ -9557,8 +11347,11 @@
       <c r="C500" t="s">
         <v>1040</v>
       </c>
-    </row>
-    <row r="501" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E500" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="501" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A501">
         <v>614</v>
       </c>
@@ -9568,8 +11361,11 @@
       <c r="C501" t="s">
         <v>1041</v>
       </c>
-    </row>
-    <row r="502" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E501" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="502" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A502">
         <v>615</v>
       </c>
@@ -9579,8 +11375,11 @@
       <c r="C502" t="s">
         <v>1042</v>
       </c>
-    </row>
-    <row r="503" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E502" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="503" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A503">
         <v>616</v>
       </c>
@@ -9590,8 +11389,11 @@
       <c r="C503" t="s">
         <v>1043</v>
       </c>
-    </row>
-    <row r="504" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E503" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="504" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A504">
         <v>617</v>
       </c>
@@ -9601,8 +11403,11 @@
       <c r="C504" t="s">
         <v>1044</v>
       </c>
-    </row>
-    <row r="505" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E504" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="505" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A505">
         <v>618</v>
       </c>
@@ -9612,8 +11417,11 @@
       <c r="C505" t="s">
         <v>1045</v>
       </c>
-    </row>
-    <row r="506" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E505" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="506" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A506">
         <v>619</v>
       </c>
@@ -9623,8 +11431,11 @@
       <c r="C506" t="s">
         <v>1046</v>
       </c>
-    </row>
-    <row r="507" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E506" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="507" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A507">
         <v>620</v>
       </c>
@@ -9634,8 +11445,11 @@
       <c r="C507" t="s">
         <v>1047</v>
       </c>
-    </row>
-    <row r="508" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E507" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="508" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A508">
         <v>621</v>
       </c>
@@ -9645,8 +11459,11 @@
       <c r="C508" t="s">
         <v>1048</v>
       </c>
-    </row>
-    <row r="509" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E508" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="509" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A509">
         <v>622</v>
       </c>
@@ -9656,8 +11473,11 @@
       <c r="C509" t="s">
         <v>1049</v>
       </c>
-    </row>
-    <row r="510" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E509" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="510" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A510">
         <v>623</v>
       </c>
@@ -9667,8 +11487,11 @@
       <c r="C510" t="s">
         <v>1050</v>
       </c>
-    </row>
-    <row r="511" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E510" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="511" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A511">
         <v>624</v>
       </c>
@@ -9678,8 +11501,11 @@
       <c r="C511" t="s">
         <v>1051</v>
       </c>
-    </row>
-    <row r="512" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E511" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="512" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A512">
         <v>625</v>
       </c>
@@ -9689,8 +11515,11 @@
       <c r="C512" t="s">
         <v>1052</v>
       </c>
-    </row>
-    <row r="513" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E512" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="513" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A513">
         <v>626</v>
       </c>
@@ -9700,8 +11529,11 @@
       <c r="C513" t="s">
         <v>1053</v>
       </c>
-    </row>
-    <row r="514" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E513" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="514" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A514">
         <v>627</v>
       </c>
@@ -9711,8 +11543,11 @@
       <c r="C514" t="s">
         <v>1054</v>
       </c>
-    </row>
-    <row r="515" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E514" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="515" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A515">
         <v>628</v>
       </c>
@@ -9722,8 +11557,11 @@
       <c r="C515" t="s">
         <v>1055</v>
       </c>
-    </row>
-    <row r="516" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E515" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="516" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A516">
         <v>629</v>
       </c>
@@ -9733,8 +11571,11 @@
       <c r="C516" t="s">
         <v>1056</v>
       </c>
-    </row>
-    <row r="517" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E516" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="517" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A517">
         <v>630</v>
       </c>
@@ -9744,8 +11585,11 @@
       <c r="C517" t="s">
         <v>1057</v>
       </c>
-    </row>
-    <row r="518" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E517" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="518" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A518">
         <v>631</v>
       </c>
@@ -9755,8 +11599,11 @@
       <c r="C518" t="s">
         <v>1058</v>
       </c>
-    </row>
-    <row r="519" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E518" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="519" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A519">
         <v>632</v>
       </c>
@@ -9766,8 +11613,11 @@
       <c r="C519" t="s">
         <v>1059</v>
       </c>
-    </row>
-    <row r="520" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E519" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="520" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A520">
         <v>633</v>
       </c>
@@ -9777,8 +11627,11 @@
       <c r="C520" t="s">
         <v>1060</v>
       </c>
-    </row>
-    <row r="521" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E520" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="521" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A521">
         <v>634</v>
       </c>
@@ -9788,8 +11641,11 @@
       <c r="C521" t="s">
         <v>1061</v>
       </c>
-    </row>
-    <row r="522" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E521" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="522" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A522">
         <v>635</v>
       </c>
@@ -9799,8 +11655,11 @@
       <c r="C522" t="s">
         <v>1062</v>
       </c>
-    </row>
-    <row r="523" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E522" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="523" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A523">
         <v>636</v>
       </c>
@@ -9810,8 +11669,11 @@
       <c r="C523" t="s">
         <v>1063</v>
       </c>
-    </row>
-    <row r="524" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E523" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="524" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A524">
         <v>637</v>
       </c>
@@ -9821,8 +11683,11 @@
       <c r="C524" t="s">
         <v>1064</v>
       </c>
-    </row>
-    <row r="525" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E524" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="525" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A525">
         <v>638</v>
       </c>
@@ -9832,8 +11697,11 @@
       <c r="C525" t="s">
         <v>1065</v>
       </c>
-    </row>
-    <row r="526" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E525" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="526" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A526">
         <v>639</v>
       </c>
@@ -9843,8 +11711,11 @@
       <c r="C526" t="s">
         <v>1066</v>
       </c>
-    </row>
-    <row r="527" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E526" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="527" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A527">
         <v>640</v>
       </c>
@@ -9854,8 +11725,11 @@
       <c r="C527" t="s">
         <v>1067</v>
       </c>
-    </row>
-    <row r="528" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E527" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="528" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A528">
         <v>641</v>
       </c>
@@ -9865,8 +11739,11 @@
       <c r="C528" t="s">
         <v>1068</v>
       </c>
-    </row>
-    <row r="529" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E528" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="529" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A529">
         <v>642</v>
       </c>
@@ -9876,8 +11753,11 @@
       <c r="C529" t="s">
         <v>1069</v>
       </c>
-    </row>
-    <row r="530" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E529" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="530" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A530">
         <v>643</v>
       </c>
@@ -9887,8 +11767,11 @@
       <c r="C530" t="s">
         <v>1070</v>
       </c>
-    </row>
-    <row r="531" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E530" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="531" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A531">
         <v>644</v>
       </c>
@@ -9898,8 +11781,11 @@
       <c r="C531" t="s">
         <v>1071</v>
       </c>
-    </row>
-    <row r="532" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E531" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="532" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A532">
         <v>645</v>
       </c>
@@ -9909,8 +11795,11 @@
       <c r="C532" t="s">
         <v>1072</v>
       </c>
-    </row>
-    <row r="533" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E532" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="533" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A533">
         <v>646</v>
       </c>
@@ -9920,8 +11809,11 @@
       <c r="C533" t="s">
         <v>1073</v>
       </c>
-    </row>
-    <row r="534" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E533" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="534" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A534">
         <v>647</v>
       </c>
@@ -9931,8 +11823,11 @@
       <c r="C534" t="s">
         <v>1074</v>
       </c>
-    </row>
-    <row r="535" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E534" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="535" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A535">
         <v>648</v>
       </c>
@@ -9942,8 +11837,11 @@
       <c r="C535" t="s">
         <v>1075</v>
       </c>
-    </row>
-    <row r="536" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E535" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="536" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A536">
         <v>649</v>
       </c>
@@ -9953,8 +11851,11 @@
       <c r="C536" t="s">
         <v>1076</v>
       </c>
-    </row>
-    <row r="537" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E536" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="537" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A537">
         <v>650</v>
       </c>
@@ -9964,8 +11865,11 @@
       <c r="C537" t="s">
         <v>1077</v>
       </c>
-    </row>
-    <row r="538" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E537" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="538" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A538">
         <v>651</v>
       </c>
@@ -9975,8 +11879,11 @@
       <c r="C538" t="s">
         <v>1078</v>
       </c>
-    </row>
-    <row r="539" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E538" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="539" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A539">
         <v>652</v>
       </c>
@@ -9986,8 +11893,11 @@
       <c r="C539" t="s">
         <v>1079</v>
       </c>
-    </row>
-    <row r="540" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E539" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="540" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A540">
         <v>653</v>
       </c>
@@ -9997,8 +11907,11 @@
       <c r="C540" t="s">
         <v>1080</v>
       </c>
-    </row>
-    <row r="541" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E540" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="541" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A541">
         <v>654</v>
       </c>
@@ -10010,6 +11923,10 @@
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="F4" r:id="rId1" xr:uid="{FC924530-9D20-4B0C-8B08-C35D65377ECD}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId2"/>
 </worksheet>
 </file>
--- a/database/Take Notes/RL/RL.xlsx
+++ b/database/Take Notes/RL/RL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Cursor AI\database\Take Notes\RL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B57E6282-4218-4CA2-9B8E-B7252A83C886}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C79FF580-3655-4ED8-8491-955CBDA46FE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1631" uniqueCount="1095">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1632" uniqueCount="1096">
   <si>
     <t>ID</t>
   </si>
@@ -3926,6 +3926,9 @@
 Well done! Vehicle-dependent means needing vehicles to live and work.
 That's the end of the video!  
 I’m Bel — like and subscribe for Better English Learning!</t>
+  </si>
+  <si>
+    <t>https://youtu.be/1V0aZUO57xY</t>
   </si>
 </sst>
 </file>
@@ -4420,6 +4423,9 @@
       <c r="E5" s="3" t="s">
         <v>1094</v>
       </c>
+      <c r="F5" t="s">
+        <v>1095</v>
+      </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6">

--- a/database/Take Notes/RL/RL.xlsx
+++ b/database/Take Notes/RL/RL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Cursor AI\database\Take Notes\RL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C79FF580-3655-4ED8-8491-955CBDA46FE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1C86EA3-987A-4656-943D-37BE15686436}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1632" uniqueCount="1096">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1634" uniqueCount="1100">
   <si>
     <t>ID</t>
   </si>
@@ -3929,6 +3929,176 @@
   </si>
   <si>
     <t>https://youtu.be/1V0aZUO57xY</t>
+  </si>
+  <si>
+    <t>https://youtu.be/HoCzqTtCbJc</t>
+  </si>
+  <si>
+    <t>Host (Bel):
+Welcome to today’s learning podcast! I’m Bel, and I’m really happy you’re listening today.
+In this episode, we’re going to talk about what makes a city fair and just. This idea comes from philosophy, but don’t worry — we’re going to explain everything in a simple and clear way.
+When we talk about a “just city,” we are really asking some important questions.
+Who benefits from city policies?
+Who is helped the most?
+And who might be hurt?
+To help us explore these questions, I’m joined by Alison. Alison has studied philosophy and has spent a lot of time thinking about fairness, cities, and social policy.
+Alison, thank you so much for being here today.
+Expert (Alison):
+Thank you, Bel. I’m very happy to be here and to talk with your listeners.
+Host (Bel):
+So, Alison, let’s start at the beginning. For our listeners, can you explain how philosophy helped you think about what makes a city just?
+Expert (Alison):
+Of course. From reading philosophy, I came up with three guiding principles for a just city. These principles are equity, democracy, and diversity.
+Host (Bel):
+Three principles already give us a clear structure. For our listeners, where do these ideas come from?
+Expert (Alison):
+They come from the work of several philosophers. One philosopher who influenced me a lot is Ross.
+Host (Bel):
+Let me pause you there, because this is really important.
+You choose the word equity, not equality. Many of our listeners may think these words mean the same thing.
+Can you explain the difference to our listeners?
+Expert (Alison):
+Yes, this is a key idea.
+Equality means everyone gets the same thing.
+Equity means that policies should help people so that those who are worst off become better off.
+Host (Bel):
+So, just to make sure everyone is following — equity does not mean everyone must become equal?
+Expert (Alison):
+That’s right. Equity does not mean everyone is the same.
+But it does mean that no policy should make the most disadvantaged people even more disadvantaged.
+Host (Bel):
+That feels very powerful.
+So when we talk about city policies, when should we think about equity?
+Expert (Alison):
+We must think about equity at the moment the policy is created and used, not only in the future.
+Host (Bel):
+Can you explain that a bit more for our listeners?
+Expert (Alison):
+Sure. Sometimes people say, “We need to make our city more competitive now, and later the benefits will reach everyone.”
+But this does not justify hurting the weakest people today.
+Host (Bel):
+I think many listeners will recognize that idea.
+Expert (Alison):
+Yes. Around the world, we see examples where people’s homes are destroyed in the name of the “greater good.”
+They are told that one day they will benefit — but right now, they suffer.
+Host (Bel):
+So equity asks us to be very careful, doesn’t it?
+Expert (Alison):
+Exactly. Equity means we do not take advantage of people who are weakest, even if we say it is for a better future.
+Host (Bel):
+Let me say this again in simple words for our listeners.
+Equity means we should never improve a city by hurting the people who already have the least.
+Expert (Alison):
+Yes. That is exactly the heart of the idea.
+Host (Bel):
+Thank you so much, Alison, for explaining this so clearly.
+And thank you to our listeners for spending time with us today.
+If you want, next I can:
+✅ Add a listener recap + vocabulary section
+✅ Convert this into your standard Version 2 teaching script
+✅ Make it even more interactive (questions directly to the listener)
+✅ Simplify further to A2 only
+Just tell me what you’d like next 🎧✨</t>
+  </si>
+  <si>
+    <t>https://youtu.be/vY1V59_i82c</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Welcome to today’s learning podcast! I am Bel, and I’m really happy you’re listening today.
+In this episode, we’re talking about what makes a city fair and just. This idea comes from philosophy, but don’t worry, we’ll explain everything in a simple way.
+When we talk about a just city, we ask important questions. Who benefits from city policies? Who is helped the most? And who might be hurt?
+We're going to explore these ideas with Alison, a philosophy expert.
+So, how did philosophy help shape these ideas, Alison?
+From reading philosophy, three guiding principles for a just city were identified: equity, democracy, and diversity.
+These ideas come from the work of several philosophers. One important philosopher is Ross.
+You may be wondering: why use the word equity instead of equality?
+That’s a great question.
+Equality means everyone gets the same thing. Equity means helping people so that those who are worst off become better off.
+Equity does not mean everyone must be equal. But it does mean that no policy should make the most disadvantaged people more disadvantaged.
+So when should we think about equity?
+We need to think about equity at the time a policy is created, not only in the future.
+Sometimes people say, “We must make the city more competitive now, and later the benefits will reach everyone.”
+But this does not justify hurting the weakest people today.
+Around the world, we see examples of people losing their homes in the name of the greater good. They are told they will benefit one day, but they suffer now.
+Equity means we do not take advantage of people who are weakest.
+In simple words, equity means we should never improve a city by hurting the people who already have the least.
+Now let’s recap what we learned today.
+A just city is a fair city.
+Philosophy gives us three principles for a just city: equity, democracy, and diversity.
+Equity means helping the people who are worst off.
+Equity is different from equality.
+Good policies should not harm the weakest people, even in the name of the future.
+That's the main ideas that you learned today! We will now review some new vocabularies.
+Repeat after me.
+Just city
+&lt;break time="2s" /&gt;
+Just city
+&lt;break time="2s" /&gt;
+Just city
+&lt;break time="2s" /&gt;
+Good job! A just city is a city that is fair to everyone.
+&lt;break time="0.5s" /&gt;
+Next
+&lt;break time="0.5s" /&gt;
+Equity
+&lt;break time="2s" /&gt;
+Equity
+&lt;break time="2s" /&gt;
+Equity
+&lt;break time="2s" /&gt;
+Great! Equity means helping people so the weakest become better off.
+&lt;break time="0.5s" /&gt;
+Next
+&lt;break time="0.5s" /&gt;
+Equality
+&lt;break time="2s" /&gt;
+Equality
+&lt;break time="2s" /&gt;
+Equality
+&lt;break time="2s" /&gt;
+Well done! Equality means everyone gets the same thing.
+&lt;break time="0.5s" /&gt;
+Next
+&lt;break time="0.5s" /&gt;
+Policy
+&lt;break time="1s" /&gt;
+Policy
+&lt;break time="1s" /&gt;
+Policy
+&lt;break time="1s" /&gt;
+A policy is a plan or rule made by a government or city.
+&lt;break time="0.5s" /&gt;
+Next
+&lt;break time="0.5s" /&gt;
+Disadvantaged
+&lt;break time="1s" /&gt;
+Disadvantaged
+&lt;break time="1s" /&gt;
+Disadvantaged
+&lt;break time="1s" /&gt;
+Disadvantaged means having less help or fewer chances.
+&lt;break time="0.5s" /&gt;
+Next
+&lt;break time="0.5s" /&gt;
+Greater good
+&lt;break time="1s" /&gt;
+Greater good
+&lt;break time="1s" /&gt;
+Greater good
+&lt;break time="1s" /&gt;
+The greater good means helping many people, sometimes at a cost.
+&lt;break time="0.5s" /&gt;
+Next
+&lt;break time="0.5s" /&gt;
+Philosophy
+&lt;break time="1s" /&gt;
+Philosophy
+&lt;break time="1s" /&gt;
+Philosophy
+&lt;break time="1s" /&gt;
+Well done! Philosophy is the study of ideas about life, fairness, and meaning.
+That's the end of the video!
+I’m Bel — like and subscribe for Better English Learning!</t>
   </si>
 </sst>
 </file>
@@ -4015,8 +4185,8 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -4403,8 +4573,8 @@
       <c r="E4" t="s">
         <v>1091</v>
       </c>
-      <c r="F4" s="4" t="s">
-        <v>1088</v>
+      <c r="F4" s="3" t="s">
+        <v>1096</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -4417,10 +4587,10 @@
       <c r="C5" t="s">
         <v>545</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" t="s">
         <v>1093</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" t="s">
         <v>1094</v>
       </c>
       <c r="F5" t="s">
@@ -4437,8 +4607,14 @@
       <c r="C6" t="s">
         <v>546</v>
       </c>
-      <c r="E6" t="s">
-        <v>1092</v>
+      <c r="D6" s="4" t="s">
+        <v>1097</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>1099</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>1098</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -11930,7 +12106,7 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="F4" r:id="rId1" xr:uid="{FC924530-9D20-4B0C-8B08-C35D65377ECD}"/>
+    <hyperlink ref="F6" r:id="rId1" xr:uid="{E98772F5-F3A2-4178-B97F-E8A8C6014580}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId2"/>

--- a/database/Take Notes/RL/RL.xlsx
+++ b/database/Take Notes/RL/RL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Cursor AI\database\Take Notes\RL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1C86EA3-987A-4656-943D-37BE15686436}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43C590F8-9C35-4A49-8ACC-1E718FF65A62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1634" uniqueCount="1100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1631" uniqueCount="1100">
   <si>
     <t>ID</t>
   </si>
@@ -3548,9 +3548,6 @@
   </si>
   <si>
     <t>As the world's population grows, ensuring everyone has access to sufficient, nutritious food is a critical challenge. Sustainable farming practices offer a promising solution to this challenge. Firstly, sustainable farming involves methods that are environmentally friendly, such as reducing chemical use, conserving water, and promoting biodiversity. These practices are not only crucial for protecting our environment but also for ensuring long-term agricultural productivity. Healthy ecosystems are more resilient and can provide the resources needed for continuous food production. Secondly, sustainable farming includes a focus on local production and distribution. By supporting local food systems, we can reduce the carbon footprint associated with long-distance transportation of food. Additionally, local farming empowers communities, supports the local economy, and ensures fresher, more nutritious food reaches consumers. However, transitioning to sustainable farming requires effort and collaboration from various stakeholders, including governments, farmers, and consumers. It involves embracing new technologies, investing in education, and creating policies that support sustainable practices. In conclusion, sustainable farming is not just an environmentally responsible choice; it's a necessary step towards global food security and a healthier planet. By adopting these practices, we can ensure that future generations have access to the food they need to thrive.</t>
-  </si>
-  <si>
-    <t>Podcast script</t>
   </si>
   <si>
     <t>Podcast transcript</t>
@@ -3596,53 +3593,6 @@
 Great job listening and repeating. See you next time.</t>
   </si>
   <si>
-    <t>Welcome to today’s science podcast! Today we are talking about gas giant planets, like Jupiter. How do these big planets form?
-That’s a great question. Scientists have two main ideas, or theories, about how gas giants form.
-Two theories? What are they?
-The first one is called core accretion. This means a small, hard center forms first, and then gas slowly collects around it.
-The second theory is called disk instability. In this idea, gas comes together very fast and forms a planet quickly.
-So scientists are still not sure which theory is correct?
-Yes, that’s right. We are still learning, and both ideas are possible.
-I also hear scientists talk a lot about pressure. Why is pressure important?
-Pressure means how hard something is pushed. Inside gas giant planets, the pressure is very, very high.
-Scientists try to make high pressure in a laboratory to understand what happens inside these planets.
-What do scientists want to learn about the inside of gas giants?
-They want to learn about the core, or the center of the planet. Gas giants may have a metallic core, but it may not be made of iron.
-Not iron? Then what kind of metal?
-Hydrogen. At very high pressure, hydrogen can become metallic.
-So inside gas giants, there could be metallic hydrogen, rocky parts, or different layers.
-Let me check if I understand.
-Gas giants may have metal, hydrogen, or rock inside them.
-Scientists use high pressure in labs to learn more about this.
-Exactly. This also helps us understand exoplanets, which are very large planets outside our solar system.
-Now let’s recap what we learned today.
-Gas giants are very big planets made mostly of gas.
-There are two theories about how they form: core accretion and disk instability.
-Scientists are not 100% sure which theory is correct.
-Inside gas giants, the pressure is very high.
-High pressure can change hydrogen into metal.
-Studying pressure helps us understand gas giants and exoplanets.
-Now repeat after me.
-Gas giant — gas giant — gas giant
-A very big planet made mostly of gas.
-Theory — theory — theory
-An idea that explains how something works.
-Core accretion — core accretion — core accretion
-A slow way a planet forms, starting with a hard center.
-Disk instability — disk instability — disk instability
-A fast way a planet forms from gas.
-Pressure — pressure — pressure
-How strong something pushes.
-Laboratory — laboratory — laboratory
-A place where scientists do experiments.
-Metallic core — metallic core — metallic core
-The metal center of a planet.
-Hydrogen — hydrogen — hydrogen
-A gas that can become metal at high pressure.
-Exoplanet — exoplanet — exoplanet
-A planet outside our solar system.</t>
-  </si>
-  <si>
     <t>Transcript</t>
   </si>
   <si>
@@ -3653,62 +3603,6 @@
   </si>
   <si>
     <t>https://youtu.be/H9750VLTvt0</t>
-  </si>
-  <si>
-    <t>Podcast Conversation: What Is Supersymmetry? (A2–B1 Level)
-Host:
-Welcome to today’s science podcast! I am Bel, and today we are talking about supersymmetry. It sounds difficult, but we will explain it in a simple way. So, what is supersymmetry?
-Expert:
-Supersymmetry is a mathematical idea. Scientists use it to understand the basic parts of matter and how they are organized.
-Host:
-Why do scientists use ideas like symmetry?
-Expert:
-Because we have learned that things that look different can actually be connected by symmetry.
-For example, think about a sphere, like a basketball. When you turn it, it looks different, but it is still the same shape.
-Host:
-So symmetry means something stays the same, even when it changes?
-Expert:
-Yes, exactly. In physics, we found that some particles can change into other particles, but the math equations describing them stay the same.
-Host:
-That sounds interesting. But what was missing?
-Expert:
-What we could not find was a symmetry that connects two big groups of particles:
-matter particles and force particles.
-Host:
-What are matter particles?
-Expert:
-Matter particles are particles that make things. For example, electrons, muons, and quarks.
-Host:
-And force particles?
-Expert:
-Force particles carry forces. For example, photons, gluons, and W and Z bosons.
-Host:
-So how does supersymmetry help?
-Expert:
-Supersymmetry is a symmetry that connects matter particles and force particles.
-It says they are related at a deep level.
-Host:
-Does supersymmetry exist in the real world?
-Expert:
-Mathematically, scientists have shown that supersymmetry could be the last possible symmetry of fundamental particles.
-But so far, we have no clear evidence that nature uses it.
-Host:
-So what are scientists doing now?
-Expert:
-They are looking for evidence. They want to see if supersymmetry is really working in the universe.
-✅ Final Recap
-Host:
-Now let’s recap what we learned today.
-Supersymmetry is a mathematical idea.
-Symmetry means something stays the same after a change.
-Particles can look different but follow the same rules.
-There are matter particles and force particles.
-Supersymmetry connects these two groups.
-Scientists are still searching for proof in the real world.
-Host:
-That’s the main ideas that you learned today!
-I’m Bel — thank you for listening.
-Like and subscribe for Better English Learning!</t>
   </si>
   <si>
     <t>Welcome to today’s science podcast! I am Bel, and today we are talking about supersymmetry. It sounds difficult, but we will explain it in a simple way. So, what is supersymmetry?
@@ -3795,63 +3689,6 @@
     <t xml:space="preserve"> </t>
   </si>
   <si>
-    <t>Podcast Conversation: Changes in Air Pollution (A2–B1 Level)
-Host:
-Welcome to today’s science podcast! I am Bel, and today we are talking about air pollution and how it has changed since the 1950s. What was air pollution like in the past?
-Expert:
-In the 1950s, air pollution was very easy to see. Many big cities had thick black fogs called smogs.
-Host:
-What caused these smogs?
-Expert:
-The main cause was factories. They burned a lot of coal, and this caused serious health problems.
-Host:
-Was it dangerous?
-Expert:
-Yes, very dangerous. In London, in 1952, a very bad smog caused over four thousand deaths.
-Host:
-That sounds terrible. What did people do?
-Expert:
-In 1956, Britain introduced the Clean Air Act. This law controlled pollution from factories.
-Host:
-And did it work?
-Expert:
-Yes. After that, the black smogs disappeared.
-Host:
-But air pollution is still a problem today, right?
-Expert:
-Yes, it is. The big difference today is that air pollution is mostly invisible.
-Host:
-So where does pollution come from now?
-Expert:
-Today, the main source is vehicles, like cars and lorries. They don’t make black smoke, but they still harm our health.
-Host:
-Why is this type of pollution increasing?
-Expert:
-Because we are much more vehicle-dependent.
-There are far more cars, lorries, trains, and planes than in the 1950s.
-Host:
-Let me check if I understand.
-Host:
-In the past, factories caused visible smog.
-Today, vehicles cause invisible pollution.
-Both are dangerous to health.
-Expert:
-Exactly. Vehicle pollution is now the main source of air pollution around the world.
-✅ Final Recap
-Host:
-Now let’s recap what we learned today.
-In the 1950s, air pollution was visible.
-Thick black smogs came from factories.
-Smog caused serious health problems.
-The Clean Air Act helped reduce factory pollution.
-Today, air pollution is mostly invisible.
-Cars and lorries are now the main source.
-Host:
-That’s the main ideas that you learned today!
-I’m Bel — thank you for listening.
-Like and subscribe for Better English Learning!</t>
-  </si>
-  <si>
     <t xml:space="preserve"> Welcome to today’s science podcast! I am Bel, and today we are talking about air pollution and how it has changed since the 1950s.
 In today’s lecture, I’m going to talk about changes in air pollution since the middle of the last century and what caused these changes.
 By the 1950s, air pollution was very visible. Many large cities had thick black fogs called smogs.
@@ -3932,73 +3769,6 @@
   </si>
   <si>
     <t>https://youtu.be/HoCzqTtCbJc</t>
-  </si>
-  <si>
-    <t>Host (Bel):
-Welcome to today’s learning podcast! I’m Bel, and I’m really happy you’re listening today.
-In this episode, we’re going to talk about what makes a city fair and just. This idea comes from philosophy, but don’t worry — we’re going to explain everything in a simple and clear way.
-When we talk about a “just city,” we are really asking some important questions.
-Who benefits from city policies?
-Who is helped the most?
-And who might be hurt?
-To help us explore these questions, I’m joined by Alison. Alison has studied philosophy and has spent a lot of time thinking about fairness, cities, and social policy.
-Alison, thank you so much for being here today.
-Expert (Alison):
-Thank you, Bel. I’m very happy to be here and to talk with your listeners.
-Host (Bel):
-So, Alison, let’s start at the beginning. For our listeners, can you explain how philosophy helped you think about what makes a city just?
-Expert (Alison):
-Of course. From reading philosophy, I came up with three guiding principles for a just city. These principles are equity, democracy, and diversity.
-Host (Bel):
-Three principles already give us a clear structure. For our listeners, where do these ideas come from?
-Expert (Alison):
-They come from the work of several philosophers. One philosopher who influenced me a lot is Ross.
-Host (Bel):
-Let me pause you there, because this is really important.
-You choose the word equity, not equality. Many of our listeners may think these words mean the same thing.
-Can you explain the difference to our listeners?
-Expert (Alison):
-Yes, this is a key idea.
-Equality means everyone gets the same thing.
-Equity means that policies should help people so that those who are worst off become better off.
-Host (Bel):
-So, just to make sure everyone is following — equity does not mean everyone must become equal?
-Expert (Alison):
-That’s right. Equity does not mean everyone is the same.
-But it does mean that no policy should make the most disadvantaged people even more disadvantaged.
-Host (Bel):
-That feels very powerful.
-So when we talk about city policies, when should we think about equity?
-Expert (Alison):
-We must think about equity at the moment the policy is created and used, not only in the future.
-Host (Bel):
-Can you explain that a bit more for our listeners?
-Expert (Alison):
-Sure. Sometimes people say, “We need to make our city more competitive now, and later the benefits will reach everyone.”
-But this does not justify hurting the weakest people today.
-Host (Bel):
-I think many listeners will recognize that idea.
-Expert (Alison):
-Yes. Around the world, we see examples where people’s homes are destroyed in the name of the “greater good.”
-They are told that one day they will benefit — but right now, they suffer.
-Host (Bel):
-So equity asks us to be very careful, doesn’t it?
-Expert (Alison):
-Exactly. Equity means we do not take advantage of people who are weakest, even if we say it is for a better future.
-Host (Bel):
-Let me say this again in simple words for our listeners.
-Equity means we should never improve a city by hurting the people who already have the least.
-Expert (Alison):
-Yes. That is exactly the heart of the idea.
-Host (Bel):
-Thank you so much, Alison, for explaining this so clearly.
-And thank you to our listeners for spending time with us today.
-If you want, next I can:
-✅ Add a listener recap + vocabulary section
-✅ Convert this into your standard Version 2 teaching script
-✅ Make it even more interactive (questions directly to the listener)
-✅ Simplify further to A2 only
-Just tell me what you’d like next 🎧✨</t>
   </si>
   <si>
     <t>https://youtu.be/vY1V59_i82c</t>
@@ -4100,6 +3870,200 @@
 That's the end of the video!
 I’m Bel — like and subscribe for Better English Learning!</t>
   </si>
+  <si>
+    <t>https://youtu.be/_WhgSSCeMSA</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Welcome to today’s learning podcast! I am Bel, and I’m really happy you’re listening today.
+In this episode, we’re talking about how Apple works as a company and why teamwork is so important to its success.
+Many people think big companies are slow and full of committees. But Apple works in a very different way.
+To help us understand this, I’m joined by our expert today, Ms. Alison. Thank you so much for being here.
+Thank you, Bel. I’m happy to be here.
+Let’s start with something that surprises many people. Can you explain to our listeners how Apple is organized?
+Of course. One key to Apple’s success is that it is an incredibly collaborative company.
+And here is something surprising — Apple has zero committees.
+Zero committees? That’s very unusual for such a big company. How does Apple work without them?
+Apple is organized like a startup. Each person has a very clear role and responsibility.
+Can you give us some examples so our listeners can understand better?
+Sure. One person is in charge of iPhone software.
+Another person is in charge of Mac hardware.
+Another person is responsible for iPhone hardware engineering.
+Another person leads worldwide marketing.
+And another person is in charge of operations.
+So everyone knows exactly what their job is?
+Exactly. Even though Apple is very large, it works like the biggest startup in the world.
+So how do all these people stay connected and work together?
+The leaders meet once a week for about three hours.
+They talk about everything happening in the business.
+And how does that affect the rest of the company?
+That teamwork at the top spreads throughout the whole company.
+People communicate often and work closely together.
+It sounds like trust is very important here.
+Yes, trust is essential. Teamwork depends on trusting others to do their part without watching them all the time.
+That’s a great lesson for our listeners.
+Apple is also very good at dividing work into strong teams.
+The teams work on the same goal, communicate often, and bring everything together into one product.
+So what do you spend most of your day doing?
+I spend most of my day meeting with teams, working on ideas, and solving problems — for new products or new marketing programs.
+Thank you for sharing that. Let me summarize this for our listeners.
+Now let’s recap what we learned today.
+Apple works like a startup, even though it is very big.
+Apple has no committees.
+Each person has a clear responsibility.
+Teamwork is very important at Apple.
+Trust helps teams work well.
+Good teamwork helps turn ideas into products.
+That's the main ideas that you learned today! We will now review some new vocabularies.
+Repeat after me.
+Teamwork
+&lt;break time="2s" /&gt;
+Teamwork
+&lt;break time="2s" /&gt;
+Teamwork
+&lt;break time="2s" /&gt;
+Good job! Teamwork means working well together with other people.
+&lt;break time="1s" /&gt;
+Next
+&lt;break time="1s" /&gt;
+Startup
+&lt;break time="2s" /&gt;
+Startup
+&lt;break time="2s" /&gt;
+Startup
+&lt;break time="2s" /&gt;
+Great! A startup is a young company that works in a fast and flexible way.
+&lt;break time="1s" /&gt;
+Next
+&lt;break time="1s" /&gt;
+Committee
+&lt;break time="2s" /&gt;
+Committee
+&lt;break time="2s" /&gt;
+Committee
+&lt;break time="2s" /&gt;
+Well done! A committee is a group of people who make decisions together.
+&lt;break time="1s" /&gt;
+Next
+&lt;break time="1s" /&gt;
+Responsibility
+&lt;break time="1s" /&gt;
+Responsibility
+&lt;break time="1s" /&gt;
+Responsibility
+&lt;break time="1s" /&gt;
+Responsibility means a job or duty you must take care of.
+&lt;break time="1s" /&gt;
+Next
+&lt;break time="1s" /&gt;
+Trust
+&lt;break time="1s" /&gt;
+Trust
+&lt;break time="1s" /&gt;
+Trust
+&lt;break time="1s" /&gt;
+Trust means believing that someone will do what they promise.
+&lt;break time="1s" /&gt;
+Next
+&lt;break time="1s" /&gt;
+Product
+&lt;break time="1s" /&gt;
+Product
+&lt;break time="1s" /&gt;
+Product
+&lt;break time="1s" /&gt;
+Well done! A product is something a company makes and sells.
+That's the end of the video!
+I’m Bel — like and subscribe for Better English Learning!</t>
+  </si>
+  <si>
+    <t>https://youtu.be/ITbc1KXc3XI</t>
+  </si>
+  <si>
+    <t>https://youtu.be/EyQ1CSlRIyc</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Welcome to today’s learning podcast! I am Bel, and I’m very happy to have you with us. This podcast is made especially for learners who want to improve their English while learning something interesting and useful. Today’s topic connects science, energy, and things from everyday life.
+I’m not alone today. I’m joined by Alison, our expert, who helps explain scientific ideas in clear and simple English. Together, we’re going to talk about a special piece of lab equipment that scientists use to measure energy.
+Thanks, Bel. Hi everyone. 
+I’m Alison, and I’m excited to be here. Today we’re going to explore how scientists find out how much energy is inside fuels and even food.
+That’s right. For our listeners, we’re talking about a tool called a bomb calorimeter. Scientists use it to measure energy in things like biodiesel, petroleum fuels, and even potato chips. Let’s get started.
+So Alison, first of all, what is a bomb calorimeter?
+A bomb calorimeter is a piece of equipment that scientists use to measure how much energy is inside a substance, like biodiesel or even potato chips.
+Wait, potato chips? The same chips I eat for lunch?
+Yes, exactly. Scientists can burn food in a bomb calorimeter to find out how much energy it contains.
+That’s interesting. So how is energy measured in this machine?
+Energy is measured as heat. Scientists usually use units like joules or calories to describe this heat.
+Okay, let’s look inside the bomb calorimeter. What do we see?
+Inside, there is a large container filled with water. In the center, there is a smaller strong metal container called the bomb.
+And what goes inside this bomb?
+You put a small sample of fuel inside it. This could be biodiesel, for example.
+How does the fuel start burning?
+There are two electrodes connected to the bomb. They create a spark, which  ignites the fuel and starts combustion.
+So when the fuel burns, energy is released. What happens to that energy?
+The energy comes out as heat. Because the system is closed, the heat cannot escape. Instead, it goes into the water around the bomb.
+Why is the water important?
+The water absorbs the heat. There is also a stirrer in the lid that moves the water, so the heat spreads evenly.
+That makes sense. How do scientists measure the heat?
+There is a temperature probe placed in the water. As the fuel burns, the water temperature increases, and the probe measures this change.
+Is oxygen needed for this process?
+Yes. Combustion cannot happen without oxygen. Oxygen is added from a tank connected to the calorimeter.
+So in the end, what information do scientists get?
+They learn how much energy the fuel releases. This helps them compare fuels, like biodiesel and petroleum-based fuels such as octane.
+So for our listeners, this tool helps scientists understand which fuels give more energy.
+Exactly. It’s a simple idea, but very powerful in science and energy research.
+Let’s do a quick recap.
+We talked about a bomb calorimeter, a tool used to measure energy as heat. A fuel sample is burned in a closed system, heat warms the water, and scientists measure the temperature change to calculate energy. This helps compare different fuels.
+Now let’s review some key vocabulary.
+Repeat after me.
+bomb calorimeter
+&lt;break time="1s" /&gt;
+bomb calorimeter
+&lt;break time="1s" /&gt;
+bomb calorimeter
+&lt;break time="1s" /&gt; 
+Nice! a bomb calorimeter is a device used to measure energy by burning a sample.
+&lt;break time="1s" /&gt;
+Next
+&lt;break time="1s" /&gt;
+energy
+&lt;break time="1s" /&gt;
+energy
+&lt;break time="1s" /&gt;
+energy
+&lt;break time="1s" /&gt; 
+Wonderful! energy is the ability to do work or produce heat.
+&lt;break time="1s" /&gt;
+Next
+&lt;break time="1s" /&gt;
+combustion
+&lt;break time="1s" /&gt;
+combustion
+&lt;break time="1s" /&gt;
+combustion
+Good job! combustion is the process of burning with oxygen.
+&lt;break time="1s" /&gt;
+Next
+&lt;break time="1s" /&gt;
+temperature
+&lt;break time="1s" /&gt;
+temperature
+&lt;break time="1s" /&gt;
+temperature
+&lt;break time="1s" /&gt; 
+Great! temperature shows how hot or cold something is.
+&lt;break time="1s" /&gt;
+Next
+&lt;break time="1s" /&gt;
+fuel
+&lt;break time="1s" /&gt;
+fuel
+&lt;break time="1s" /&gt;
+fuel
+&lt;break time="1s" /&gt; 
+Well done! fuel is a material that is burned to produce energy.
+Thanks for listening and learning with us today. We hope this episode helped you understand both the science and the English a little better. Keep practicing, stay curious, and remember that learning happens step by step.
+That’s the end of the video! I’m Bel — like and subscribe for Better English Learning!</t>
+  </si>
 </sst>
 </file>
 
@@ -4177,7 +4141,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -4186,7 +4150,6 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -4492,15 +4455,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H541"/>
+  <dimension ref="A1:G541"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="4" max="4" width="16.7109375" customWidth="1"/>
-    <col min="5" max="5" width="27.28515625" customWidth="1"/>
-    <col min="6" max="6" width="21.42578125" customWidth="1"/>
+    <col min="2" max="2" width="24" customWidth="1"/>
+    <col min="3" max="3" width="113" customWidth="1"/>
+    <col min="4" max="4" width="27.28515625" customWidth="1"/>
+    <col min="5" max="5" width="21.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4508,19 +4472,16 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1086</v>
+        <v>1084</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>1082</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>1083</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>1087</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -4531,16 +4492,13 @@
         <v>542</v>
       </c>
       <c r="D2" t="s">
-        <v>1085</v>
+        <v>1083</v>
       </c>
       <c r="E2" t="s">
-        <v>1084</v>
-      </c>
-      <c r="F2" t="s">
-        <v>1088</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+        <v>1086</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -4550,14 +4508,14 @@
       <c r="C3" t="s">
         <v>543</v>
       </c>
-      <c r="F3" t="s">
-        <v>1089</v>
-      </c>
-      <c r="H3" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E3" t="s">
+        <v>1087</v>
+      </c>
+      <c r="G3" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -4568,16 +4526,13 @@
         <v>544</v>
       </c>
       <c r="D4" t="s">
-        <v>1090</v>
-      </c>
-      <c r="E4" t="s">
-        <v>1091</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>1096</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+        <v>1088</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -4588,16 +4543,13 @@
         <v>545</v>
       </c>
       <c r="D5" t="s">
-        <v>1093</v>
+        <v>1090</v>
       </c>
       <c r="E5" t="s">
-        <v>1094</v>
-      </c>
-      <c r="F5" t="s">
-        <v>1095</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+        <v>1091</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -4607,17 +4559,14 @@
       <c r="C6" t="s">
         <v>546</v>
       </c>
-      <c r="D6" s="4" t="s">
-        <v>1097</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>1099</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>1098</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D6" t="s">
+        <v>1094</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>1093</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -4627,11 +4576,11 @@
       <c r="C7" t="s">
         <v>547</v>
       </c>
-      <c r="E7" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D7" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -4641,11 +4590,11 @@
       <c r="C8" t="s">
         <v>548</v>
       </c>
-      <c r="E8" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D8" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -4655,11 +4604,11 @@
       <c r="C9" t="s">
         <v>549</v>
       </c>
-      <c r="E9" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D9" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -4669,11 +4618,11 @@
       <c r="C10" t="s">
         <v>550</v>
       </c>
-      <c r="E10" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D10" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
@@ -4683,11 +4632,11 @@
       <c r="C11" t="s">
         <v>551</v>
       </c>
-      <c r="E11" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D11" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
@@ -4697,11 +4646,11 @@
       <c r="C12" t="s">
         <v>552</v>
       </c>
-      <c r="E12" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D12" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
@@ -4711,11 +4660,11 @@
       <c r="C13" t="s">
         <v>553</v>
       </c>
-      <c r="E13" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D13" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
@@ -4725,11 +4674,14 @@
       <c r="C14" t="s">
         <v>554</v>
       </c>
+      <c r="D14" t="s">
+        <v>1096</v>
+      </c>
       <c r="E14" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
@@ -4739,11 +4691,11 @@
       <c r="C15" t="s">
         <v>555</v>
       </c>
-      <c r="E15" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D15" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
@@ -4753,11 +4705,11 @@
       <c r="C16" t="s">
         <v>556</v>
       </c>
-      <c r="E16" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D16" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
@@ -4767,11 +4719,11 @@
       <c r="C17" t="s">
         <v>557</v>
       </c>
-      <c r="E17" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D17" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
@@ -4781,11 +4733,11 @@
       <c r="C18" t="s">
         <v>558</v>
       </c>
-      <c r="E18" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D18" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
@@ -4795,11 +4747,11 @@
       <c r="C19" t="s">
         <v>559</v>
       </c>
-      <c r="E19" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D19" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
@@ -4809,11 +4761,11 @@
       <c r="C20" t="s">
         <v>560</v>
       </c>
-      <c r="E20" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D20" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
@@ -4823,11 +4775,11 @@
       <c r="C21" t="s">
         <v>561</v>
       </c>
-      <c r="E21" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D21" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21</v>
       </c>
@@ -4837,11 +4789,11 @@
       <c r="C22" t="s">
         <v>562</v>
       </c>
-      <c r="E22" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D22" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>22</v>
       </c>
@@ -4851,11 +4803,11 @@
       <c r="C23" t="s">
         <v>563</v>
       </c>
-      <c r="E23" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D23" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>23</v>
       </c>
@@ -4865,11 +4817,11 @@
       <c r="C24" t="s">
         <v>564</v>
       </c>
-      <c r="E24" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D24" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>24</v>
       </c>
@@ -4879,11 +4831,11 @@
       <c r="C25" t="s">
         <v>565</v>
       </c>
-      <c r="E25" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D25" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25</v>
       </c>
@@ -4893,11 +4845,11 @@
       <c r="C26" t="s">
         <v>566</v>
       </c>
-      <c r="E26" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D26" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26</v>
       </c>
@@ -4907,11 +4859,11 @@
       <c r="C27" t="s">
         <v>567</v>
       </c>
-      <c r="E27" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D27" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>27</v>
       </c>
@@ -4921,11 +4873,11 @@
       <c r="C28" t="s">
         <v>568</v>
       </c>
-      <c r="E28" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D28" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>28</v>
       </c>
@@ -4935,11 +4887,11 @@
       <c r="C29" t="s">
         <v>569</v>
       </c>
-      <c r="E29" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D29" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>29</v>
       </c>
@@ -4949,11 +4901,11 @@
       <c r="C30" t="s">
         <v>570</v>
       </c>
-      <c r="E30" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D30" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>30</v>
       </c>
@@ -4963,11 +4915,11 @@
       <c r="C31" t="s">
         <v>571</v>
       </c>
-      <c r="E31" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D31" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>31</v>
       </c>
@@ -4977,11 +4929,11 @@
       <c r="C32" t="s">
         <v>572</v>
       </c>
-      <c r="E32" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D32" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>32</v>
       </c>
@@ -4991,11 +4943,11 @@
       <c r="C33" t="s">
         <v>573</v>
       </c>
-      <c r="E33" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D33" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>33</v>
       </c>
@@ -5005,11 +4957,11 @@
       <c r="C34" t="s">
         <v>574</v>
       </c>
-      <c r="E34" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D34" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>34</v>
       </c>
@@ -5019,11 +4971,11 @@
       <c r="C35" t="s">
         <v>575</v>
       </c>
-      <c r="E35" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D35" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>35</v>
       </c>
@@ -5033,11 +4985,11 @@
       <c r="C36" t="s">
         <v>576</v>
       </c>
-      <c r="E36" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D36" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>36</v>
       </c>
@@ -5047,11 +4999,11 @@
       <c r="C37" t="s">
         <v>577</v>
       </c>
-      <c r="E37" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D37" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>37</v>
       </c>
@@ -5061,11 +5013,11 @@
       <c r="C38" t="s">
         <v>578</v>
       </c>
-      <c r="E38" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D38" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>38</v>
       </c>
@@ -5075,11 +5027,11 @@
       <c r="C39" t="s">
         <v>579</v>
       </c>
-      <c r="E39" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D39" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>39</v>
       </c>
@@ -5089,11 +5041,11 @@
       <c r="C40" t="s">
         <v>580</v>
       </c>
-      <c r="E40" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D40" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>40</v>
       </c>
@@ -5103,11 +5055,11 @@
       <c r="C41" t="s">
         <v>581</v>
       </c>
-      <c r="E41" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D41" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>41</v>
       </c>
@@ -5117,11 +5069,11 @@
       <c r="C42" t="s">
         <v>582</v>
       </c>
-      <c r="E42" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D42" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>42</v>
       </c>
@@ -5131,11 +5083,11 @@
       <c r="C43" t="s">
         <v>583</v>
       </c>
-      <c r="E43" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D43" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>43</v>
       </c>
@@ -5145,11 +5097,11 @@
       <c r="C44" t="s">
         <v>584</v>
       </c>
-      <c r="E44" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D44" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>44</v>
       </c>
@@ -5159,11 +5111,11 @@
       <c r="C45" t="s">
         <v>585</v>
       </c>
-      <c r="E45" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D45" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>45</v>
       </c>
@@ -5173,11 +5125,11 @@
       <c r="C46" t="s">
         <v>586</v>
       </c>
-      <c r="E46" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D46" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>46</v>
       </c>
@@ -5187,11 +5139,11 @@
       <c r="C47" t="s">
         <v>587</v>
       </c>
-      <c r="E47" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D47" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>47</v>
       </c>
@@ -5201,8 +5153,8 @@
       <c r="C48" t="s">
         <v>588</v>
       </c>
-      <c r="E48" t="s">
-        <v>1092</v>
+      <c r="D48" t="s">
+        <v>1089</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
@@ -5215,8 +5167,8 @@
       <c r="C49" t="s">
         <v>589</v>
       </c>
-      <c r="E49" t="s">
-        <v>1092</v>
+      <c r="D49" t="s">
+        <v>1089</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
@@ -5229,8 +5181,8 @@
       <c r="C50" t="s">
         <v>590</v>
       </c>
-      <c r="E50" t="s">
-        <v>1092</v>
+      <c r="D50" t="s">
+        <v>1089</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
@@ -5243,8 +5195,8 @@
       <c r="C51" t="s">
         <v>591</v>
       </c>
-      <c r="E51" t="s">
-        <v>1092</v>
+      <c r="D51" t="s">
+        <v>1089</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
@@ -5257,8 +5209,8 @@
       <c r="C52" t="s">
         <v>592</v>
       </c>
-      <c r="E52" t="s">
-        <v>1092</v>
+      <c r="D52" t="s">
+        <v>1089</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
@@ -5271,8 +5223,8 @@
       <c r="C53" t="s">
         <v>593</v>
       </c>
-      <c r="E53" t="s">
-        <v>1092</v>
+      <c r="D53" t="s">
+        <v>1089</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
@@ -5285,8 +5237,8 @@
       <c r="C54" t="s">
         <v>594</v>
       </c>
-      <c r="E54" t="s">
-        <v>1092</v>
+      <c r="D54" t="s">
+        <v>1089</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
@@ -5299,8 +5251,8 @@
       <c r="C55" t="s">
         <v>595</v>
       </c>
-      <c r="E55" t="s">
-        <v>1092</v>
+      <c r="D55" t="s">
+        <v>1089</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
@@ -5313,8 +5265,8 @@
       <c r="C56" t="s">
         <v>596</v>
       </c>
-      <c r="E56" t="s">
-        <v>1092</v>
+      <c r="D56" t="s">
+        <v>1089</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
@@ -5327,8 +5279,8 @@
       <c r="C57" t="s">
         <v>597</v>
       </c>
-      <c r="E57" t="s">
-        <v>1092</v>
+      <c r="D57" t="s">
+        <v>1089</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
@@ -5341,8 +5293,8 @@
       <c r="C58" t="s">
         <v>598</v>
       </c>
-      <c r="E58" t="s">
-        <v>1092</v>
+      <c r="D58" t="s">
+        <v>1089</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
@@ -5355,8 +5307,8 @@
       <c r="C59" t="s">
         <v>599</v>
       </c>
-      <c r="E59" t="s">
-        <v>1092</v>
+      <c r="D59" t="s">
+        <v>1089</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
@@ -5369,8 +5321,8 @@
       <c r="C60" t="s">
         <v>600</v>
       </c>
-      <c r="E60" t="s">
-        <v>1092</v>
+      <c r="D60" t="s">
+        <v>1089</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
@@ -5383,8 +5335,8 @@
       <c r="C61" t="s">
         <v>601</v>
       </c>
-      <c r="E61" t="s">
-        <v>1092</v>
+      <c r="D61" t="s">
+        <v>1089</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
@@ -5398,7 +5350,7 @@
         <v>602</v>
       </c>
       <c r="E62" t="s">
-        <v>1092</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
@@ -5411,8 +5363,8 @@
       <c r="C63" t="s">
         <v>603</v>
       </c>
-      <c r="E63" t="s">
-        <v>1092</v>
+      <c r="D63" t="s">
+        <v>1089</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
@@ -5425,8 +5377,8 @@
       <c r="C64" t="s">
         <v>604</v>
       </c>
-      <c r="E64" t="s">
-        <v>1092</v>
+      <c r="D64" t="s">
+        <v>1089</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
@@ -5439,8 +5391,8 @@
       <c r="C65" t="s">
         <v>605</v>
       </c>
-      <c r="E65" t="s">
-        <v>1092</v>
+      <c r="D65" t="s">
+        <v>1089</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
@@ -5453,8 +5405,8 @@
       <c r="C66" t="s">
         <v>606</v>
       </c>
-      <c r="E66" t="s">
-        <v>1092</v>
+      <c r="D66" t="s">
+        <v>1089</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
@@ -5467,8 +5419,8 @@
       <c r="C67" t="s">
         <v>607</v>
       </c>
-      <c r="E67" t="s">
-        <v>1092</v>
+      <c r="D67" t="s">
+        <v>1089</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
@@ -5481,8 +5433,8 @@
       <c r="C68" t="s">
         <v>608</v>
       </c>
-      <c r="E68" t="s">
-        <v>1092</v>
+      <c r="D68" t="s">
+        <v>1089</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
@@ -5495,8 +5447,8 @@
       <c r="C69" t="s">
         <v>609</v>
       </c>
-      <c r="E69" t="s">
-        <v>1092</v>
+      <c r="D69" t="s">
+        <v>1089</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
@@ -5509,8 +5461,8 @@
       <c r="C70" t="s">
         <v>610</v>
       </c>
-      <c r="E70" t="s">
-        <v>1092</v>
+      <c r="D70" t="s">
+        <v>1089</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
@@ -5523,8 +5475,8 @@
       <c r="C71" t="s">
         <v>611</v>
       </c>
-      <c r="E71" t="s">
-        <v>1092</v>
+      <c r="D71" t="s">
+        <v>1089</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
@@ -5537,8 +5489,11 @@
       <c r="C72" t="s">
         <v>612</v>
       </c>
+      <c r="D72" t="s">
+        <v>1099</v>
+      </c>
       <c r="E72" t="s">
-        <v>1092</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
@@ -5551,8 +5506,8 @@
       <c r="C73" t="s">
         <v>613</v>
       </c>
-      <c r="E73" t="s">
-        <v>1092</v>
+      <c r="D73" t="s">
+        <v>1089</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
@@ -5565,8 +5520,8 @@
       <c r="C74" t="s">
         <v>614</v>
       </c>
-      <c r="E74" t="s">
-        <v>1092</v>
+      <c r="D74" t="s">
+        <v>1089</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
@@ -5579,8 +5534,8 @@
       <c r="C75" t="s">
         <v>615</v>
       </c>
-      <c r="E75" t="s">
-        <v>1092</v>
+      <c r="D75" t="s">
+        <v>1089</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
@@ -5593,8 +5548,8 @@
       <c r="C76" t="s">
         <v>616</v>
       </c>
-      <c r="E76" t="s">
-        <v>1092</v>
+      <c r="D76" t="s">
+        <v>1089</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
@@ -5607,8 +5562,8 @@
       <c r="C77" t="s">
         <v>617</v>
       </c>
-      <c r="E77" t="s">
-        <v>1092</v>
+      <c r="D77" t="s">
+        <v>1089</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
@@ -5621,8 +5576,8 @@
       <c r="C78" t="s">
         <v>618</v>
       </c>
-      <c r="E78" t="s">
-        <v>1092</v>
+      <c r="D78" t="s">
+        <v>1089</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
@@ -5635,8 +5590,8 @@
       <c r="C79" t="s">
         <v>619</v>
       </c>
-      <c r="E79" t="s">
-        <v>1092</v>
+      <c r="D79" t="s">
+        <v>1089</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
@@ -5649,11 +5604,11 @@
       <c r="C80" t="s">
         <v>620</v>
       </c>
-      <c r="E80" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D80" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>81</v>
       </c>
@@ -5663,11 +5618,11 @@
       <c r="C81" t="s">
         <v>621</v>
       </c>
-      <c r="E81" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D81" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>82</v>
       </c>
@@ -5677,11 +5632,11 @@
       <c r="C82" t="s">
         <v>622</v>
       </c>
-      <c r="E82" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D82" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>83</v>
       </c>
@@ -5691,11 +5646,11 @@
       <c r="C83" t="s">
         <v>623</v>
       </c>
-      <c r="E83" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D83" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>84</v>
       </c>
@@ -5705,11 +5660,11 @@
       <c r="C84" t="s">
         <v>624</v>
       </c>
-      <c r="E84" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D84" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>85</v>
       </c>
@@ -5719,11 +5674,11 @@
       <c r="C85" t="s">
         <v>625</v>
       </c>
-      <c r="E85" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D85" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>86</v>
       </c>
@@ -5733,11 +5688,11 @@
       <c r="C86" t="s">
         <v>626</v>
       </c>
-      <c r="E86" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D86" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>87</v>
       </c>
@@ -5747,11 +5702,11 @@
       <c r="C87" t="s">
         <v>627</v>
       </c>
-      <c r="E87" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D87" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>88</v>
       </c>
@@ -5761,11 +5716,11 @@
       <c r="C88" t="s">
         <v>628</v>
       </c>
-      <c r="E88" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D88" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>89</v>
       </c>
@@ -5775,11 +5730,11 @@
       <c r="C89" t="s">
         <v>629</v>
       </c>
-      <c r="E89" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D89" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>90</v>
       </c>
@@ -5789,11 +5744,11 @@
       <c r="C90" t="s">
         <v>630</v>
       </c>
-      <c r="E90" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D90" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>91</v>
       </c>
@@ -5803,11 +5758,11 @@
       <c r="C91" t="s">
         <v>631</v>
       </c>
-      <c r="E91" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D91" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>92</v>
       </c>
@@ -5817,11 +5772,11 @@
       <c r="C92" t="s">
         <v>632</v>
       </c>
-      <c r="E92" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D92" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>93</v>
       </c>
@@ -5831,11 +5786,11 @@
       <c r="C93" t="s">
         <v>633</v>
       </c>
-      <c r="E93" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D93" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>94</v>
       </c>
@@ -5845,11 +5800,11 @@
       <c r="C94" t="s">
         <v>634</v>
       </c>
-      <c r="E94" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D94" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>95</v>
       </c>
@@ -5859,11 +5814,11 @@
       <c r="C95" t="s">
         <v>635</v>
       </c>
-      <c r="E95" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D95" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>96</v>
       </c>
@@ -5873,11 +5828,11 @@
       <c r="C96" t="s">
         <v>636</v>
       </c>
-      <c r="E96" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D96" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>97</v>
       </c>
@@ -5887,11 +5842,11 @@
       <c r="C97" t="s">
         <v>637</v>
       </c>
-      <c r="E97" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D97" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>98</v>
       </c>
@@ -5901,11 +5856,11 @@
       <c r="C98" t="s">
         <v>638</v>
       </c>
-      <c r="E98" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D98" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>99</v>
       </c>
@@ -5915,11 +5870,11 @@
       <c r="C99" t="s">
         <v>639</v>
       </c>
-      <c r="E99" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D99" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>100</v>
       </c>
@@ -5929,11 +5884,11 @@
       <c r="C100" t="s">
         <v>640</v>
       </c>
-      <c r="E100" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D100" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>101</v>
       </c>
@@ -5943,11 +5898,11 @@
       <c r="C101" t="s">
         <v>641</v>
       </c>
-      <c r="E101" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D101" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A102">
         <v>102</v>
       </c>
@@ -5957,11 +5912,11 @@
       <c r="C102" t="s">
         <v>642</v>
       </c>
-      <c r="E102" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D102" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>103</v>
       </c>
@@ -5971,11 +5926,11 @@
       <c r="C103" t="s">
         <v>643</v>
       </c>
-      <c r="E103" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D103" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>104</v>
       </c>
@@ -5985,11 +5940,11 @@
       <c r="C104" t="s">
         <v>644</v>
       </c>
-      <c r="E104" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D104" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>105</v>
       </c>
@@ -5999,11 +5954,11 @@
       <c r="C105" t="s">
         <v>645</v>
       </c>
-      <c r="E105" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D105" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A106">
         <v>106</v>
       </c>
@@ -6013,11 +5968,11 @@
       <c r="C106" t="s">
         <v>646</v>
       </c>
-      <c r="E106" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D106" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A107">
         <v>107</v>
       </c>
@@ -6027,11 +5982,11 @@
       <c r="C107" t="s">
         <v>647</v>
       </c>
-      <c r="E107" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D107" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A108">
         <v>108</v>
       </c>
@@ -6041,11 +5996,11 @@
       <c r="C108" t="s">
         <v>648</v>
       </c>
-      <c r="E108" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D108" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A109">
         <v>109</v>
       </c>
@@ -6055,11 +6010,11 @@
       <c r="C109" t="s">
         <v>649</v>
       </c>
-      <c r="E109" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D109" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A110">
         <v>110</v>
       </c>
@@ -6069,11 +6024,11 @@
       <c r="C110" t="s">
         <v>650</v>
       </c>
-      <c r="E110" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D110" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A111">
         <v>111</v>
       </c>
@@ -6083,11 +6038,11 @@
       <c r="C111" t="s">
         <v>651</v>
       </c>
-      <c r="E111" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D111" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A112">
         <v>112</v>
       </c>
@@ -6097,11 +6052,11 @@
       <c r="C112" t="s">
         <v>652</v>
       </c>
-      <c r="E112" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D112" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A113">
         <v>113</v>
       </c>
@@ -6111,11 +6066,11 @@
       <c r="C113" t="s">
         <v>653</v>
       </c>
-      <c r="E113" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D113" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A114">
         <v>114</v>
       </c>
@@ -6125,11 +6080,11 @@
       <c r="C114" t="s">
         <v>654</v>
       </c>
-      <c r="E114" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D114" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A115">
         <v>115</v>
       </c>
@@ -6139,11 +6094,11 @@
       <c r="C115" t="s">
         <v>655</v>
       </c>
-      <c r="E115" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D115" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A116">
         <v>116</v>
       </c>
@@ -6153,11 +6108,11 @@
       <c r="C116" t="s">
         <v>656</v>
       </c>
-      <c r="E116" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D116" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A117">
         <v>117</v>
       </c>
@@ -6167,11 +6122,11 @@
       <c r="C117" t="s">
         <v>657</v>
       </c>
-      <c r="E117" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D117" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A118">
         <v>118</v>
       </c>
@@ -6181,11 +6136,11 @@
       <c r="C118" t="s">
         <v>658</v>
       </c>
-      <c r="E118" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D118" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A119">
         <v>119</v>
       </c>
@@ -6195,11 +6150,11 @@
       <c r="C119" t="s">
         <v>659</v>
       </c>
-      <c r="E119" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D119" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A120">
         <v>120</v>
       </c>
@@ -6209,11 +6164,11 @@
       <c r="C120" t="s">
         <v>660</v>
       </c>
-      <c r="E120" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D120" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A121">
         <v>121</v>
       </c>
@@ -6223,11 +6178,11 @@
       <c r="C121" t="s">
         <v>661</v>
       </c>
-      <c r="E121" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D121" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A122">
         <v>122</v>
       </c>
@@ -6237,11 +6192,11 @@
       <c r="C122" t="s">
         <v>662</v>
       </c>
-      <c r="E122" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D122" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A123">
         <v>123</v>
       </c>
@@ -6251,11 +6206,11 @@
       <c r="C123" t="s">
         <v>663</v>
       </c>
-      <c r="E123" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D123" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A124">
         <v>124</v>
       </c>
@@ -6265,11 +6220,11 @@
       <c r="C124" t="s">
         <v>664</v>
       </c>
-      <c r="E124" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D124" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A125">
         <v>125</v>
       </c>
@@ -6279,11 +6234,11 @@
       <c r="C125" t="s">
         <v>665</v>
       </c>
-      <c r="E125" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D125" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A126">
         <v>126</v>
       </c>
@@ -6293,11 +6248,11 @@
       <c r="C126" t="s">
         <v>666</v>
       </c>
-      <c r="E126" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D126" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A127">
         <v>127</v>
       </c>
@@ -6307,11 +6262,11 @@
       <c r="C127" t="s">
         <v>667</v>
       </c>
-      <c r="E127" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D127" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A128">
         <v>128</v>
       </c>
@@ -6321,11 +6276,11 @@
       <c r="C128" t="s">
         <v>668</v>
       </c>
-      <c r="E128" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D128" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A129">
         <v>129</v>
       </c>
@@ -6335,11 +6290,11 @@
       <c r="C129" t="s">
         <v>669</v>
       </c>
-      <c r="E129" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D129" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A130">
         <v>130</v>
       </c>
@@ -6349,11 +6304,11 @@
       <c r="C130" t="s">
         <v>670</v>
       </c>
-      <c r="E130" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D130" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A131">
         <v>131</v>
       </c>
@@ -6363,11 +6318,11 @@
       <c r="C131" t="s">
         <v>671</v>
       </c>
-      <c r="E131" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D131" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A132">
         <v>132</v>
       </c>
@@ -6377,11 +6332,11 @@
       <c r="C132" t="s">
         <v>672</v>
       </c>
-      <c r="E132" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D132" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A133">
         <v>133</v>
       </c>
@@ -6391,11 +6346,11 @@
       <c r="C133" t="s">
         <v>673</v>
       </c>
-      <c r="E133" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D133" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A134">
         <v>134</v>
       </c>
@@ -6405,11 +6360,11 @@
       <c r="C134" t="s">
         <v>674</v>
       </c>
-      <c r="E134" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D134" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A135">
         <v>135</v>
       </c>
@@ -6419,11 +6374,11 @@
       <c r="C135" t="s">
         <v>675</v>
       </c>
-      <c r="E135" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D135" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A136">
         <v>136</v>
       </c>
@@ -6433,11 +6388,11 @@
       <c r="C136" t="s">
         <v>676</v>
       </c>
-      <c r="E136" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D136" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A137">
         <v>137</v>
       </c>
@@ -6447,11 +6402,11 @@
       <c r="C137" t="s">
         <v>677</v>
       </c>
-      <c r="E137" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D137" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A138">
         <v>138</v>
       </c>
@@ -6461,11 +6416,11 @@
       <c r="C138" t="s">
         <v>678</v>
       </c>
-      <c r="E138" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D138" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A139">
         <v>139</v>
       </c>
@@ -6475,11 +6430,11 @@
       <c r="C139" t="s">
         <v>679</v>
       </c>
-      <c r="E139" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D139" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="140" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A140">
         <v>140</v>
       </c>
@@ -6489,11 +6444,11 @@
       <c r="C140" t="s">
         <v>680</v>
       </c>
-      <c r="E140" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D140" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="141" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A141">
         <v>141</v>
       </c>
@@ -6503,11 +6458,11 @@
       <c r="C141" t="s">
         <v>681</v>
       </c>
-      <c r="E141" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D141" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A142">
         <v>142</v>
       </c>
@@ -6517,11 +6472,11 @@
       <c r="C142" t="s">
         <v>682</v>
       </c>
-      <c r="E142" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D142" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="143" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A143">
         <v>143</v>
       </c>
@@ -6531,11 +6486,11 @@
       <c r="C143" t="s">
         <v>683</v>
       </c>
-      <c r="E143" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D143" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A144">
         <v>144</v>
       </c>
@@ -6545,11 +6500,11 @@
       <c r="C144" t="s">
         <v>684</v>
       </c>
-      <c r="E144" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D144" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="145" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A145">
         <v>145</v>
       </c>
@@ -6559,11 +6514,11 @@
       <c r="C145" t="s">
         <v>685</v>
       </c>
-      <c r="E145" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D145" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="146" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A146">
         <v>146</v>
       </c>
@@ -6573,11 +6528,11 @@
       <c r="C146" t="s">
         <v>686</v>
       </c>
-      <c r="E146" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D146" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="147" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A147">
         <v>147</v>
       </c>
@@ -6587,11 +6542,11 @@
       <c r="C147" t="s">
         <v>687</v>
       </c>
-      <c r="E147" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D147" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="148" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A148">
         <v>148</v>
       </c>
@@ -6601,11 +6556,11 @@
       <c r="C148" t="s">
         <v>688</v>
       </c>
-      <c r="E148" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D148" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="149" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A149">
         <v>149</v>
       </c>
@@ -6615,11 +6570,11 @@
       <c r="C149" t="s">
         <v>689</v>
       </c>
-      <c r="E149" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D149" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="150" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A150">
         <v>150</v>
       </c>
@@ -6629,11 +6584,11 @@
       <c r="C150" t="s">
         <v>690</v>
       </c>
-      <c r="E150" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D150" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="151" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A151">
         <v>151</v>
       </c>
@@ -6643,11 +6598,11 @@
       <c r="C151" t="s">
         <v>691</v>
       </c>
-      <c r="E151" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D151" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="152" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A152">
         <v>152</v>
       </c>
@@ -6657,11 +6612,11 @@
       <c r="C152" t="s">
         <v>692</v>
       </c>
-      <c r="E152" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D152" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="153" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A153">
         <v>153</v>
       </c>
@@ -6671,11 +6626,11 @@
       <c r="C153" t="s">
         <v>693</v>
       </c>
-      <c r="E153" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D153" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="154" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A154">
         <v>154</v>
       </c>
@@ -6685,11 +6640,11 @@
       <c r="C154" t="s">
         <v>694</v>
       </c>
-      <c r="E154" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D154" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="155" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A155">
         <v>155</v>
       </c>
@@ -6699,11 +6654,11 @@
       <c r="C155" t="s">
         <v>695</v>
       </c>
-      <c r="E155" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D155" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="156" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A156">
         <v>156</v>
       </c>
@@ -6713,11 +6668,11 @@
       <c r="C156" t="s">
         <v>696</v>
       </c>
-      <c r="E156" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="157" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D156" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="157" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A157">
         <v>157</v>
       </c>
@@ -6727,11 +6682,11 @@
       <c r="C157" t="s">
         <v>697</v>
       </c>
-      <c r="E157" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="158" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D157" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="158" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A158">
         <v>159</v>
       </c>
@@ -6741,11 +6696,11 @@
       <c r="C158" t="s">
         <v>698</v>
       </c>
-      <c r="E158" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="159" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D158" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="159" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A159">
         <v>160</v>
       </c>
@@ -6755,11 +6710,11 @@
       <c r="C159" t="s">
         <v>699</v>
       </c>
-      <c r="E159" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="160" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D159" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="160" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A160">
         <v>161</v>
       </c>
@@ -6769,11 +6724,11 @@
       <c r="C160" t="s">
         <v>700</v>
       </c>
-      <c r="E160" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="161" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D160" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="161" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A161">
         <v>162</v>
       </c>
@@ -6783,11 +6738,11 @@
       <c r="C161" t="s">
         <v>701</v>
       </c>
-      <c r="E161" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="162" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D161" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="162" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A162">
         <v>163</v>
       </c>
@@ -6797,11 +6752,11 @@
       <c r="C162" t="s">
         <v>702</v>
       </c>
-      <c r="E162" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="163" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D162" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="163" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A163">
         <v>164</v>
       </c>
@@ -6811,11 +6766,11 @@
       <c r="C163" t="s">
         <v>703</v>
       </c>
-      <c r="E163" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="164" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D163" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="164" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A164">
         <v>165</v>
       </c>
@@ -6825,11 +6780,11 @@
       <c r="C164" t="s">
         <v>704</v>
       </c>
-      <c r="E164" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="165" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D164" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="165" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A165">
         <v>166</v>
       </c>
@@ -6839,11 +6794,11 @@
       <c r="C165" t="s">
         <v>705</v>
       </c>
-      <c r="E165" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="166" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D165" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="166" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A166">
         <v>167</v>
       </c>
@@ -6853,11 +6808,11 @@
       <c r="C166" t="s">
         <v>706</v>
       </c>
-      <c r="E166" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="167" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D166" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="167" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A167">
         <v>168</v>
       </c>
@@ -6867,11 +6822,11 @@
       <c r="C167" t="s">
         <v>707</v>
       </c>
-      <c r="E167" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="168" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D167" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="168" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A168">
         <v>169</v>
       </c>
@@ -6881,11 +6836,11 @@
       <c r="C168" t="s">
         <v>708</v>
       </c>
-      <c r="E168" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="169" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D168" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="169" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A169">
         <v>170</v>
       </c>
@@ -6895,11 +6850,11 @@
       <c r="C169" t="s">
         <v>709</v>
       </c>
-      <c r="E169" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="170" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D169" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="170" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A170">
         <v>171</v>
       </c>
@@ -6909,11 +6864,11 @@
       <c r="C170" t="s">
         <v>710</v>
       </c>
-      <c r="E170" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="171" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D170" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="171" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A171">
         <v>172</v>
       </c>
@@ -6923,11 +6878,11 @@
       <c r="C171" t="s">
         <v>711</v>
       </c>
-      <c r="E171" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="172" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D171" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="172" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A172">
         <v>173</v>
       </c>
@@ -6937,11 +6892,11 @@
       <c r="C172" t="s">
         <v>712</v>
       </c>
-      <c r="E172" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="173" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D172" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="173" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A173">
         <v>174</v>
       </c>
@@ -6951,11 +6906,11 @@
       <c r="C173" t="s">
         <v>713</v>
       </c>
-      <c r="E173" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="174" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D173" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="174" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A174">
         <v>175</v>
       </c>
@@ -6965,11 +6920,11 @@
       <c r="C174" t="s">
         <v>714</v>
       </c>
-      <c r="E174" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="175" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D174" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="175" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A175">
         <v>180</v>
       </c>
@@ -6979,11 +6934,11 @@
       <c r="C175" t="s">
         <v>715</v>
       </c>
-      <c r="E175" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="176" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D175" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="176" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A176">
         <v>181</v>
       </c>
@@ -6993,11 +6948,11 @@
       <c r="C176" t="s">
         <v>716</v>
       </c>
-      <c r="E176" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="177" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D176" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="177" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A177">
         <v>182</v>
       </c>
@@ -7007,11 +6962,11 @@
       <c r="C177" t="s">
         <v>717</v>
       </c>
-      <c r="E177" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="178" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D177" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="178" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A178">
         <v>183</v>
       </c>
@@ -7021,11 +6976,11 @@
       <c r="C178" t="s">
         <v>718</v>
       </c>
-      <c r="E178" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="179" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D178" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="179" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A179">
         <v>184</v>
       </c>
@@ -7035,11 +6990,11 @@
       <c r="C179" t="s">
         <v>719</v>
       </c>
-      <c r="E179" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="180" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D179" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="180" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A180">
         <v>185</v>
       </c>
@@ -7049,11 +7004,11 @@
       <c r="C180" t="s">
         <v>720</v>
       </c>
-      <c r="E180" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="181" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D180" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="181" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A181">
         <v>186</v>
       </c>
@@ -7063,11 +7018,11 @@
       <c r="C181" t="s">
         <v>721</v>
       </c>
-      <c r="E181" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="182" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D181" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="182" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A182">
         <v>188</v>
       </c>
@@ -7077,11 +7032,11 @@
       <c r="C182" t="s">
         <v>722</v>
       </c>
-      <c r="E182" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="183" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D182" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="183" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A183">
         <v>189</v>
       </c>
@@ -7091,11 +7046,11 @@
       <c r="C183" t="s">
         <v>723</v>
       </c>
-      <c r="E183" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="184" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D183" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="184" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A184">
         <v>191</v>
       </c>
@@ -7105,11 +7060,11 @@
       <c r="C184" t="s">
         <v>724</v>
       </c>
-      <c r="E184" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="185" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D184" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="185" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A185">
         <v>192</v>
       </c>
@@ -7119,11 +7074,11 @@
       <c r="C185" t="s">
         <v>725</v>
       </c>
-      <c r="E185" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="186" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D185" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="186" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A186">
         <v>193</v>
       </c>
@@ -7133,11 +7088,11 @@
       <c r="C186" t="s">
         <v>726</v>
       </c>
-      <c r="E186" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="187" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D186" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="187" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A187">
         <v>194</v>
       </c>
@@ -7147,11 +7102,11 @@
       <c r="C187" t="s">
         <v>727</v>
       </c>
-      <c r="E187" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="188" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D187" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="188" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A188">
         <v>199</v>
       </c>
@@ -7161,11 +7116,11 @@
       <c r="C188" t="s">
         <v>728</v>
       </c>
-      <c r="E188" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="189" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D188" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="189" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A189">
         <v>200</v>
       </c>
@@ -7175,11 +7130,11 @@
       <c r="C189" t="s">
         <v>729</v>
       </c>
-      <c r="E189" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="190" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D189" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="190" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A190">
         <v>203</v>
       </c>
@@ -7189,11 +7144,11 @@
       <c r="C190" t="s">
         <v>730</v>
       </c>
-      <c r="E190" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="191" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D190" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="191" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A191">
         <v>216</v>
       </c>
@@ -7203,11 +7158,11 @@
       <c r="C191" t="s">
         <v>731</v>
       </c>
-      <c r="E191" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="192" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D191" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="192" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A192">
         <v>217</v>
       </c>
@@ -7217,11 +7172,11 @@
       <c r="C192" t="s">
         <v>732</v>
       </c>
-      <c r="E192" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="193" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D192" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="193" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A193">
         <v>223</v>
       </c>
@@ -7231,11 +7186,11 @@
       <c r="C193" t="s">
         <v>733</v>
       </c>
-      <c r="E193" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="194" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D193" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="194" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A194">
         <v>229</v>
       </c>
@@ -7245,11 +7200,11 @@
       <c r="C194" t="s">
         <v>734</v>
       </c>
-      <c r="E194" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="195" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D194" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="195" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A195">
         <v>230</v>
       </c>
@@ -7259,11 +7214,11 @@
       <c r="C195" t="s">
         <v>735</v>
       </c>
-      <c r="E195" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="196" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D195" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="196" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A196">
         <v>232</v>
       </c>
@@ -7273,11 +7228,11 @@
       <c r="C196" t="s">
         <v>736</v>
       </c>
-      <c r="E196" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="197" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D196" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="197" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A197">
         <v>233</v>
       </c>
@@ -7287,11 +7242,11 @@
       <c r="C197" t="s">
         <v>737</v>
       </c>
-      <c r="E197" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="198" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D197" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="198" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A198">
         <v>234</v>
       </c>
@@ -7301,11 +7256,11 @@
       <c r="C198" t="s">
         <v>738</v>
       </c>
-      <c r="E198" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="199" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D198" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="199" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A199">
         <v>235</v>
       </c>
@@ -7315,11 +7270,11 @@
       <c r="C199" t="s">
         <v>739</v>
       </c>
-      <c r="E199" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="200" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D199" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="200" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A200">
         <v>237</v>
       </c>
@@ -7329,11 +7284,11 @@
       <c r="C200" t="s">
         <v>740</v>
       </c>
-      <c r="E200" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="201" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D200" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="201" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A201">
         <v>238</v>
       </c>
@@ -7343,11 +7298,11 @@
       <c r="C201" t="s">
         <v>741</v>
       </c>
-      <c r="E201" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="202" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D201" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="202" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A202">
         <v>240</v>
       </c>
@@ -7357,11 +7312,11 @@
       <c r="C202" t="s">
         <v>742</v>
       </c>
-      <c r="E202" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="203" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D202" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="203" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A203">
         <v>242</v>
       </c>
@@ -7371,11 +7326,11 @@
       <c r="C203" t="s">
         <v>743</v>
       </c>
-      <c r="E203" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="204" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D203" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="204" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A204">
         <v>243</v>
       </c>
@@ -7385,11 +7340,11 @@
       <c r="C204" t="s">
         <v>744</v>
       </c>
-      <c r="E204" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="205" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D204" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="205" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A205">
         <v>244</v>
       </c>
@@ -7399,11 +7354,11 @@
       <c r="C205" t="s">
         <v>745</v>
       </c>
-      <c r="E205" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="206" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D205" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="206" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A206">
         <v>245</v>
       </c>
@@ -7413,11 +7368,11 @@
       <c r="C206" t="s">
         <v>746</v>
       </c>
-      <c r="E206" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="207" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D206" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="207" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A207">
         <v>247</v>
       </c>
@@ -7427,11 +7382,11 @@
       <c r="C207" t="s">
         <v>747</v>
       </c>
-      <c r="E207" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="208" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D207" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="208" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A208">
         <v>248</v>
       </c>
@@ -7441,11 +7396,11 @@
       <c r="C208" t="s">
         <v>748</v>
       </c>
-      <c r="E208" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="209" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D208" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="209" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A209">
         <v>249</v>
       </c>
@@ -7455,11 +7410,11 @@
       <c r="C209" t="s">
         <v>749</v>
       </c>
-      <c r="E209" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="210" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D209" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="210" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A210">
         <v>250</v>
       </c>
@@ -7469,11 +7424,11 @@
       <c r="C210" t="s">
         <v>750</v>
       </c>
-      <c r="E210" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="211" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D210" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="211" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A211">
         <v>252</v>
       </c>
@@ -7483,11 +7438,11 @@
       <c r="C211" t="s">
         <v>751</v>
       </c>
-      <c r="E211" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="212" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D211" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="212" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A212">
         <v>253</v>
       </c>
@@ -7497,11 +7452,11 @@
       <c r="C212" t="s">
         <v>752</v>
       </c>
-      <c r="E212" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="213" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D212" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="213" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A213">
         <v>254</v>
       </c>
@@ -7511,11 +7466,11 @@
       <c r="C213" t="s">
         <v>753</v>
       </c>
-      <c r="E213" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="214" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D213" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="214" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A214">
         <v>256</v>
       </c>
@@ -7525,11 +7480,11 @@
       <c r="C214" t="s">
         <v>754</v>
       </c>
-      <c r="E214" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="215" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D214" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="215" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A215">
         <v>257</v>
       </c>
@@ -7539,11 +7494,11 @@
       <c r="C215" t="s">
         <v>755</v>
       </c>
-      <c r="E215" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="216" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D215" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="216" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A216">
         <v>258</v>
       </c>
@@ -7553,11 +7508,11 @@
       <c r="C216" t="s">
         <v>756</v>
       </c>
-      <c r="E216" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="217" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D216" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="217" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A217">
         <v>259</v>
       </c>
@@ -7567,11 +7522,11 @@
       <c r="C217" t="s">
         <v>757</v>
       </c>
-      <c r="E217" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="218" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D217" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="218" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A218">
         <v>260</v>
       </c>
@@ -7581,11 +7536,11 @@
       <c r="C218" t="s">
         <v>758</v>
       </c>
-      <c r="E218" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="219" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D218" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="219" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A219">
         <v>261</v>
       </c>
@@ -7595,11 +7550,11 @@
       <c r="C219" t="s">
         <v>759</v>
       </c>
-      <c r="E219" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="220" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D219" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="220" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A220">
         <v>262</v>
       </c>
@@ -7609,11 +7564,11 @@
       <c r="C220" t="s">
         <v>760</v>
       </c>
-      <c r="E220" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="221" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D220" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="221" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A221">
         <v>263</v>
       </c>
@@ -7623,11 +7578,11 @@
       <c r="C221" t="s">
         <v>761</v>
       </c>
-      <c r="E221" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="222" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D221" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="222" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A222">
         <v>264</v>
       </c>
@@ -7637,11 +7592,11 @@
       <c r="C222" t="s">
         <v>762</v>
       </c>
-      <c r="E222" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="223" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D222" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="223" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A223">
         <v>265</v>
       </c>
@@ -7651,11 +7606,11 @@
       <c r="C223" t="s">
         <v>763</v>
       </c>
-      <c r="E223" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="224" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D223" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="224" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A224">
         <v>266</v>
       </c>
@@ -7665,11 +7620,11 @@
       <c r="C224" t="s">
         <v>764</v>
       </c>
-      <c r="E224" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="225" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D224" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="225" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A225">
         <v>268</v>
       </c>
@@ -7679,11 +7634,11 @@
       <c r="C225" t="s">
         <v>765</v>
       </c>
-      <c r="E225" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="226" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D225" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="226" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A226">
         <v>269</v>
       </c>
@@ -7693,11 +7648,11 @@
       <c r="C226" t="s">
         <v>766</v>
       </c>
-      <c r="E226" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="227" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D226" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="227" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A227">
         <v>270</v>
       </c>
@@ -7707,11 +7662,11 @@
       <c r="C227" t="s">
         <v>767</v>
       </c>
-      <c r="E227" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="228" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D227" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="228" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A228">
         <v>271</v>
       </c>
@@ -7721,11 +7676,11 @@
       <c r="C228" t="s">
         <v>768</v>
       </c>
-      <c r="E228" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="229" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D228" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="229" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A229">
         <v>272</v>
       </c>
@@ -7735,11 +7690,11 @@
       <c r="C229" t="s">
         <v>769</v>
       </c>
-      <c r="E229" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="230" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D229" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="230" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A230">
         <v>273</v>
       </c>
@@ -7749,11 +7704,11 @@
       <c r="C230" t="s">
         <v>770</v>
       </c>
-      <c r="E230" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="231" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D230" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="231" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A231">
         <v>274</v>
       </c>
@@ -7763,11 +7718,11 @@
       <c r="C231" t="s">
         <v>771</v>
       </c>
-      <c r="E231" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="232" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D231" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="232" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A232">
         <v>276</v>
       </c>
@@ -7777,11 +7732,11 @@
       <c r="C232" t="s">
         <v>772</v>
       </c>
-      <c r="E232" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="233" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D232" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="233" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A233">
         <v>278</v>
       </c>
@@ -7791,11 +7746,11 @@
       <c r="C233" t="s">
         <v>773</v>
       </c>
-      <c r="E233" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="234" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D233" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="234" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A234">
         <v>279</v>
       </c>
@@ -7805,11 +7760,11 @@
       <c r="C234" t="s">
         <v>774</v>
       </c>
-      <c r="E234" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="235" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D234" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="235" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A235">
         <v>280</v>
       </c>
@@ -7819,11 +7774,11 @@
       <c r="C235" t="s">
         <v>775</v>
       </c>
-      <c r="E235" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="236" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D235" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="236" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A236">
         <v>281</v>
       </c>
@@ -7833,11 +7788,11 @@
       <c r="C236" t="s">
         <v>776</v>
       </c>
-      <c r="E236" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="237" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D236" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="237" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A237">
         <v>283</v>
       </c>
@@ -7847,11 +7802,11 @@
       <c r="C237" t="s">
         <v>777</v>
       </c>
-      <c r="E237" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="238" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D237" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="238" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A238">
         <v>284</v>
       </c>
@@ -7861,11 +7816,11 @@
       <c r="C238" t="s">
         <v>778</v>
       </c>
-      <c r="E238" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="239" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D238" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="239" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A239">
         <v>286</v>
       </c>
@@ -7875,11 +7830,11 @@
       <c r="C239" t="s">
         <v>779</v>
       </c>
-      <c r="E239" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="240" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D239" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="240" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A240">
         <v>287</v>
       </c>
@@ -7889,11 +7844,11 @@
       <c r="C240" t="s">
         <v>780</v>
       </c>
-      <c r="E240" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="241" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D240" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="241" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A241">
         <v>288</v>
       </c>
@@ -7903,11 +7858,11 @@
       <c r="C241" t="s">
         <v>781</v>
       </c>
-      <c r="E241" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="242" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D241" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="242" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A242">
         <v>294</v>
       </c>
@@ -7917,11 +7872,11 @@
       <c r="C242" t="s">
         <v>782</v>
       </c>
-      <c r="E242" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="243" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D242" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="243" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A243">
         <v>295</v>
       </c>
@@ -7931,11 +7886,11 @@
       <c r="C243" t="s">
         <v>783</v>
       </c>
-      <c r="E243" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="244" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D243" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="244" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A244">
         <v>296</v>
       </c>
@@ -7945,11 +7900,11 @@
       <c r="C244" t="s">
         <v>784</v>
       </c>
-      <c r="E244" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="245" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D244" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="245" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A245">
         <v>297</v>
       </c>
@@ -7959,11 +7914,11 @@
       <c r="C245" t="s">
         <v>785</v>
       </c>
-      <c r="E245" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="246" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D245" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="246" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A246">
         <v>305</v>
       </c>
@@ -7973,11 +7928,11 @@
       <c r="C246" t="s">
         <v>786</v>
       </c>
-      <c r="E246" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="247" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D246" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="247" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A247">
         <v>306</v>
       </c>
@@ -7987,11 +7942,11 @@
       <c r="C247" t="s">
         <v>787</v>
       </c>
-      <c r="E247" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="248" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D247" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="248" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A248">
         <v>307</v>
       </c>
@@ -8001,11 +7956,11 @@
       <c r="C248" t="s">
         <v>788</v>
       </c>
-      <c r="E248" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="249" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D248" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="249" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A249">
         <v>311</v>
       </c>
@@ -8015,11 +7970,11 @@
       <c r="C249" t="s">
         <v>789</v>
       </c>
-      <c r="E249" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="250" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D249" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="250" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A250">
         <v>315</v>
       </c>
@@ -8029,11 +7984,11 @@
       <c r="C250" t="s">
         <v>790</v>
       </c>
-      <c r="E250" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="251" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D250" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="251" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A251">
         <v>322</v>
       </c>
@@ -8043,11 +7998,11 @@
       <c r="C251" t="s">
         <v>791</v>
       </c>
-      <c r="E251" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="252" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D251" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="252" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A252">
         <v>326</v>
       </c>
@@ -8057,11 +8012,11 @@
       <c r="C252" t="s">
         <v>792</v>
       </c>
-      <c r="E252" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="253" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D252" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="253" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A253">
         <v>327</v>
       </c>
@@ -8071,11 +8026,11 @@
       <c r="C253" t="s">
         <v>793</v>
       </c>
-      <c r="E253" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="254" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D253" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="254" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A254">
         <v>328</v>
       </c>
@@ -8085,11 +8040,11 @@
       <c r="C254" t="s">
         <v>794</v>
       </c>
-      <c r="E254" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="255" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D254" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="255" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A255">
         <v>330</v>
       </c>
@@ -8099,11 +8054,11 @@
       <c r="C255" t="s">
         <v>795</v>
       </c>
-      <c r="E255" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="256" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D255" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="256" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A256">
         <v>331</v>
       </c>
@@ -8113,11 +8068,11 @@
       <c r="C256" t="s">
         <v>796</v>
       </c>
-      <c r="E256" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="257" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D256" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="257" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A257">
         <v>332</v>
       </c>
@@ -8127,11 +8082,11 @@
       <c r="C257" t="s">
         <v>797</v>
       </c>
-      <c r="E257" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="258" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D257" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="258" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A258">
         <v>333</v>
       </c>
@@ -8141,11 +8096,11 @@
       <c r="C258" t="s">
         <v>798</v>
       </c>
-      <c r="E258" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="259" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D258" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="259" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A259">
         <v>335</v>
       </c>
@@ -8155,11 +8110,11 @@
       <c r="C259" t="s">
         <v>799</v>
       </c>
-      <c r="E259" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="260" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D259" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="260" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A260">
         <v>336</v>
       </c>
@@ -8169,11 +8124,11 @@
       <c r="C260" t="s">
         <v>800</v>
       </c>
-      <c r="E260" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="261" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D260" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="261" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A261">
         <v>337</v>
       </c>
@@ -8183,11 +8138,11 @@
       <c r="C261" t="s">
         <v>801</v>
       </c>
-      <c r="E261" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="262" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D261" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="262" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A262">
         <v>338</v>
       </c>
@@ -8197,11 +8152,11 @@
       <c r="C262" t="s">
         <v>802</v>
       </c>
-      <c r="E262" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="263" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D262" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="263" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A263">
         <v>339</v>
       </c>
@@ -8211,11 +8166,11 @@
       <c r="C263" t="s">
         <v>803</v>
       </c>
-      <c r="E263" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="264" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D263" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="264" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A264">
         <v>340</v>
       </c>
@@ -8225,11 +8180,11 @@
       <c r="C264" t="s">
         <v>804</v>
       </c>
-      <c r="E264" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="265" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D264" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="265" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A265">
         <v>342</v>
       </c>
@@ -8239,11 +8194,11 @@
       <c r="C265" t="s">
         <v>805</v>
       </c>
-      <c r="E265" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="266" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D265" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="266" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A266">
         <v>343</v>
       </c>
@@ -8253,11 +8208,11 @@
       <c r="C266" t="s">
         <v>806</v>
       </c>
-      <c r="E266" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="267" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D266" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="267" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A267">
         <v>344</v>
       </c>
@@ -8267,11 +8222,11 @@
       <c r="C267" t="s">
         <v>807</v>
       </c>
-      <c r="E267" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="268" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D267" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="268" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A268">
         <v>345</v>
       </c>
@@ -8281,11 +8236,11 @@
       <c r="C268" t="s">
         <v>808</v>
       </c>
-      <c r="E268" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="269" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D268" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="269" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A269">
         <v>346</v>
       </c>
@@ -8295,11 +8250,11 @@
       <c r="C269" t="s">
         <v>809</v>
       </c>
-      <c r="E269" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="270" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D269" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="270" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A270">
         <v>347</v>
       </c>
@@ -8309,11 +8264,11 @@
       <c r="C270" t="s">
         <v>810</v>
       </c>
-      <c r="E270" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="271" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D270" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="271" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A271">
         <v>348</v>
       </c>
@@ -8323,11 +8278,11 @@
       <c r="C271" t="s">
         <v>811</v>
       </c>
-      <c r="E271" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="272" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D271" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="272" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A272">
         <v>349</v>
       </c>
@@ -8337,11 +8292,11 @@
       <c r="C272" t="s">
         <v>812</v>
       </c>
-      <c r="E272" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="273" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D272" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="273" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A273">
         <v>350</v>
       </c>
@@ -8351,11 +8306,11 @@
       <c r="C273" t="s">
         <v>813</v>
       </c>
-      <c r="E273" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="274" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D273" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="274" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A274">
         <v>351</v>
       </c>
@@ -8365,11 +8320,11 @@
       <c r="C274" t="s">
         <v>814</v>
       </c>
-      <c r="E274" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="275" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D274" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="275" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A275">
         <v>352</v>
       </c>
@@ -8379,11 +8334,11 @@
       <c r="C275" t="s">
         <v>815</v>
       </c>
-      <c r="E275" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="276" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D275" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="276" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A276">
         <v>353</v>
       </c>
@@ -8393,11 +8348,11 @@
       <c r="C276" t="s">
         <v>816</v>
       </c>
-      <c r="E276" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="277" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D276" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="277" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A277">
         <v>354</v>
       </c>
@@ -8407,11 +8362,11 @@
       <c r="C277" t="s">
         <v>817</v>
       </c>
-      <c r="E277" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="278" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D277" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="278" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A278">
         <v>355</v>
       </c>
@@ -8421,11 +8376,11 @@
       <c r="C278" t="s">
         <v>818</v>
       </c>
-      <c r="E278" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="279" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D278" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="279" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A279">
         <v>356</v>
       </c>
@@ -8435,11 +8390,11 @@
       <c r="C279" t="s">
         <v>819</v>
       </c>
-      <c r="E279" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="280" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D279" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="280" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A280">
         <v>357</v>
       </c>
@@ -8449,11 +8404,11 @@
       <c r="C280" t="s">
         <v>820</v>
       </c>
-      <c r="E280" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="281" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D280" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="281" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A281">
         <v>358</v>
       </c>
@@ -8463,11 +8418,11 @@
       <c r="C281" t="s">
         <v>821</v>
       </c>
-      <c r="E281" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="282" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D281" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="282" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A282">
         <v>359</v>
       </c>
@@ -8477,11 +8432,11 @@
       <c r="C282" t="s">
         <v>822</v>
       </c>
-      <c r="E282" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="283" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D282" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="283" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A283">
         <v>360</v>
       </c>
@@ -8491,11 +8446,11 @@
       <c r="C283" t="s">
         <v>823</v>
       </c>
-      <c r="E283" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="284" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D283" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="284" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A284">
         <v>361</v>
       </c>
@@ -8505,11 +8460,11 @@
       <c r="C284" t="s">
         <v>824</v>
       </c>
-      <c r="E284" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="285" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D284" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="285" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A285">
         <v>362</v>
       </c>
@@ -8519,11 +8474,11 @@
       <c r="C285" t="s">
         <v>825</v>
       </c>
-      <c r="E285" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="286" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D285" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="286" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A286">
         <v>363</v>
       </c>
@@ -8533,11 +8488,11 @@
       <c r="C286" t="s">
         <v>826</v>
       </c>
-      <c r="E286" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="287" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D286" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="287" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A287">
         <v>364</v>
       </c>
@@ -8547,11 +8502,11 @@
       <c r="C287" t="s">
         <v>827</v>
       </c>
-      <c r="E287" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="288" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D287" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="288" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A288">
         <v>365</v>
       </c>
@@ -8561,11 +8516,11 @@
       <c r="C288" t="s">
         <v>828</v>
       </c>
-      <c r="E288" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="289" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D288" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="289" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A289">
         <v>366</v>
       </c>
@@ -8575,11 +8530,11 @@
       <c r="C289" t="s">
         <v>829</v>
       </c>
-      <c r="E289" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="290" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D289" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="290" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A290">
         <v>367</v>
       </c>
@@ -8589,11 +8544,11 @@
       <c r="C290" t="s">
         <v>830</v>
       </c>
-      <c r="E290" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="291" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D290" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="291" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A291">
         <v>368</v>
       </c>
@@ -8603,11 +8558,11 @@
       <c r="C291" t="s">
         <v>831</v>
       </c>
-      <c r="E291" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="292" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D291" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="292" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A292">
         <v>369</v>
       </c>
@@ -8617,11 +8572,11 @@
       <c r="C292" t="s">
         <v>832</v>
       </c>
-      <c r="E292" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="293" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D292" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="293" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A293">
         <v>370</v>
       </c>
@@ -8631,11 +8586,11 @@
       <c r="C293" t="s">
         <v>833</v>
       </c>
-      <c r="E293" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="294" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D293" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="294" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A294">
         <v>371</v>
       </c>
@@ -8645,11 +8600,11 @@
       <c r="C294" t="s">
         <v>834</v>
       </c>
-      <c r="E294" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="295" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D294" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="295" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A295">
         <v>372</v>
       </c>
@@ -8659,11 +8614,11 @@
       <c r="C295" t="s">
         <v>835</v>
       </c>
-      <c r="E295" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="296" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D295" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="296" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A296">
         <v>373</v>
       </c>
@@ -8673,11 +8628,11 @@
       <c r="C296" t="s">
         <v>836</v>
       </c>
-      <c r="E296" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="297" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D296" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="297" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A297">
         <v>374</v>
       </c>
@@ -8687,11 +8642,11 @@
       <c r="C297" t="s">
         <v>837</v>
       </c>
-      <c r="E297" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="298" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D297" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="298" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A298">
         <v>375</v>
       </c>
@@ -8701,11 +8656,11 @@
       <c r="C298" t="s">
         <v>838</v>
       </c>
-      <c r="E298" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="299" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D298" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="299" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A299">
         <v>376</v>
       </c>
@@ -8715,11 +8670,11 @@
       <c r="C299" t="s">
         <v>839</v>
       </c>
-      <c r="E299" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="300" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D299" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="300" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A300">
         <v>377</v>
       </c>
@@ -8729,11 +8684,11 @@
       <c r="C300" t="s">
         <v>840</v>
       </c>
-      <c r="E300" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="301" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D300" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="301" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A301">
         <v>378</v>
       </c>
@@ -8743,11 +8698,11 @@
       <c r="C301" t="s">
         <v>841</v>
       </c>
-      <c r="E301" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="302" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D301" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="302" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A302">
         <v>379</v>
       </c>
@@ -8757,11 +8712,11 @@
       <c r="C302" t="s">
         <v>842</v>
       </c>
-      <c r="E302" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="303" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D302" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="303" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A303">
         <v>380</v>
       </c>
@@ -8771,11 +8726,11 @@
       <c r="C303" t="s">
         <v>843</v>
       </c>
-      <c r="E303" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="304" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D303" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="304" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A304">
         <v>381</v>
       </c>
@@ -8785,11 +8740,11 @@
       <c r="C304" t="s">
         <v>844</v>
       </c>
-      <c r="E304" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="305" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D304" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="305" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A305">
         <v>382</v>
       </c>
@@ -8799,11 +8754,11 @@
       <c r="C305" t="s">
         <v>845</v>
       </c>
-      <c r="E305" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="306" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D305" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="306" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A306">
         <v>383</v>
       </c>
@@ -8813,11 +8768,11 @@
       <c r="C306" t="s">
         <v>846</v>
       </c>
-      <c r="E306" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="307" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D306" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="307" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A307">
         <v>384</v>
       </c>
@@ -8827,11 +8782,11 @@
       <c r="C307" t="s">
         <v>847</v>
       </c>
-      <c r="E307" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="308" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D307" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="308" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A308">
         <v>385</v>
       </c>
@@ -8841,11 +8796,11 @@
       <c r="C308" t="s">
         <v>848</v>
       </c>
-      <c r="E308" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="309" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D308" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="309" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A309">
         <v>386</v>
       </c>
@@ -8855,11 +8810,11 @@
       <c r="C309" t="s">
         <v>849</v>
       </c>
-      <c r="E309" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="310" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D309" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="310" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A310">
         <v>387</v>
       </c>
@@ -8869,11 +8824,11 @@
       <c r="C310" t="s">
         <v>850</v>
       </c>
-      <c r="E310" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="311" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D310" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="311" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A311">
         <v>388</v>
       </c>
@@ -8883,11 +8838,11 @@
       <c r="C311" t="s">
         <v>851</v>
       </c>
-      <c r="E311" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="312" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D311" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="312" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A312">
         <v>389</v>
       </c>
@@ -8897,11 +8852,11 @@
       <c r="C312" t="s">
         <v>852</v>
       </c>
-      <c r="E312" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="313" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D312" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="313" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A313">
         <v>390</v>
       </c>
@@ -8911,11 +8866,11 @@
       <c r="C313" t="s">
         <v>853</v>
       </c>
-      <c r="E313" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="314" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D313" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="314" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A314">
         <v>391</v>
       </c>
@@ -8925,11 +8880,11 @@
       <c r="C314" t="s">
         <v>854</v>
       </c>
-      <c r="E314" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="315" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D314" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="315" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A315">
         <v>392</v>
       </c>
@@ -8939,11 +8894,11 @@
       <c r="C315" t="s">
         <v>855</v>
       </c>
-      <c r="E315" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="316" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D315" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="316" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A316">
         <v>393</v>
       </c>
@@ -8953,11 +8908,11 @@
       <c r="C316" t="s">
         <v>856</v>
       </c>
-      <c r="E316" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="317" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D316" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="317" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A317">
         <v>394</v>
       </c>
@@ -8967,11 +8922,11 @@
       <c r="C317" t="s">
         <v>857</v>
       </c>
-      <c r="E317" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="318" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D317" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="318" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A318">
         <v>395</v>
       </c>
@@ -8981,11 +8936,11 @@
       <c r="C318" t="s">
         <v>858</v>
       </c>
-      <c r="E318" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="319" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D318" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="319" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A319">
         <v>396</v>
       </c>
@@ -8995,11 +8950,11 @@
       <c r="C319" t="s">
         <v>859</v>
       </c>
-      <c r="E319" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="320" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D319" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="320" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A320">
         <v>397</v>
       </c>
@@ -9009,11 +8964,11 @@
       <c r="C320" t="s">
         <v>860</v>
       </c>
-      <c r="E320" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="321" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D320" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="321" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A321">
         <v>398</v>
       </c>
@@ -9023,11 +8978,11 @@
       <c r="C321" t="s">
         <v>861</v>
       </c>
-      <c r="E321" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="322" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D321" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="322" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A322">
         <v>399</v>
       </c>
@@ -9037,11 +8992,11 @@
       <c r="C322" t="s">
         <v>862</v>
       </c>
-      <c r="E322" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="323" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D322" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="323" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A323">
         <v>400</v>
       </c>
@@ -9051,11 +9006,11 @@
       <c r="C323" t="s">
         <v>863</v>
       </c>
-      <c r="E323" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="324" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D323" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="324" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A324">
         <v>401</v>
       </c>
@@ -9065,11 +9020,11 @@
       <c r="C324" t="s">
         <v>864</v>
       </c>
-      <c r="E324" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="325" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D324" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="325" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A325">
         <v>426</v>
       </c>
@@ -9079,11 +9034,11 @@
       <c r="C325" t="s">
         <v>865</v>
       </c>
-      <c r="E325" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="326" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D325" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="326" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A326">
         <v>427</v>
       </c>
@@ -9093,11 +9048,11 @@
       <c r="C326" t="s">
         <v>866</v>
       </c>
-      <c r="E326" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="327" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D326" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="327" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A327">
         <v>428</v>
       </c>
@@ -9107,11 +9062,11 @@
       <c r="C327" t="s">
         <v>867</v>
       </c>
-      <c r="E327" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="328" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D327" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="328" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A328">
         <v>430</v>
       </c>
@@ -9121,11 +9076,11 @@
       <c r="C328" t="s">
         <v>868</v>
       </c>
-      <c r="E328" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="329" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D328" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="329" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A329">
         <v>431</v>
       </c>
@@ -9135,11 +9090,11 @@
       <c r="C329" t="s">
         <v>869</v>
       </c>
-      <c r="E329" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="330" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D329" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="330" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A330">
         <v>432</v>
       </c>
@@ -9149,11 +9104,11 @@
       <c r="C330" t="s">
         <v>870</v>
       </c>
-      <c r="E330" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="331" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D330" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="331" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A331">
         <v>433</v>
       </c>
@@ -9163,11 +9118,11 @@
       <c r="C331" t="s">
         <v>871</v>
       </c>
-      <c r="E331" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="332" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D331" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="332" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A332">
         <v>434</v>
       </c>
@@ -9177,11 +9132,11 @@
       <c r="C332" t="s">
         <v>872</v>
       </c>
-      <c r="E332" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="333" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D332" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="333" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A333">
         <v>435</v>
       </c>
@@ -9191,11 +9146,11 @@
       <c r="C333" t="s">
         <v>873</v>
       </c>
-      <c r="E333" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="334" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D333" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="334" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A334">
         <v>436</v>
       </c>
@@ -9205,11 +9160,11 @@
       <c r="C334" t="s">
         <v>874</v>
       </c>
-      <c r="E334" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="335" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D334" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="335" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A335">
         <v>437</v>
       </c>
@@ -9219,11 +9174,11 @@
       <c r="C335" t="s">
         <v>875</v>
       </c>
-      <c r="E335" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="336" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D335" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="336" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A336">
         <v>438</v>
       </c>
@@ -9233,11 +9188,11 @@
       <c r="C336" t="s">
         <v>876</v>
       </c>
-      <c r="E336" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="337" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D336" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="337" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A337">
         <v>439</v>
       </c>
@@ -9247,11 +9202,11 @@
       <c r="C337" t="s">
         <v>877</v>
       </c>
-      <c r="E337" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="338" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D337" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="338" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A338">
         <v>440</v>
       </c>
@@ -9261,11 +9216,11 @@
       <c r="C338" t="s">
         <v>878</v>
       </c>
-      <c r="E338" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="339" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D338" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="339" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A339">
         <v>441</v>
       </c>
@@ -9275,11 +9230,11 @@
       <c r="C339" t="s">
         <v>879</v>
       </c>
-      <c r="E339" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="340" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D339" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="340" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A340">
         <v>442</v>
       </c>
@@ -9289,11 +9244,11 @@
       <c r="C340" t="s">
         <v>880</v>
       </c>
-      <c r="E340" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="341" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D340" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="341" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A341">
         <v>443</v>
       </c>
@@ -9303,11 +9258,11 @@
       <c r="C341" t="s">
         <v>881</v>
       </c>
-      <c r="E341" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="342" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D341" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="342" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A342">
         <v>444</v>
       </c>
@@ -9317,11 +9272,11 @@
       <c r="C342" t="s">
         <v>882</v>
       </c>
-      <c r="E342" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="343" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D342" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="343" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A343">
         <v>445</v>
       </c>
@@ -9331,11 +9286,11 @@
       <c r="C343" t="s">
         <v>883</v>
       </c>
-      <c r="E343" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="344" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D343" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="344" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A344">
         <v>446</v>
       </c>
@@ -9345,11 +9300,11 @@
       <c r="C344" t="s">
         <v>884</v>
       </c>
-      <c r="E344" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="345" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D344" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="345" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A345">
         <v>447</v>
       </c>
@@ -9359,11 +9314,11 @@
       <c r="C345" t="s">
         <v>885</v>
       </c>
-      <c r="E345" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="346" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D345" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="346" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A346">
         <v>449</v>
       </c>
@@ -9373,11 +9328,11 @@
       <c r="C346" t="s">
         <v>886</v>
       </c>
-      <c r="E346" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="347" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D346" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="347" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A347">
         <v>450</v>
       </c>
@@ -9387,11 +9342,11 @@
       <c r="C347" t="s">
         <v>887</v>
       </c>
-      <c r="E347" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="348" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D347" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="348" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A348">
         <v>451</v>
       </c>
@@ -9401,11 +9356,11 @@
       <c r="C348" t="s">
         <v>888</v>
       </c>
-      <c r="E348" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="349" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D348" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="349" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A349">
         <v>452</v>
       </c>
@@ -9415,11 +9370,11 @@
       <c r="C349" t="s">
         <v>889</v>
       </c>
-      <c r="E349" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="350" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D349" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="350" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A350">
         <v>453</v>
       </c>
@@ -9429,11 +9384,11 @@
       <c r="C350" t="s">
         <v>890</v>
       </c>
-      <c r="E350" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="351" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D350" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="351" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A351">
         <v>454</v>
       </c>
@@ -9443,11 +9398,11 @@
       <c r="C351" t="s">
         <v>891</v>
       </c>
-      <c r="E351" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="352" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D351" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="352" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A352">
         <v>456</v>
       </c>
@@ -9457,11 +9412,11 @@
       <c r="C352" t="s">
         <v>892</v>
       </c>
-      <c r="E352" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="353" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D352" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="353" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A353">
         <v>457</v>
       </c>
@@ -9471,11 +9426,11 @@
       <c r="C353" t="s">
         <v>893</v>
       </c>
-      <c r="E353" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="354" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D353" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="354" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A354">
         <v>458</v>
       </c>
@@ -9485,11 +9440,11 @@
       <c r="C354" t="s">
         <v>894</v>
       </c>
-      <c r="E354" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="355" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D354" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="355" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A355">
         <v>459</v>
       </c>
@@ -9499,11 +9454,11 @@
       <c r="C355" t="s">
         <v>895</v>
       </c>
-      <c r="E355" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="356" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D355" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="356" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A356">
         <v>460</v>
       </c>
@@ -9513,11 +9468,11 @@
       <c r="C356" t="s">
         <v>896</v>
       </c>
-      <c r="E356" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="357" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D356" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="357" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A357">
         <v>461</v>
       </c>
@@ -9527,11 +9482,11 @@
       <c r="C357" t="s">
         <v>897</v>
       </c>
-      <c r="E357" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="358" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D357" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="358" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A358">
         <v>462</v>
       </c>
@@ -9541,11 +9496,11 @@
       <c r="C358" t="s">
         <v>898</v>
       </c>
-      <c r="E358" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="359" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D358" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="359" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A359">
         <v>463</v>
       </c>
@@ -9555,11 +9510,11 @@
       <c r="C359" t="s">
         <v>899</v>
       </c>
-      <c r="E359" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="360" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D359" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="360" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A360">
         <v>464</v>
       </c>
@@ -9569,11 +9524,11 @@
       <c r="C360" t="s">
         <v>900</v>
       </c>
-      <c r="E360" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="361" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D360" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="361" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A361">
         <v>465</v>
       </c>
@@ -9583,11 +9538,11 @@
       <c r="C361" t="s">
         <v>901</v>
       </c>
-      <c r="E361" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="362" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D361" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="362" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A362">
         <v>466</v>
       </c>
@@ -9597,11 +9552,11 @@
       <c r="C362" t="s">
         <v>902</v>
       </c>
-      <c r="E362" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="363" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D362" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="363" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A363">
         <v>469</v>
       </c>
@@ -9611,11 +9566,11 @@
       <c r="C363" t="s">
         <v>903</v>
       </c>
-      <c r="E363" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="364" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D363" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="364" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A364">
         <v>470</v>
       </c>
@@ -9625,11 +9580,11 @@
       <c r="C364" t="s">
         <v>904</v>
       </c>
-      <c r="E364" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="365" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D364" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="365" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A365">
         <v>471</v>
       </c>
@@ -9639,11 +9594,11 @@
       <c r="C365" t="s">
         <v>905</v>
       </c>
-      <c r="E365" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="366" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D365" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="366" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A366">
         <v>472</v>
       </c>
@@ -9653,11 +9608,11 @@
       <c r="C366" t="s">
         <v>906</v>
       </c>
-      <c r="E366" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="367" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D366" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="367" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A367">
         <v>473</v>
       </c>
@@ -9667,11 +9622,11 @@
       <c r="C367" t="s">
         <v>907</v>
       </c>
-      <c r="E367" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="368" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D367" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="368" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A368">
         <v>474</v>
       </c>
@@ -9681,11 +9636,11 @@
       <c r="C368" t="s">
         <v>908</v>
       </c>
-      <c r="E368" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="369" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D368" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="369" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A369">
         <v>475</v>
       </c>
@@ -9695,11 +9650,11 @@
       <c r="C369" t="s">
         <v>909</v>
       </c>
-      <c r="E369" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="370" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D369" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="370" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A370">
         <v>476</v>
       </c>
@@ -9709,11 +9664,11 @@
       <c r="C370" t="s">
         <v>910</v>
       </c>
-      <c r="E370" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="371" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D370" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="371" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A371">
         <v>477</v>
       </c>
@@ -9723,11 +9678,11 @@
       <c r="C371" t="s">
         <v>911</v>
       </c>
-      <c r="E371" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="372" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D371" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="372" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A372">
         <v>478</v>
       </c>
@@ -9737,11 +9692,11 @@
       <c r="C372" t="s">
         <v>912</v>
       </c>
-      <c r="E372" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="373" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D372" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="373" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A373">
         <v>481</v>
       </c>
@@ -9751,11 +9706,11 @@
       <c r="C373" t="s">
         <v>913</v>
       </c>
-      <c r="E373" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="374" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D373" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="374" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A374">
         <v>482</v>
       </c>
@@ -9765,11 +9720,11 @@
       <c r="C374" t="s">
         <v>914</v>
       </c>
-      <c r="E374" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="375" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D374" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="375" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A375">
         <v>483</v>
       </c>
@@ -9779,11 +9734,11 @@
       <c r="C375" t="s">
         <v>915</v>
       </c>
-      <c r="E375" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="376" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D375" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="376" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A376">
         <v>484</v>
       </c>
@@ -9793,11 +9748,11 @@
       <c r="C376" t="s">
         <v>916</v>
       </c>
-      <c r="E376" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="377" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D376" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="377" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A377">
         <v>485</v>
       </c>
@@ -9807,11 +9762,11 @@
       <c r="C377" t="s">
         <v>917</v>
       </c>
-      <c r="E377" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="378" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D377" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="378" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A378">
         <v>487</v>
       </c>
@@ -9821,11 +9776,11 @@
       <c r="C378" t="s">
         <v>918</v>
       </c>
-      <c r="E378" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="379" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D378" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="379" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A379">
         <v>488</v>
       </c>
@@ -9835,11 +9790,11 @@
       <c r="C379" t="s">
         <v>919</v>
       </c>
-      <c r="E379" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="380" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D379" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="380" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A380">
         <v>489</v>
       </c>
@@ -9849,11 +9804,11 @@
       <c r="C380" t="s">
         <v>920</v>
       </c>
-      <c r="E380" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="381" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D380" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="381" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A381">
         <v>490</v>
       </c>
@@ -9863,11 +9818,11 @@
       <c r="C381" t="s">
         <v>921</v>
       </c>
-      <c r="E381" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="382" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D381" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="382" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A382">
         <v>491</v>
       </c>
@@ -9877,11 +9832,11 @@
       <c r="C382" t="s">
         <v>922</v>
       </c>
-      <c r="E382" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="383" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D382" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="383" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A383">
         <v>492</v>
       </c>
@@ -9891,11 +9846,11 @@
       <c r="C383" t="s">
         <v>923</v>
       </c>
-      <c r="E383" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="384" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D383" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="384" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A384">
         <v>493</v>
       </c>
@@ -9905,11 +9860,11 @@
       <c r="C384" t="s">
         <v>924</v>
       </c>
-      <c r="E384" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="385" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D384" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="385" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A385">
         <v>494</v>
       </c>
@@ -9919,11 +9874,11 @@
       <c r="C385" t="s">
         <v>925</v>
       </c>
-      <c r="E385" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="386" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D385" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="386" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A386">
         <v>495</v>
       </c>
@@ -9933,11 +9888,11 @@
       <c r="C386" t="s">
         <v>926</v>
       </c>
-      <c r="E386" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="387" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D386" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="387" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A387">
         <v>496</v>
       </c>
@@ -9947,11 +9902,11 @@
       <c r="C387" t="s">
         <v>927</v>
       </c>
-      <c r="E387" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="388" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D387" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="388" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A388">
         <v>498</v>
       </c>
@@ -9961,11 +9916,11 @@
       <c r="C388" t="s">
         <v>928</v>
       </c>
-      <c r="E388" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="389" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D388" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="389" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A389">
         <v>499</v>
       </c>
@@ -9975,11 +9930,11 @@
       <c r="C389" t="s">
         <v>929</v>
       </c>
-      <c r="E389" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="390" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D389" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="390" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A390">
         <v>500</v>
       </c>
@@ -9989,11 +9944,11 @@
       <c r="C390" t="s">
         <v>930</v>
       </c>
-      <c r="E390" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="391" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D390" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="391" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A391">
         <v>501</v>
       </c>
@@ -10003,11 +9958,11 @@
       <c r="C391" t="s">
         <v>931</v>
       </c>
-      <c r="E391" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="392" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D391" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="392" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A392">
         <v>502</v>
       </c>
@@ -10017,11 +9972,11 @@
       <c r="C392" t="s">
         <v>932</v>
       </c>
-      <c r="E392" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="393" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D392" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="393" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A393">
         <v>503</v>
       </c>
@@ -10031,11 +9986,11 @@
       <c r="C393" t="s">
         <v>933</v>
       </c>
-      <c r="E393" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="394" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D393" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="394" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A394">
         <v>504</v>
       </c>
@@ -10045,11 +10000,11 @@
       <c r="C394" t="s">
         <v>934</v>
       </c>
-      <c r="E394" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="395" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D394" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="395" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A395">
         <v>505</v>
       </c>
@@ -10059,11 +10014,11 @@
       <c r="C395" t="s">
         <v>935</v>
       </c>
-      <c r="E395" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="396" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D395" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="396" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A396">
         <v>506</v>
       </c>
@@ -10073,11 +10028,11 @@
       <c r="C396" t="s">
         <v>936</v>
       </c>
-      <c r="E396" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="397" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D396" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="397" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A397">
         <v>507</v>
       </c>
@@ -10087,11 +10042,11 @@
       <c r="C397" t="s">
         <v>937</v>
       </c>
-      <c r="E397" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="398" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D397" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="398" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A398">
         <v>508</v>
       </c>
@@ -10101,11 +10056,11 @@
       <c r="C398" t="s">
         <v>938</v>
       </c>
-      <c r="E398" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="399" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D398" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="399" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A399">
         <v>509</v>
       </c>
@@ -10115,11 +10070,11 @@
       <c r="C399" t="s">
         <v>939</v>
       </c>
-      <c r="E399" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="400" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D399" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="400" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A400">
         <v>510</v>
       </c>
@@ -10129,11 +10084,11 @@
       <c r="C400" t="s">
         <v>940</v>
       </c>
-      <c r="E400" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="401" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D400" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="401" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A401">
         <v>511</v>
       </c>
@@ -10143,11 +10098,11 @@
       <c r="C401" t="s">
         <v>941</v>
       </c>
-      <c r="E401" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="402" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D401" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="402" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A402">
         <v>512</v>
       </c>
@@ -10157,11 +10112,11 @@
       <c r="C402" t="s">
         <v>942</v>
       </c>
-      <c r="E402" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="403" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D402" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="403" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A403">
         <v>513</v>
       </c>
@@ -10171,11 +10126,11 @@
       <c r="C403" t="s">
         <v>943</v>
       </c>
-      <c r="E403" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="404" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D403" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="404" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A404">
         <v>514</v>
       </c>
@@ -10185,11 +10140,11 @@
       <c r="C404" t="s">
         <v>944</v>
       </c>
-      <c r="E404" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="405" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D404" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="405" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A405">
         <v>515</v>
       </c>
@@ -10199,11 +10154,11 @@
       <c r="C405" t="s">
         <v>945</v>
       </c>
-      <c r="E405" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="406" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D405" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="406" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A406">
         <v>516</v>
       </c>
@@ -10213,11 +10168,11 @@
       <c r="C406" t="s">
         <v>946</v>
       </c>
-      <c r="E406" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="407" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D406" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="407" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A407">
         <v>517</v>
       </c>
@@ -10227,11 +10182,11 @@
       <c r="C407" t="s">
         <v>947</v>
       </c>
-      <c r="E407" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="408" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D407" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="408" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A408">
         <v>518</v>
       </c>
@@ -10241,11 +10196,11 @@
       <c r="C408" t="s">
         <v>948</v>
       </c>
-      <c r="E408" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="409" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D408" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="409" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A409">
         <v>519</v>
       </c>
@@ -10255,11 +10210,11 @@
       <c r="C409" t="s">
         <v>949</v>
       </c>
-      <c r="E409" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="410" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D409" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="410" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A410">
         <v>520</v>
       </c>
@@ -10269,11 +10224,11 @@
       <c r="C410" t="s">
         <v>950</v>
       </c>
-      <c r="E410" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="411" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D410" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="411" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A411">
         <v>521</v>
       </c>
@@ -10283,11 +10238,11 @@
       <c r="C411" t="s">
         <v>951</v>
       </c>
-      <c r="E411" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="412" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D411" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="412" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A412">
         <v>522</v>
       </c>
@@ -10297,11 +10252,11 @@
       <c r="C412" t="s">
         <v>952</v>
       </c>
-      <c r="E412" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="413" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D412" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="413" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A413">
         <v>523</v>
       </c>
@@ -10311,11 +10266,11 @@
       <c r="C413" t="s">
         <v>953</v>
       </c>
-      <c r="E413" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="414" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D413" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="414" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A414">
         <v>524</v>
       </c>
@@ -10325,11 +10280,11 @@
       <c r="C414" t="s">
         <v>954</v>
       </c>
-      <c r="E414" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="415" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D414" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="415" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A415">
         <v>525</v>
       </c>
@@ -10339,11 +10294,11 @@
       <c r="C415" t="s">
         <v>955</v>
       </c>
-      <c r="E415" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="416" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D415" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="416" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A416">
         <v>526</v>
       </c>
@@ -10353,11 +10308,11 @@
       <c r="C416" t="s">
         <v>956</v>
       </c>
-      <c r="E416" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="417" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D416" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="417" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A417">
         <v>527</v>
       </c>
@@ -10367,11 +10322,11 @@
       <c r="C417" t="s">
         <v>957</v>
       </c>
-      <c r="E417" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="418" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D417" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="418" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A418">
         <v>528</v>
       </c>
@@ -10381,11 +10336,11 @@
       <c r="C418" t="s">
         <v>958</v>
       </c>
-      <c r="E418" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="419" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D418" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="419" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A419">
         <v>529</v>
       </c>
@@ -10395,11 +10350,11 @@
       <c r="C419" t="s">
         <v>959</v>
       </c>
-      <c r="E419" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="420" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D419" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="420" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A420">
         <v>530</v>
       </c>
@@ -10409,11 +10364,11 @@
       <c r="C420" t="s">
         <v>960</v>
       </c>
-      <c r="E420" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="421" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D420" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="421" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A421">
         <v>531</v>
       </c>
@@ -10423,11 +10378,11 @@
       <c r="C421" t="s">
         <v>961</v>
       </c>
-      <c r="E421" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="422" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D421" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="422" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A422">
         <v>532</v>
       </c>
@@ -10437,11 +10392,11 @@
       <c r="C422" t="s">
         <v>962</v>
       </c>
-      <c r="E422" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="423" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D422" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="423" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A423">
         <v>533</v>
       </c>
@@ -10451,11 +10406,11 @@
       <c r="C423" t="s">
         <v>963</v>
       </c>
-      <c r="E423" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="424" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D423" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="424" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A424">
         <v>534</v>
       </c>
@@ -10465,11 +10420,11 @@
       <c r="C424" t="s">
         <v>964</v>
       </c>
-      <c r="E424" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="425" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D424" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="425" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A425">
         <v>535</v>
       </c>
@@ -10479,11 +10434,11 @@
       <c r="C425" t="s">
         <v>965</v>
       </c>
-      <c r="E425" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="426" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D425" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="426" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A426">
         <v>536</v>
       </c>
@@ -10493,11 +10448,11 @@
       <c r="C426" t="s">
         <v>966</v>
       </c>
-      <c r="E426" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="427" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D426" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="427" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A427">
         <v>537</v>
       </c>
@@ -10507,11 +10462,11 @@
       <c r="C427" t="s">
         <v>967</v>
       </c>
-      <c r="E427" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="428" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D427" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="428" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A428">
         <v>538</v>
       </c>
@@ -10521,11 +10476,11 @@
       <c r="C428" t="s">
         <v>968</v>
       </c>
-      <c r="E428" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="429" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D428" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="429" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A429">
         <v>539</v>
       </c>
@@ -10535,11 +10490,11 @@
       <c r="C429" t="s">
         <v>969</v>
       </c>
-      <c r="E429" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="430" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D429" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="430" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A430">
         <v>540</v>
       </c>
@@ -10549,11 +10504,11 @@
       <c r="C430" t="s">
         <v>970</v>
       </c>
-      <c r="E430" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="431" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D430" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="431" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A431">
         <v>541</v>
       </c>
@@ -10563,11 +10518,11 @@
       <c r="C431" t="s">
         <v>971</v>
       </c>
-      <c r="E431" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="432" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D431" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="432" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A432">
         <v>542</v>
       </c>
@@ -10577,11 +10532,11 @@
       <c r="C432" t="s">
         <v>972</v>
       </c>
-      <c r="E432" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="433" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D432" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="433" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A433">
         <v>543</v>
       </c>
@@ -10591,11 +10546,11 @@
       <c r="C433" t="s">
         <v>973</v>
       </c>
-      <c r="E433" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="434" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D433" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="434" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A434">
         <v>544</v>
       </c>
@@ -10605,11 +10560,11 @@
       <c r="C434" t="s">
         <v>974</v>
       </c>
-      <c r="E434" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="435" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D434" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="435" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A435">
         <v>545</v>
       </c>
@@ -10619,11 +10574,11 @@
       <c r="C435" t="s">
         <v>975</v>
       </c>
-      <c r="E435" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="436" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D435" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="436" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A436">
         <v>546</v>
       </c>
@@ -10633,11 +10588,11 @@
       <c r="C436" t="s">
         <v>976</v>
       </c>
-      <c r="E436" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="437" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D436" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="437" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A437">
         <v>547</v>
       </c>
@@ -10647,11 +10602,11 @@
       <c r="C437" t="s">
         <v>977</v>
       </c>
-      <c r="E437" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="438" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D437" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="438" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A438">
         <v>548</v>
       </c>
@@ -10661,11 +10616,11 @@
       <c r="C438" t="s">
         <v>978</v>
       </c>
-      <c r="E438" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="439" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D438" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="439" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A439">
         <v>549</v>
       </c>
@@ -10675,11 +10630,11 @@
       <c r="C439" t="s">
         <v>979</v>
       </c>
-      <c r="E439" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="440" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D439" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="440" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A440">
         <v>550</v>
       </c>
@@ -10689,11 +10644,11 @@
       <c r="C440" t="s">
         <v>980</v>
       </c>
-      <c r="E440" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="441" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D440" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="441" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A441">
         <v>551</v>
       </c>
@@ -10703,11 +10658,11 @@
       <c r="C441" t="s">
         <v>981</v>
       </c>
-      <c r="E441" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="442" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D441" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="442" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A442">
         <v>552</v>
       </c>
@@ -10717,11 +10672,11 @@
       <c r="C442" t="s">
         <v>982</v>
       </c>
-      <c r="E442" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="443" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D442" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="443" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A443">
         <v>553</v>
       </c>
@@ -10731,11 +10686,11 @@
       <c r="C443" t="s">
         <v>983</v>
       </c>
-      <c r="E443" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="444" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D443" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="444" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A444">
         <v>554</v>
       </c>
@@ -10745,11 +10700,11 @@
       <c r="C444" t="s">
         <v>984</v>
       </c>
-      <c r="E444" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="445" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D444" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="445" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A445">
         <v>555</v>
       </c>
@@ -10759,11 +10714,11 @@
       <c r="C445" t="s">
         <v>985</v>
       </c>
-      <c r="E445" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="446" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D445" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="446" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A446">
         <v>556</v>
       </c>
@@ -10773,11 +10728,11 @@
       <c r="C446" t="s">
         <v>986</v>
       </c>
-      <c r="E446" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="447" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D446" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="447" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A447">
         <v>557</v>
       </c>
@@ -10787,11 +10742,11 @@
       <c r="C447" t="s">
         <v>987</v>
       </c>
-      <c r="E447" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="448" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D447" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="448" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A448">
         <v>558</v>
       </c>
@@ -10801,11 +10756,11 @@
       <c r="C448" t="s">
         <v>988</v>
       </c>
-      <c r="E448" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="449" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D448" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="449" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A449">
         <v>559</v>
       </c>
@@ -10815,11 +10770,11 @@
       <c r="C449" t="s">
         <v>989</v>
       </c>
-      <c r="E449" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="450" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D449" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="450" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A450">
         <v>560</v>
       </c>
@@ -10829,11 +10784,11 @@
       <c r="C450" t="s">
         <v>990</v>
       </c>
-      <c r="E450" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="451" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D450" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="451" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A451">
         <v>561</v>
       </c>
@@ -10843,11 +10798,11 @@
       <c r="C451" t="s">
         <v>991</v>
       </c>
-      <c r="E451" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="452" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D451" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="452" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A452">
         <v>562</v>
       </c>
@@ -10857,11 +10812,11 @@
       <c r="C452" t="s">
         <v>992</v>
       </c>
-      <c r="E452" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="453" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D452" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="453" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A453">
         <v>563</v>
       </c>
@@ -10871,11 +10826,11 @@
       <c r="C453" t="s">
         <v>993</v>
       </c>
-      <c r="E453" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="454" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D453" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="454" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A454">
         <v>564</v>
       </c>
@@ -10885,11 +10840,11 @@
       <c r="C454" t="s">
         <v>994</v>
       </c>
-      <c r="E454" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="455" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D454" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="455" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A455">
         <v>565</v>
       </c>
@@ -10899,11 +10854,11 @@
       <c r="C455" t="s">
         <v>995</v>
       </c>
-      <c r="E455" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="456" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D455" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="456" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A456">
         <v>566</v>
       </c>
@@ -10913,11 +10868,11 @@
       <c r="C456" t="s">
         <v>996</v>
       </c>
-      <c r="E456" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="457" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D456" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="457" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A457">
         <v>567</v>
       </c>
@@ -10927,11 +10882,11 @@
       <c r="C457" t="s">
         <v>997</v>
       </c>
-      <c r="E457" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="458" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D457" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="458" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A458">
         <v>568</v>
       </c>
@@ -10941,11 +10896,11 @@
       <c r="C458" t="s">
         <v>998</v>
       </c>
-      <c r="E458" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="459" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D458" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="459" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A459">
         <v>569</v>
       </c>
@@ -10955,11 +10910,11 @@
       <c r="C459" t="s">
         <v>999</v>
       </c>
-      <c r="E459" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="460" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D459" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="460" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A460">
         <v>570</v>
       </c>
@@ -10969,11 +10924,11 @@
       <c r="C460" t="s">
         <v>1000</v>
       </c>
-      <c r="E460" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="461" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D460" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="461" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A461">
         <v>571</v>
       </c>
@@ -10983,11 +10938,11 @@
       <c r="C461" t="s">
         <v>1001</v>
       </c>
-      <c r="E461" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="462" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D461" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="462" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A462">
         <v>572</v>
       </c>
@@ -10997,11 +10952,11 @@
       <c r="C462" t="s">
         <v>1002</v>
       </c>
-      <c r="E462" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="463" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D462" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="463" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A463">
         <v>573</v>
       </c>
@@ -11011,11 +10966,11 @@
       <c r="C463" t="s">
         <v>1003</v>
       </c>
-      <c r="E463" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="464" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D463" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="464" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A464">
         <v>574</v>
       </c>
@@ -11025,11 +10980,11 @@
       <c r="C464" t="s">
         <v>1004</v>
       </c>
-      <c r="E464" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="465" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D464" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="465" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A465">
         <v>575</v>
       </c>
@@ -11039,11 +10994,11 @@
       <c r="C465" t="s">
         <v>1005</v>
       </c>
-      <c r="E465" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="466" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D465" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="466" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A466">
         <v>576</v>
       </c>
@@ -11053,11 +11008,11 @@
       <c r="C466" t="s">
         <v>1006</v>
       </c>
-      <c r="E466" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="467" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D466" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="467" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A467">
         <v>577</v>
       </c>
@@ -11067,11 +11022,11 @@
       <c r="C467" t="s">
         <v>1007</v>
       </c>
-      <c r="E467" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="468" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D467" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="468" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A468">
         <v>578</v>
       </c>
@@ -11081,11 +11036,11 @@
       <c r="C468" t="s">
         <v>1008</v>
       </c>
-      <c r="E468" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="469" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D468" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="469" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A469">
         <v>579</v>
       </c>
@@ -11095,11 +11050,11 @@
       <c r="C469" t="s">
         <v>1009</v>
       </c>
-      <c r="E469" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="470" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D469" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="470" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A470">
         <v>580</v>
       </c>
@@ -11109,11 +11064,11 @@
       <c r="C470" t="s">
         <v>1010</v>
       </c>
-      <c r="E470" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="471" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D470" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="471" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A471">
         <v>581</v>
       </c>
@@ -11123,11 +11078,11 @@
       <c r="C471" t="s">
         <v>1011</v>
       </c>
-      <c r="E471" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="472" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D471" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="472" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A472">
         <v>582</v>
       </c>
@@ -11137,11 +11092,11 @@
       <c r="C472" t="s">
         <v>1012</v>
       </c>
-      <c r="E472" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="473" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D472" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="473" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A473">
         <v>583</v>
       </c>
@@ -11151,11 +11106,11 @@
       <c r="C473" t="s">
         <v>1013</v>
       </c>
-      <c r="E473" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="474" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D473" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="474" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A474">
         <v>584</v>
       </c>
@@ -11165,11 +11120,11 @@
       <c r="C474" t="s">
         <v>1014</v>
       </c>
-      <c r="E474" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="475" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D474" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="475" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A475">
         <v>585</v>
       </c>
@@ -11179,11 +11134,11 @@
       <c r="C475" t="s">
         <v>1015</v>
       </c>
-      <c r="E475" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="476" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D475" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="476" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A476">
         <v>586</v>
       </c>
@@ -11193,11 +11148,11 @@
       <c r="C476" t="s">
         <v>1016</v>
       </c>
-      <c r="E476" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="477" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D476" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="477" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A477">
         <v>590</v>
       </c>
@@ -11207,11 +11162,11 @@
       <c r="C477" t="s">
         <v>1017</v>
       </c>
-      <c r="E477" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="478" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D477" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="478" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A478">
         <v>591</v>
       </c>
@@ -11221,11 +11176,11 @@
       <c r="C478" t="s">
         <v>1018</v>
       </c>
-      <c r="E478" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="479" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D478" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="479" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A479">
         <v>592</v>
       </c>
@@ -11235,11 +11190,11 @@
       <c r="C479" t="s">
         <v>1019</v>
       </c>
-      <c r="E479" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="480" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D479" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="480" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A480">
         <v>593</v>
       </c>
@@ -11249,11 +11204,11 @@
       <c r="C480" t="s">
         <v>1020</v>
       </c>
-      <c r="E480" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="481" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D480" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="481" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A481">
         <v>594</v>
       </c>
@@ -11263,11 +11218,11 @@
       <c r="C481" t="s">
         <v>1021</v>
       </c>
-      <c r="E481" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="482" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D481" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="482" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A482">
         <v>595</v>
       </c>
@@ -11277,11 +11232,11 @@
       <c r="C482" t="s">
         <v>1022</v>
       </c>
-      <c r="E482" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="483" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D482" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="483" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A483">
         <v>596</v>
       </c>
@@ -11291,11 +11246,11 @@
       <c r="C483" t="s">
         <v>1023</v>
       </c>
-      <c r="E483" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="484" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D483" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="484" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A484">
         <v>597</v>
       </c>
@@ -11305,11 +11260,11 @@
       <c r="C484" t="s">
         <v>1024</v>
       </c>
-      <c r="E484" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="485" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D484" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="485" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A485">
         <v>598</v>
       </c>
@@ -11319,11 +11274,11 @@
       <c r="C485" t="s">
         <v>1025</v>
       </c>
-      <c r="E485" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="486" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D485" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="486" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A486">
         <v>599</v>
       </c>
@@ -11333,11 +11288,11 @@
       <c r="C486" t="s">
         <v>1026</v>
       </c>
-      <c r="E486" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="487" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D486" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="487" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A487">
         <v>600</v>
       </c>
@@ -11347,11 +11302,11 @@
       <c r="C487" t="s">
         <v>1027</v>
       </c>
-      <c r="E487" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="488" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D487" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="488" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A488">
         <v>601</v>
       </c>
@@ -11361,11 +11316,11 @@
       <c r="C488" t="s">
         <v>1028</v>
       </c>
-      <c r="E488" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="489" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D488" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="489" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A489">
         <v>602</v>
       </c>
@@ -11375,11 +11330,11 @@
       <c r="C489" t="s">
         <v>1029</v>
       </c>
-      <c r="E489" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="490" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D489" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="490" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A490">
         <v>603</v>
       </c>
@@ -11389,11 +11344,11 @@
       <c r="C490" t="s">
         <v>1030</v>
       </c>
-      <c r="E490" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="491" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D490" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="491" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A491">
         <v>604</v>
       </c>
@@ -11403,11 +11358,11 @@
       <c r="C491" t="s">
         <v>1031</v>
       </c>
-      <c r="E491" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="492" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D491" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="492" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A492">
         <v>605</v>
       </c>
@@ -11417,11 +11372,11 @@
       <c r="C492" t="s">
         <v>1032</v>
       </c>
-      <c r="E492" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="493" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D492" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="493" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A493">
         <v>606</v>
       </c>
@@ -11431,11 +11386,11 @@
       <c r="C493" t="s">
         <v>1033</v>
       </c>
-      <c r="E493" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="494" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D493" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="494" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A494">
         <v>607</v>
       </c>
@@ -11445,11 +11400,11 @@
       <c r="C494" t="s">
         <v>1034</v>
       </c>
-      <c r="E494" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="495" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D494" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="495" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A495">
         <v>608</v>
       </c>
@@ -11459,11 +11414,11 @@
       <c r="C495" t="s">
         <v>1035</v>
       </c>
-      <c r="E495" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="496" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D495" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="496" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A496">
         <v>609</v>
       </c>
@@ -11473,11 +11428,11 @@
       <c r="C496" t="s">
         <v>1036</v>
       </c>
-      <c r="E496" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="497" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D496" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="497" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A497">
         <v>610</v>
       </c>
@@ -11487,11 +11442,11 @@
       <c r="C497" t="s">
         <v>1037</v>
       </c>
-      <c r="E497" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="498" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D497" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="498" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A498">
         <v>611</v>
       </c>
@@ -11501,11 +11456,11 @@
       <c r="C498" t="s">
         <v>1038</v>
       </c>
-      <c r="E498" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="499" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D498" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="499" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A499">
         <v>612</v>
       </c>
@@ -11515,11 +11470,11 @@
       <c r="C499" t="s">
         <v>1039</v>
       </c>
-      <c r="E499" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="500" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D499" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="500" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A500">
         <v>613</v>
       </c>
@@ -11529,11 +11484,11 @@
       <c r="C500" t="s">
         <v>1040</v>
       </c>
-      <c r="E500" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="501" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D500" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="501" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A501">
         <v>614</v>
       </c>
@@ -11543,11 +11498,11 @@
       <c r="C501" t="s">
         <v>1041</v>
       </c>
-      <c r="E501" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="502" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D501" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="502" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A502">
         <v>615</v>
       </c>
@@ -11557,11 +11512,11 @@
       <c r="C502" t="s">
         <v>1042</v>
       </c>
-      <c r="E502" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="503" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D502" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="503" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A503">
         <v>616</v>
       </c>
@@ -11571,11 +11526,11 @@
       <c r="C503" t="s">
         <v>1043</v>
       </c>
-      <c r="E503" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="504" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D503" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="504" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A504">
         <v>617</v>
       </c>
@@ -11585,11 +11540,11 @@
       <c r="C504" t="s">
         <v>1044</v>
       </c>
-      <c r="E504" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="505" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D504" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="505" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A505">
         <v>618</v>
       </c>
@@ -11599,11 +11554,11 @@
       <c r="C505" t="s">
         <v>1045</v>
       </c>
-      <c r="E505" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="506" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D505" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="506" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A506">
         <v>619</v>
       </c>
@@ -11613,11 +11568,11 @@
       <c r="C506" t="s">
         <v>1046</v>
       </c>
-      <c r="E506" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="507" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D506" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="507" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A507">
         <v>620</v>
       </c>
@@ -11627,11 +11582,11 @@
       <c r="C507" t="s">
         <v>1047</v>
       </c>
-      <c r="E507" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="508" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D507" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="508" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A508">
         <v>621</v>
       </c>
@@ -11641,11 +11596,11 @@
       <c r="C508" t="s">
         <v>1048</v>
       </c>
-      <c r="E508" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="509" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D508" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="509" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A509">
         <v>622</v>
       </c>
@@ -11655,11 +11610,11 @@
       <c r="C509" t="s">
         <v>1049</v>
       </c>
-      <c r="E509" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="510" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D509" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="510" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A510">
         <v>623</v>
       </c>
@@ -11669,11 +11624,11 @@
       <c r="C510" t="s">
         <v>1050</v>
       </c>
-      <c r="E510" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="511" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D510" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="511" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A511">
         <v>624</v>
       </c>
@@ -11683,11 +11638,11 @@
       <c r="C511" t="s">
         <v>1051</v>
       </c>
-      <c r="E511" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="512" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D511" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="512" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A512">
         <v>625</v>
       </c>
@@ -11697,11 +11652,11 @@
       <c r="C512" t="s">
         <v>1052</v>
       </c>
-      <c r="E512" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="513" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D512" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="513" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A513">
         <v>626</v>
       </c>
@@ -11711,11 +11666,11 @@
       <c r="C513" t="s">
         <v>1053</v>
       </c>
-      <c r="E513" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="514" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D513" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="514" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A514">
         <v>627</v>
       </c>
@@ -11725,11 +11680,11 @@
       <c r="C514" t="s">
         <v>1054</v>
       </c>
-      <c r="E514" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="515" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D514" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="515" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A515">
         <v>628</v>
       </c>
@@ -11739,11 +11694,11 @@
       <c r="C515" t="s">
         <v>1055</v>
       </c>
-      <c r="E515" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="516" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D515" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="516" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A516">
         <v>629</v>
       </c>
@@ -11753,11 +11708,11 @@
       <c r="C516" t="s">
         <v>1056</v>
       </c>
-      <c r="E516" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="517" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D516" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="517" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A517">
         <v>630</v>
       </c>
@@ -11767,11 +11722,11 @@
       <c r="C517" t="s">
         <v>1057</v>
       </c>
-      <c r="E517" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="518" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D517" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="518" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A518">
         <v>631</v>
       </c>
@@ -11781,11 +11736,11 @@
       <c r="C518" t="s">
         <v>1058</v>
       </c>
-      <c r="E518" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="519" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D518" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="519" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A519">
         <v>632</v>
       </c>
@@ -11795,11 +11750,11 @@
       <c r="C519" t="s">
         <v>1059</v>
       </c>
-      <c r="E519" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="520" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D519" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="520" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A520">
         <v>633</v>
       </c>
@@ -11809,11 +11764,11 @@
       <c r="C520" t="s">
         <v>1060</v>
       </c>
-      <c r="E520" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="521" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D520" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="521" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A521">
         <v>634</v>
       </c>
@@ -11823,11 +11778,11 @@
       <c r="C521" t="s">
         <v>1061</v>
       </c>
-      <c r="E521" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="522" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D521" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="522" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A522">
         <v>635</v>
       </c>
@@ -11837,11 +11792,11 @@
       <c r="C522" t="s">
         <v>1062</v>
       </c>
-      <c r="E522" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="523" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D522" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="523" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A523">
         <v>636</v>
       </c>
@@ -11851,11 +11806,11 @@
       <c r="C523" t="s">
         <v>1063</v>
       </c>
-      <c r="E523" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="524" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D523" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="524" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A524">
         <v>637</v>
       </c>
@@ -11865,11 +11820,11 @@
       <c r="C524" t="s">
         <v>1064</v>
       </c>
-      <c r="E524" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="525" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D524" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="525" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A525">
         <v>638</v>
       </c>
@@ -11879,11 +11834,11 @@
       <c r="C525" t="s">
         <v>1065</v>
       </c>
-      <c r="E525" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="526" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D525" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="526" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A526">
         <v>639</v>
       </c>
@@ -11893,11 +11848,11 @@
       <c r="C526" t="s">
         <v>1066</v>
       </c>
-      <c r="E526" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="527" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D526" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="527" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A527">
         <v>640</v>
       </c>
@@ -11907,11 +11862,11 @@
       <c r="C527" t="s">
         <v>1067</v>
       </c>
-      <c r="E527" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="528" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D527" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="528" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A528">
         <v>641</v>
       </c>
@@ -11921,11 +11876,11 @@
       <c r="C528" t="s">
         <v>1068</v>
       </c>
-      <c r="E528" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="529" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D528" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="529" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A529">
         <v>642</v>
       </c>
@@ -11935,11 +11890,11 @@
       <c r="C529" t="s">
         <v>1069</v>
       </c>
-      <c r="E529" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="530" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D529" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="530" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A530">
         <v>643</v>
       </c>
@@ -11949,11 +11904,11 @@
       <c r="C530" t="s">
         <v>1070</v>
       </c>
-      <c r="E530" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="531" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D530" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="531" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A531">
         <v>644</v>
       </c>
@@ -11963,11 +11918,11 @@
       <c r="C531" t="s">
         <v>1071</v>
       </c>
-      <c r="E531" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="532" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D531" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="532" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A532">
         <v>645</v>
       </c>
@@ -11977,11 +11932,11 @@
       <c r="C532" t="s">
         <v>1072</v>
       </c>
-      <c r="E532" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="533" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D532" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="533" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A533">
         <v>646</v>
       </c>
@@ -11991,11 +11946,11 @@
       <c r="C533" t="s">
         <v>1073</v>
       </c>
-      <c r="E533" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="534" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D533" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="534" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A534">
         <v>647</v>
       </c>
@@ -12005,11 +11960,11 @@
       <c r="C534" t="s">
         <v>1074</v>
       </c>
-      <c r="E534" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="535" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D534" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="535" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A535">
         <v>648</v>
       </c>
@@ -12019,11 +11974,11 @@
       <c r="C535" t="s">
         <v>1075</v>
       </c>
-      <c r="E535" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="536" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D535" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="536" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A536">
         <v>649</v>
       </c>
@@ -12033,11 +11988,11 @@
       <c r="C536" t="s">
         <v>1076</v>
       </c>
-      <c r="E536" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="537" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D536" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="537" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A537">
         <v>650</v>
       </c>
@@ -12047,11 +12002,11 @@
       <c r="C537" t="s">
         <v>1077</v>
       </c>
-      <c r="E537" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="538" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D537" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="538" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A538">
         <v>651</v>
       </c>
@@ -12061,11 +12016,11 @@
       <c r="C538" t="s">
         <v>1078</v>
       </c>
-      <c r="E538" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="539" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D538" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="539" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A539">
         <v>652</v>
       </c>
@@ -12075,11 +12030,11 @@
       <c r="C539" t="s">
         <v>1079</v>
       </c>
-      <c r="E539" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="540" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D539" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="540" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A540">
         <v>653</v>
       </c>
@@ -12089,11 +12044,11 @@
       <c r="C540" t="s">
         <v>1080</v>
       </c>
-      <c r="E540" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="541" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D540" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="541" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A541">
         <v>654</v>
       </c>
@@ -12106,7 +12061,7 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="F6" r:id="rId1" xr:uid="{E98772F5-F3A2-4178-B97F-E8A8C6014580}"/>
+    <hyperlink ref="E6" r:id="rId1" xr:uid="{E98772F5-F3A2-4178-B97F-E8A8C6014580}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId2"/>

--- a/database/Take Notes/RL/RL.xlsx
+++ b/database/Take Notes/RL/RL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Cursor AI\database\Take Notes\RL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43C590F8-9C35-4A49-8ACC-1E718FF65A62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD172A36-C4F0-46D3-83EF-ABE0F90B7ADF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1631" uniqueCount="1100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1632" uniqueCount="1101">
   <si>
     <t>ID</t>
   </si>
@@ -4063,6 +4063,9 @@
 Well done! fuel is a material that is burned to produce energy.
 Thanks for listening and learning with us today. We hope this episode helped you understand both the science and the English a little better. Keep practicing, stay curious, and remember that learning happens step by step.
 That’s the end of the video! I’m Bel — like and subscribe for Better English Learning!</t>
+  </si>
+  <si>
+    <t>https://youtu.be/XA1Fx0n4DRo</t>
   </si>
 </sst>
 </file>
@@ -5509,6 +5512,9 @@
       <c r="D73" t="s">
         <v>1089</v>
       </c>
+      <c r="E73" t="s">
+        <v>1100</v>
+      </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74">
